--- a/data/cox_xlsx/HHDC.CO.xlsx
+++ b/data/cox_xlsx/HHDC.CO.xlsx
@@ -1317,7 +1317,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="[&gt;=100]#,###0.0\%;[&lt;=-100]-#,###0.0\%;#,###0.0\%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -1360,6 +1360,12 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FFF5475B"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1431,7 +1437,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1498,13 +1504,19 @@
     <xf borderId="3" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -3092,14 +3104,30 @@
       <c r="O32" s="19">
         <v>90.67</v>
       </c>
-      <c r="P32" s="18"/>
-      <c r="Q32" s="18"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="18"/>
-      <c r="V32" s="18"/>
-      <c r="W32" s="18"/>
+      <c r="P32" s="22">
+        <v>121.36</v>
+      </c>
+      <c r="Q32" s="22">
+        <v>124.71</v>
+      </c>
+      <c r="R32" s="22">
+        <v>261.93</v>
+      </c>
+      <c r="S32" s="22">
+        <v>382.75</v>
+      </c>
+      <c r="T32" s="22">
+        <v>386.04</v>
+      </c>
+      <c r="U32" s="22">
+        <v>360.62</v>
+      </c>
+      <c r="V32" s="22">
+        <v>299.85</v>
+      </c>
+      <c r="W32" s="22">
+        <v>345.58</v>
+      </c>
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
@@ -3577,7 +3605,7 @@
       <c r="K41" s="20">
         <v>-22.99</v>
       </c>
-      <c r="L41" s="22">
+      <c r="L41" s="23">
         <v>-102.21</v>
       </c>
       <c r="M41" s="20">
@@ -4156,13 +4184,34 @@
       <c r="P55" s="15">
         <v>106.65</v>
       </c>
-      <c r="Q55" s="18"/>
-      <c r="R55" s="18"/>
-      <c r="S55" s="18"/>
-      <c r="T55" s="18"/>
-      <c r="U55" s="18"/>
-      <c r="V55" s="18"/>
-      <c r="W55" s="18"/>
+      <c r="Q55" s="24">
+        <f t="shared" ref="Q55:W55" si="1">Q56+Q57</f>
+        <v>127.84</v>
+      </c>
+      <c r="R55" s="24">
+        <f t="shared" si="1"/>
+        <v>142.46</v>
+      </c>
+      <c r="S55" s="24">
+        <f t="shared" si="1"/>
+        <v>128.69</v>
+      </c>
+      <c r="T55" s="24">
+        <f t="shared" si="1"/>
+        <v>125.37</v>
+      </c>
+      <c r="U55" s="24">
+        <f t="shared" si="1"/>
+        <v>114.02</v>
+      </c>
+      <c r="V55" s="24">
+        <f t="shared" si="1"/>
+        <v>94.21</v>
+      </c>
+      <c r="W55" s="18">
+        <f t="shared" si="1"/>
+        <v>89.89</v>
+      </c>
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
@@ -4350,7 +4399,7 @@
       <c r="B59" s="18">
         <v>0.0</v>
       </c>
-      <c r="C59" s="22">
+      <c r="C59" s="23">
         <v>-243.08</v>
       </c>
       <c r="D59" s="18"/>
@@ -4642,7 +4691,7 @@
       <c r="O66" s="17">
         <v>237.69</v>
       </c>
-      <c r="P66" s="23">
+      <c r="P66" s="25">
         <v>-9.85</v>
       </c>
       <c r="Q66" s="17">
@@ -4700,13 +4749,13 @@
       <c r="A68" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B68" s="24">
+      <c r="B68" s="26">
         <v>-873.55</v>
       </c>
-      <c r="C68" s="25">
+      <c r="C68" s="27">
         <v>63.89</v>
       </c>
-      <c r="D68" s="24">
+      <c r="D68" s="26">
         <v>-352.24</v>
       </c>
       <c r="E68" s="17">
@@ -4733,37 +4782,37 @@
       <c r="L68" s="17">
         <v>156.36</v>
       </c>
-      <c r="M68" s="25">
+      <c r="M68" s="27">
         <v>50.45</v>
       </c>
-      <c r="N68" s="25">
+      <c r="N68" s="27">
         <v>6.16</v>
       </c>
-      <c r="O68" s="25">
+      <c r="O68" s="27">
         <v>35.76</v>
       </c>
-      <c r="P68" s="23">
+      <c r="P68" s="25">
         <v>-9.85</v>
       </c>
-      <c r="Q68" s="24">
+      <c r="Q68" s="26">
         <v>-1282.9</v>
       </c>
-      <c r="R68" s="24">
+      <c r="R68" s="26">
         <v>-240.71</v>
       </c>
-      <c r="S68" s="24">
+      <c r="S68" s="26">
         <v>-703.56</v>
       </c>
       <c r="T68" s="17">
         <v>239.22</v>
       </c>
-      <c r="U68" s="24">
+      <c r="U68" s="26">
         <v>-774.14</v>
       </c>
       <c r="V68" s="17">
         <v>152.21</v>
       </c>
-      <c r="W68" s="24">
+      <c r="W68" s="26">
         <v>-337.74</v>
       </c>
     </row>
@@ -5017,13 +5066,13 @@
       <c r="A73" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B73" s="22">
+      <c r="B73" s="23">
         <v>-144.29</v>
       </c>
-      <c r="C73" s="22">
+      <c r="C73" s="23">
         <v>-169.85</v>
       </c>
-      <c r="D73" s="22">
+      <c r="D73" s="23">
         <v>-117.92</v>
       </c>
       <c r="E73" s="20">
@@ -5035,7 +5084,7 @@
       <c r="G73" s="20">
         <v>-38.85</v>
       </c>
-      <c r="H73" s="22">
+      <c r="H73" s="23">
         <v>-203.1</v>
       </c>
       <c r="I73" s="20">
@@ -5074,13 +5123,13 @@
       <c r="A74" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B74" s="22">
+      <c r="B74" s="23">
         <v>-119.19</v>
       </c>
-      <c r="C74" s="22">
+      <c r="C74" s="23">
         <v>-154.26</v>
       </c>
-      <c r="D74" s="22">
+      <c r="D74" s="23">
         <v>-101.08</v>
       </c>
       <c r="E74" s="20">
@@ -5184,10 +5233,10 @@
       <c r="A76" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B76" s="22">
+      <c r="B76" s="23">
         <v>-108.21</v>
       </c>
-      <c r="C76" s="22">
+      <c r="C76" s="23">
         <v>-143.36</v>
       </c>
       <c r="D76" s="20">
@@ -5233,7 +5282,7 @@
       <c r="G77" s="18">
         <v>0.0</v>
       </c>
-      <c r="H77" s="22">
+      <c r="H77" s="23">
         <v>-159.58</v>
       </c>
       <c r="I77" s="18"/>
@@ -5657,59 +5706,59 @@
       <c r="A87" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B87" s="25">
         <v>-73.71</v>
       </c>
-      <c r="C87" s="24">
+      <c r="C87" s="26">
         <v>-109.08</v>
       </c>
-      <c r="D87" s="23">
+      <c r="D87" s="25">
         <v>-81.17</v>
       </c>
-      <c r="E87" s="23">
+      <c r="E87" s="25">
         <v>-20.36</v>
       </c>
-      <c r="F87" s="23">
+      <c r="F87" s="25">
         <v>-28.7</v>
       </c>
-      <c r="G87" s="23">
+      <c r="G87" s="25">
         <v>-35.97</v>
       </c>
-      <c r="H87" s="24">
+      <c r="H87" s="26">
         <v>-201.78</v>
       </c>
-      <c r="I87" s="23">
+      <c r="I87" s="25">
         <v>-48.96</v>
       </c>
-      <c r="J87" s="23">
+      <c r="J87" s="25">
         <v>-23.48</v>
       </c>
-      <c r="K87" s="23">
+      <c r="K87" s="25">
         <v>-26.86</v>
       </c>
-      <c r="L87" s="23">
+      <c r="L87" s="25">
         <v>-44.22</v>
       </c>
-      <c r="M87" s="23">
+      <c r="M87" s="25">
         <v>-49.62</v>
       </c>
-      <c r="N87" s="23">
+      <c r="N87" s="25">
         <v>-44.48</v>
       </c>
-      <c r="O87" s="23">
+      <c r="O87" s="25">
         <v>-43.09</v>
       </c>
-      <c r="P87" s="23">
+      <c r="P87" s="25">
         <v>-52.66</v>
       </c>
       <c r="Q87" s="21"/>
       <c r="R87" s="21"/>
       <c r="S87" s="21"/>
-      <c r="T87" s="23">
+      <c r="T87" s="25">
         <v>-18.67</v>
       </c>
       <c r="U87" s="21"/>
-      <c r="V87" s="25">
+      <c r="V87" s="27">
         <v>6.69</v>
       </c>
       <c r="W87" s="21"/>
@@ -5718,13 +5767,13 @@
       <c r="A88" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="B88" s="24">
+      <c r="B88" s="26">
         <v>-947.26</v>
       </c>
-      <c r="C88" s="23">
+      <c r="C88" s="25">
         <v>-45.19</v>
       </c>
-      <c r="D88" s="24">
+      <c r="D88" s="26">
         <v>-433.4</v>
       </c>
       <c r="E88" s="17">
@@ -5751,25 +5800,25 @@
       <c r="L88" s="17">
         <v>112.14</v>
       </c>
-      <c r="M88" s="25">
+      <c r="M88" s="27">
         <v>0.84</v>
       </c>
-      <c r="N88" s="23">
+      <c r="N88" s="25">
         <v>-38.32</v>
       </c>
-      <c r="O88" s="23">
+      <c r="O88" s="25">
         <v>-7.33</v>
       </c>
-      <c r="P88" s="23">
+      <c r="P88" s="25">
         <v>-62.51</v>
       </c>
-      <c r="Q88" s="24">
+      <c r="Q88" s="26">
         <v>-295.09</v>
       </c>
-      <c r="R88" s="24">
+      <c r="R88" s="26">
         <v>-308.95</v>
       </c>
-      <c r="S88" s="25">
+      <c r="S88" s="27">
         <v>1.52</v>
       </c>
       <c r="T88" s="17">
@@ -6329,70 +6378,70 @@
       <c r="A99" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="B99" s="25">
+      <c r="B99" s="27">
         <v>95.67</v>
       </c>
-      <c r="C99" s="25">
+      <c r="C99" s="27">
         <v>32.72</v>
       </c>
-      <c r="D99" s="23">
+      <c r="D99" s="25">
         <v>-56.66</v>
       </c>
       <c r="E99" s="17">
         <v>109.93</v>
       </c>
-      <c r="F99" s="25">
+      <c r="F99" s="27">
         <v>47.83</v>
       </c>
-      <c r="G99" s="25">
+      <c r="G99" s="27">
         <v>80.58</v>
       </c>
-      <c r="H99" s="25">
+      <c r="H99" s="27">
         <v>72.53</v>
       </c>
       <c r="I99" s="21">
         <v>0.0</v>
       </c>
-      <c r="J99" s="25">
+      <c r="J99" s="27">
         <v>25.91</v>
       </c>
-      <c r="K99" s="25">
+      <c r="K99" s="27">
         <v>9.94</v>
       </c>
-      <c r="L99" s="25">
+      <c r="L99" s="27">
         <v>42.11</v>
       </c>
-      <c r="M99" s="25">
+      <c r="M99" s="27">
         <v>8.47</v>
       </c>
-      <c r="N99" s="25">
+      <c r="N99" s="27">
         <v>3.69</v>
       </c>
-      <c r="O99" s="25">
+      <c r="O99" s="27">
         <v>29.68</v>
       </c>
-      <c r="P99" s="25">
+      <c r="P99" s="27">
         <v>16.84</v>
       </c>
-      <c r="Q99" s="23">
+      <c r="Q99" s="25">
         <v>-22.65</v>
       </c>
-      <c r="R99" s="23">
+      <c r="R99" s="25">
         <v>-36.35</v>
       </c>
-      <c r="S99" s="23">
+      <c r="S99" s="25">
         <v>-0.31</v>
       </c>
-      <c r="T99" s="25">
+      <c r="T99" s="27">
         <v>51.19</v>
       </c>
-      <c r="U99" s="25">
+      <c r="U99" s="27">
         <v>42.91</v>
       </c>
-      <c r="V99" s="25">
+      <c r="V99" s="27">
         <v>51.06</v>
       </c>
-      <c r="W99" s="25">
+      <c r="W99" s="27">
         <v>59.92</v>
       </c>
     </row>
@@ -6417,10 +6466,10 @@
       <c r="P100" s="18"/>
       <c r="Q100" s="18"/>
       <c r="R100" s="18"/>
-      <c r="S100" s="26">
+      <c r="S100" s="28">
         <v>0.0</v>
       </c>
-      <c r="T100" s="26">
+      <c r="T100" s="28">
         <v>0.0</v>
       </c>
       <c r="U100" s="18"/>
@@ -6460,13 +6509,13 @@
       <c r="A102" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="B102" s="24">
+      <c r="B102" s="26">
         <v>-1042.93</v>
       </c>
-      <c r="C102" s="23">
+      <c r="C102" s="25">
         <v>-77.91</v>
       </c>
-      <c r="D102" s="24">
+      <c r="D102" s="26">
         <v>-376.74</v>
       </c>
       <c r="E102" s="17">
@@ -6490,34 +6539,34 @@
       <c r="K102" s="17">
         <v>119.67</v>
       </c>
-      <c r="L102" s="25">
+      <c r="L102" s="27">
         <v>70.04</v>
       </c>
-      <c r="M102" s="23">
+      <c r="M102" s="25">
         <v>-7.63</v>
       </c>
-      <c r="N102" s="23">
+      <c r="N102" s="25">
         <v>-42.01</v>
       </c>
-      <c r="O102" s="23">
+      <c r="O102" s="25">
         <v>-37.01</v>
       </c>
-      <c r="P102" s="23">
+      <c r="P102" s="25">
         <v>-79.35</v>
       </c>
-      <c r="Q102" s="24">
+      <c r="Q102" s="26">
         <v>-282.65</v>
       </c>
-      <c r="R102" s="24">
+      <c r="R102" s="26">
         <v>-272.6</v>
       </c>
-      <c r="S102" s="25">
+      <c r="S102" s="27">
         <v>1.83</v>
       </c>
       <c r="T102" s="17">
         <v>169.36</v>
       </c>
-      <c r="U102" s="25">
+      <c r="U102" s="27">
         <v>80.12</v>
       </c>
       <c r="V102" s="17">
@@ -6531,13 +6580,13 @@
       <c r="A103" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B103" s="24">
+      <c r="B103" s="26">
         <v>-1038.23</v>
       </c>
-      <c r="C103" s="23">
+      <c r="C103" s="25">
         <v>-82.59</v>
       </c>
-      <c r="D103" s="24">
+      <c r="D103" s="26">
         <v>-379.8</v>
       </c>
       <c r="E103" s="17">
@@ -6561,34 +6610,34 @@
       <c r="K103" s="17">
         <v>119.67</v>
       </c>
-      <c r="L103" s="25">
+      <c r="L103" s="27">
         <v>70.04</v>
       </c>
-      <c r="M103" s="23">
+      <c r="M103" s="25">
         <v>-7.63</v>
       </c>
-      <c r="N103" s="23">
+      <c r="N103" s="25">
         <v>-42.01</v>
       </c>
-      <c r="O103" s="23">
+      <c r="O103" s="25">
         <v>-37.01</v>
       </c>
-      <c r="P103" s="23">
+      <c r="P103" s="25">
         <v>-79.35</v>
       </c>
-      <c r="Q103" s="24">
+      <c r="Q103" s="26">
         <v>-282.65</v>
       </c>
-      <c r="R103" s="24">
+      <c r="R103" s="26">
         <v>-272.6</v>
       </c>
-      <c r="S103" s="25">
+      <c r="S103" s="27">
         <v>1.83</v>
       </c>
       <c r="T103" s="17">
         <v>169.36</v>
       </c>
-      <c r="U103" s="25">
+      <c r="U103" s="27">
         <v>80.12</v>
       </c>
       <c r="V103" s="17">
@@ -6625,10 +6674,10 @@
       <c r="T104" s="21">
         <v>0.0</v>
       </c>
-      <c r="U104" s="23">
+      <c r="U104" s="25">
         <v>-0.39</v>
       </c>
-      <c r="V104" s="23">
+      <c r="V104" s="25">
         <v>-0.02</v>
       </c>
       <c r="W104" s="21">
@@ -6690,25 +6739,25 @@
       <c r="A106" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B106" s="25">
+      <c r="B106" s="27">
         <v>4.7</v>
       </c>
-      <c r="C106" s="23">
+      <c r="C106" s="25">
         <v>-4.67</v>
       </c>
-      <c r="D106" s="23">
+      <c r="D106" s="25">
         <v>-3.06</v>
       </c>
-      <c r="E106" s="23">
+      <c r="E106" s="25">
         <v>-19.0</v>
       </c>
-      <c r="F106" s="23">
+      <c r="F106" s="25">
         <v>-15.03</v>
       </c>
-      <c r="G106" s="23">
+      <c r="G106" s="25">
         <v>-14.39</v>
       </c>
-      <c r="H106" s="23">
+      <c r="H106" s="25">
         <v>-1.32</v>
       </c>
       <c r="I106" s="21"/>
@@ -6790,28 +6839,28 @@
       <c r="I108" s="21">
         <v>0.0</v>
       </c>
-      <c r="J108" s="23">
+      <c r="J108" s="25">
         <v>-6.64</v>
       </c>
-      <c r="K108" s="23">
+      <c r="K108" s="25">
         <v>-8.39</v>
       </c>
-      <c r="L108" s="23">
+      <c r="L108" s="25">
         <v>-22.96</v>
       </c>
-      <c r="M108" s="23">
+      <c r="M108" s="25">
         <v>-18.23</v>
       </c>
-      <c r="N108" s="23">
+      <c r="N108" s="25">
         <v>-54.84</v>
       </c>
-      <c r="O108" s="23">
+      <c r="O108" s="25">
         <v>-45.71</v>
       </c>
-      <c r="P108" s="23">
+      <c r="P108" s="25">
         <v>-50.89</v>
       </c>
-      <c r="Q108" s="23">
+      <c r="Q108" s="25">
         <v>-8.13</v>
       </c>
       <c r="R108" s="21"/>
@@ -6821,7 +6870,7 @@
       <c r="V108" s="21">
         <v>0.0</v>
       </c>
-      <c r="W108" s="25">
+      <c r="W108" s="27">
         <v>5.51</v>
       </c>
     </row>
@@ -6860,13 +6909,13 @@
       <c r="A110" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B110" s="24">
+      <c r="B110" s="26">
         <v>-1038.23</v>
       </c>
-      <c r="C110" s="23">
+      <c r="C110" s="25">
         <v>-82.59</v>
       </c>
-      <c r="D110" s="24">
+      <c r="D110" s="26">
         <v>-379.8</v>
       </c>
       <c r="E110" s="17">
@@ -6890,34 +6939,34 @@
       <c r="K110" s="17">
         <v>111.28</v>
       </c>
-      <c r="L110" s="25">
+      <c r="L110" s="27">
         <v>47.07</v>
       </c>
-      <c r="M110" s="23">
+      <c r="M110" s="25">
         <v>-25.86</v>
       </c>
-      <c r="N110" s="23">
+      <c r="N110" s="25">
         <v>-96.85</v>
       </c>
-      <c r="O110" s="23">
+      <c r="O110" s="25">
         <v>-82.72</v>
       </c>
-      <c r="P110" s="24">
+      <c r="P110" s="26">
         <v>-130.24</v>
       </c>
-      <c r="Q110" s="24">
+      <c r="Q110" s="26">
         <v>-290.78</v>
       </c>
-      <c r="R110" s="24">
+      <c r="R110" s="26">
         <v>-272.6</v>
       </c>
-      <c r="S110" s="25">
+      <c r="S110" s="27">
         <v>1.83</v>
       </c>
       <c r="T110" s="17">
         <v>169.36</v>
       </c>
-      <c r="U110" s="25">
+      <c r="U110" s="27">
         <v>80.51</v>
       </c>
       <c r="V110" s="17">
@@ -6931,13 +6980,13 @@
       <c r="A111" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="B111" s="24">
+      <c r="B111" s="26">
         <v>-1038.23</v>
       </c>
-      <c r="C111" s="23">
+      <c r="C111" s="25">
         <v>-82.59</v>
       </c>
-      <c r="D111" s="24">
+      <c r="D111" s="26">
         <v>-379.8</v>
       </c>
       <c r="E111" s="17">
@@ -6961,34 +7010,34 @@
       <c r="K111" s="17">
         <v>119.67</v>
       </c>
-      <c r="L111" s="25">
+      <c r="L111" s="27">
         <v>70.04</v>
       </c>
-      <c r="M111" s="23">
+      <c r="M111" s="25">
         <v>-7.63</v>
       </c>
-      <c r="N111" s="23">
+      <c r="N111" s="25">
         <v>-42.01</v>
       </c>
-      <c r="O111" s="23">
+      <c r="O111" s="25">
         <v>-37.01</v>
       </c>
-      <c r="P111" s="23">
+      <c r="P111" s="25">
         <v>-79.35</v>
       </c>
-      <c r="Q111" s="24">
+      <c r="Q111" s="26">
         <v>-282.65</v>
       </c>
-      <c r="R111" s="24">
+      <c r="R111" s="26">
         <v>-272.6</v>
       </c>
-      <c r="S111" s="25">
+      <c r="S111" s="27">
         <v>1.83</v>
       </c>
       <c r="T111" s="17">
         <v>169.36</v>
       </c>
-      <c r="U111" s="25">
+      <c r="U111" s="27">
         <v>80.51</v>
       </c>
       <c r="V111" s="17">
@@ -7002,13 +7051,13 @@
       <c r="A112" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B112" s="24">
+      <c r="B112" s="26">
         <v>-1038.23</v>
       </c>
-      <c r="C112" s="23">
+      <c r="C112" s="25">
         <v>-82.59</v>
       </c>
-      <c r="D112" s="24">
+      <c r="D112" s="26">
         <v>-379.8</v>
       </c>
       <c r="E112" s="17">
@@ -7032,34 +7081,34 @@
       <c r="K112" s="17">
         <v>111.28</v>
       </c>
-      <c r="L112" s="25">
+      <c r="L112" s="27">
         <v>47.07</v>
       </c>
-      <c r="M112" s="23">
+      <c r="M112" s="25">
         <v>-25.86</v>
       </c>
-      <c r="N112" s="23">
+      <c r="N112" s="25">
         <v>-96.85</v>
       </c>
-      <c r="O112" s="23">
+      <c r="O112" s="25">
         <v>-82.72</v>
       </c>
-      <c r="P112" s="24">
+      <c r="P112" s="26">
         <v>-130.24</v>
       </c>
-      <c r="Q112" s="24">
+      <c r="Q112" s="26">
         <v>-290.78</v>
       </c>
-      <c r="R112" s="24">
+      <c r="R112" s="26">
         <v>-272.6</v>
       </c>
-      <c r="S112" s="25">
+      <c r="S112" s="27">
         <v>1.83</v>
       </c>
       <c r="T112" s="17">
         <v>169.36</v>
       </c>
-      <c r="U112" s="25">
+      <c r="U112" s="27">
         <v>80.51</v>
       </c>
       <c r="V112" s="17">
@@ -7073,13 +7122,13 @@
       <c r="A113" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B113" s="22">
+      <c r="B113" s="23">
         <v>-1042.93</v>
       </c>
       <c r="C113" s="20">
         <v>-77.91</v>
       </c>
-      <c r="D113" s="22">
+      <c r="D113" s="23">
         <v>-376.74</v>
       </c>
       <c r="E113" s="15">
@@ -7276,7 +7325,7 @@
       <c r="C118" s="19">
         <v>20.26</v>
       </c>
-      <c r="D118" s="22">
+      <c r="D118" s="23">
         <v>-104.14</v>
       </c>
       <c r="E118" s="19">
@@ -7285,7 +7334,7 @@
       <c r="F118" s="19">
         <v>64.23</v>
       </c>
-      <c r="G118" s="22">
+      <c r="G118" s="23">
         <v>-158.28</v>
       </c>
       <c r="H118" s="19">
@@ -7360,22 +7409,22 @@
       <c r="A120" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="B120" s="25">
+      <c r="B120" s="27">
         <v>20.39</v>
       </c>
-      <c r="C120" s="25">
+      <c r="C120" s="27">
         <v>38.96</v>
       </c>
-      <c r="D120" s="25">
+      <c r="D120" s="27">
         <v>4.59</v>
       </c>
       <c r="E120" s="21">
         <v>0.0</v>
       </c>
-      <c r="F120" s="25">
+      <c r="F120" s="27">
         <v>61.5</v>
       </c>
-      <c r="G120" s="24">
+      <c r="G120" s="26">
         <v>-197.13</v>
       </c>
       <c r="H120" s="17">
@@ -7384,7 +7433,7 @@
       <c r="I120" s="21">
         <v>0.0</v>
       </c>
-      <c r="J120" s="25">
+      <c r="J120" s="27">
         <v>10.36</v>
       </c>
       <c r="K120" s="21"/>
@@ -7405,13 +7454,13 @@
       <c r="A121" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="B121" s="24">
+      <c r="B121" s="26">
         <v>-1022.54</v>
       </c>
-      <c r="C121" s="23">
+      <c r="C121" s="25">
         <v>-38.96</v>
       </c>
-      <c r="D121" s="24">
+      <c r="D121" s="26">
         <v>-372.14</v>
       </c>
       <c r="E121" s="17">
@@ -7876,13 +7925,13 @@
       <c r="A128" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="B128" s="22">
+      <c r="B128" s="23">
         <v>-1038.23</v>
       </c>
       <c r="C128" s="20">
         <v>-82.59</v>
       </c>
-      <c r="D128" s="22">
+      <c r="D128" s="23">
         <v>-379.8</v>
       </c>
       <c r="E128" s="15">
@@ -7918,13 +7967,13 @@
       <c r="O128" s="20">
         <v>-82.72</v>
       </c>
-      <c r="P128" s="22">
+      <c r="P128" s="23">
         <v>-130.24</v>
       </c>
-      <c r="Q128" s="22">
+      <c r="Q128" s="23">
         <v>-290.78</v>
       </c>
-      <c r="R128" s="22">
+      <c r="R128" s="23">
         <v>-272.6</v>
       </c>
       <c r="S128" s="19">
@@ -7947,13 +7996,13 @@
       <c r="A129" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="B129" s="22">
+      <c r="B129" s="23">
         <v>-1038.23</v>
       </c>
       <c r="C129" s="20">
         <v>-82.59</v>
       </c>
-      <c r="D129" s="22">
+      <c r="D129" s="23">
         <v>-379.8</v>
       </c>
       <c r="E129" s="15">
@@ -7992,10 +8041,10 @@
       <c r="P129" s="20">
         <v>-79.35</v>
       </c>
-      <c r="Q129" s="22">
+      <c r="Q129" s="23">
         <v>-282.65</v>
       </c>
-      <c r="R129" s="22">
+      <c r="R129" s="23">
         <v>-272.6</v>
       </c>
       <c r="S129" s="19">
@@ -9276,13 +9325,13 @@
       <c r="A154" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B154" s="22">
+      <c r="B154" s="23">
         <v>-1038.23</v>
       </c>
       <c r="C154" s="20">
         <v>-82.59</v>
       </c>
-      <c r="D154" s="22">
+      <c r="D154" s="23">
         <v>-379.8</v>
       </c>
       <c r="E154" s="15">
@@ -9333,13 +9382,13 @@
       <c r="A155" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="B155" s="22">
+      <c r="B155" s="23">
         <v>-1038.23</v>
       </c>
       <c r="C155" s="20">
         <v>-82.59</v>
       </c>
-      <c r="D155" s="22">
+      <c r="D155" s="23">
         <v>-379.8</v>
       </c>
       <c r="E155" s="15">
@@ -9375,7 +9424,7 @@
       <c r="O155" s="20">
         <v>-82.72</v>
       </c>
-      <c r="P155" s="22">
+      <c r="P155" s="23">
         <v>-130.24</v>
       </c>
       <c r="Q155" s="18"/>
@@ -9390,13 +9439,13 @@
       <c r="A156" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="B156" s="22">
+      <c r="B156" s="23">
         <v>-1038.23</v>
       </c>
       <c r="C156" s="20">
         <v>-82.59</v>
       </c>
-      <c r="D156" s="22">
+      <c r="D156" s="23">
         <v>-379.8</v>
       </c>
       <c r="E156" s="15">
@@ -9447,13 +9496,13 @@
       <c r="A157" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="B157" s="22">
+      <c r="B157" s="23">
         <v>-1038.23</v>
       </c>
       <c r="C157" s="20">
         <v>-82.59</v>
       </c>
-      <c r="D157" s="22">
+      <c r="D157" s="23">
         <v>-379.8</v>
       </c>
       <c r="E157" s="15">
@@ -9489,7 +9538,7 @@
       <c r="O157" s="20">
         <v>-82.72</v>
       </c>
-      <c r="P157" s="22">
+      <c r="P157" s="23">
         <v>-130.24</v>
       </c>
       <c r="Q157" s="18"/>
@@ -11986,7 +12035,7 @@
       <c r="A37" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="B37" s="22">
+      <c r="B37" s="23">
         <v>-442.93</v>
       </c>
       <c r="C37" s="20">
@@ -12041,7 +12090,7 @@
       <c r="A38" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="23">
         <v>-166.1</v>
       </c>
       <c r="C38" s="18"/>
@@ -12223,25 +12272,25 @@
       <c r="A42" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="B42" s="22">
+      <c r="B42" s="23">
         <v>-449.26</v>
       </c>
-      <c r="C42" s="22">
+      <c r="C42" s="23">
         <v>-471.85</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="23">
         <v>-378.14</v>
       </c>
-      <c r="E42" s="22">
+      <c r="E42" s="23">
         <v>-304.61</v>
       </c>
-      <c r="F42" s="22">
+      <c r="F42" s="23">
         <v>-235.64</v>
       </c>
-      <c r="G42" s="22">
+      <c r="G42" s="23">
         <v>-198.52</v>
       </c>
-      <c r="H42" s="22">
+      <c r="H42" s="23">
         <v>-140.99</v>
       </c>
       <c r="I42" s="18"/>
@@ -12300,16 +12349,16 @@
       <c r="Q43" s="18"/>
       <c r="R43" s="18"/>
       <c r="S43" s="18"/>
-      <c r="T43" s="22">
+      <c r="T43" s="23">
         <v>-667.8</v>
       </c>
-      <c r="U43" s="22">
+      <c r="U43" s="23">
         <v>-595.7</v>
       </c>
-      <c r="V43" s="22">
+      <c r="V43" s="23">
         <v>-464.14</v>
       </c>
-      <c r="W43" s="22">
+      <c r="W43" s="23">
         <v>-395.61</v>
       </c>
     </row>
@@ -12496,49 +12545,49 @@
       <c r="A47" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="B47" s="22">
+      <c r="B47" s="23">
         <v>-1108.91</v>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="23">
         <v>-1079.41</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="23">
         <v>-1033.89</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="23">
         <v>-911.01</v>
       </c>
-      <c r="F47" s="22">
+      <c r="F47" s="23">
         <v>-832.13</v>
       </c>
-      <c r="G47" s="22">
+      <c r="G47" s="23">
         <v>-818.03</v>
       </c>
-      <c r="H47" s="22">
+      <c r="H47" s="23">
         <v>-744.49</v>
       </c>
       <c r="I47" s="18"/>
-      <c r="J47" s="22">
+      <c r="J47" s="23">
         <v>-311.5</v>
       </c>
       <c r="K47" s="18"/>
       <c r="L47" s="18"/>
-      <c r="M47" s="22">
+      <c r="M47" s="23">
         <v>-242.74</v>
       </c>
-      <c r="N47" s="22">
+      <c r="N47" s="23">
         <v>-203.95</v>
       </c>
-      <c r="O47" s="22">
+      <c r="O47" s="23">
         <v>-171.29</v>
       </c>
-      <c r="P47" s="22">
+      <c r="P47" s="23">
         <v>-168.63</v>
       </c>
       <c r="Q47" s="18"/>
       <c r="R47" s="18"/>
       <c r="S47" s="18"/>
-      <c r="T47" s="22">
+      <c r="T47" s="23">
         <v>-105.92</v>
       </c>
       <c r="U47" s="20">
@@ -12673,55 +12722,55 @@
       <c r="A50" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="B50" s="22">
+      <c r="B50" s="23">
         <v>-2674.99</v>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="23">
         <v>-3067.8</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="23">
         <v>-2884.08</v>
       </c>
-      <c r="E50" s="22">
+      <c r="E50" s="23">
         <v>-2559.58</v>
       </c>
-      <c r="F50" s="22">
+      <c r="F50" s="23">
         <v>-2352.31</v>
       </c>
-      <c r="G50" s="22">
+      <c r="G50" s="23">
         <v>-2331.59</v>
       </c>
-      <c r="H50" s="22">
+      <c r="H50" s="23">
         <v>-2244.01</v>
       </c>
       <c r="I50" s="18"/>
-      <c r="J50" s="22">
+      <c r="J50" s="23">
         <v>-1097.32</v>
       </c>
       <c r="K50" s="18"/>
       <c r="L50" s="18"/>
-      <c r="M50" s="22">
+      <c r="M50" s="23">
         <v>-998.06</v>
       </c>
-      <c r="N50" s="22">
+      <c r="N50" s="23">
         <v>-851.92</v>
       </c>
-      <c r="O50" s="22">
+      <c r="O50" s="23">
         <v>-781.41</v>
       </c>
-      <c r="P50" s="22">
+      <c r="P50" s="23">
         <v>-859.88</v>
       </c>
       <c r="Q50" s="18"/>
       <c r="R50" s="18"/>
       <c r="S50" s="18"/>
-      <c r="T50" s="22">
+      <c r="T50" s="23">
         <v>-501.71</v>
       </c>
-      <c r="U50" s="22">
+      <c r="U50" s="23">
         <v>-459.44</v>
       </c>
-      <c r="V50" s="22">
+      <c r="V50" s="23">
         <v>-362.52</v>
       </c>
       <c r="W50" s="18"/>
@@ -12842,43 +12891,43 @@
       <c r="A53" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="B53" s="22">
+      <c r="B53" s="23">
         <v>-382.82</v>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="23">
         <v>-407.15</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="23">
         <v>-375.14</v>
       </c>
-      <c r="E53" s="22">
+      <c r="E53" s="23">
         <v>-304.61</v>
       </c>
-      <c r="F53" s="22">
+      <c r="F53" s="23">
         <v>-262.57</v>
       </c>
-      <c r="G53" s="22">
+      <c r="G53" s="23">
         <v>-243.58</v>
       </c>
-      <c r="H53" s="22">
+      <c r="H53" s="23">
         <v>-164.71</v>
       </c>
       <c r="I53" s="18"/>
-      <c r="J53" s="22">
+      <c r="J53" s="23">
         <v>-174.84</v>
       </c>
       <c r="K53" s="18"/>
       <c r="L53" s="18"/>
-      <c r="M53" s="22">
+      <c r="M53" s="23">
         <v>-132.79</v>
       </c>
-      <c r="N53" s="22">
+      <c r="N53" s="23">
         <v>-132.68</v>
       </c>
-      <c r="O53" s="22">
+      <c r="O53" s="23">
         <v>-114.57</v>
       </c>
-      <c r="P53" s="22">
+      <c r="P53" s="23">
         <v>-145.87</v>
       </c>
       <c r="Q53" s="18"/>
@@ -13494,16 +13543,16 @@
       <c r="S67" s="17">
         <v>141.12</v>
       </c>
-      <c r="T67" s="24">
+      <c r="T67" s="26">
         <v>-531.7</v>
       </c>
-      <c r="U67" s="24">
+      <c r="U67" s="26">
         <v>-454.53</v>
       </c>
-      <c r="V67" s="24">
+      <c r="V67" s="26">
         <v>-441.13</v>
       </c>
-      <c r="W67" s="24">
+      <c r="W67" s="26">
         <v>-366.45</v>
       </c>
     </row>
@@ -15055,35 +15104,35 @@
       <c r="A98" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="B98" s="22">
+      <c r="B98" s="23">
         <v>-109.15</v>
       </c>
-      <c r="C98" s="22">
+      <c r="C98" s="23">
         <v>-129.4</v>
       </c>
-      <c r="D98" s="22">
+      <c r="D98" s="23">
         <v>-138.05</v>
       </c>
-      <c r="E98" s="22">
+      <c r="E98" s="23">
         <v>-218.59</v>
       </c>
-      <c r="F98" s="22">
+      <c r="F98" s="23">
         <v>-185.82</v>
       </c>
-      <c r="G98" s="22">
+      <c r="G98" s="23">
         <v>-206.97</v>
       </c>
-      <c r="H98" s="22">
+      <c r="H98" s="23">
         <v>-130.45</v>
       </c>
-      <c r="I98" s="22">
+      <c r="I98" s="23">
         <v>-322.42</v>
       </c>
       <c r="J98" s="18"/>
-      <c r="K98" s="22">
+      <c r="K98" s="23">
         <v>-277.8</v>
       </c>
-      <c r="L98" s="22">
+      <c r="L98" s="23">
         <v>-314.01</v>
       </c>
       <c r="M98" s="18"/>
@@ -15180,21 +15229,21 @@
       <c r="G101" s="18"/>
       <c r="H101" s="18"/>
       <c r="I101" s="18"/>
-      <c r="J101" s="22">
+      <c r="J101" s="23">
         <v>-290.35</v>
       </c>
       <c r="K101" s="18"/>
       <c r="L101" s="18"/>
-      <c r="M101" s="22">
+      <c r="M101" s="23">
         <v>-250.42</v>
       </c>
-      <c r="N101" s="22">
+      <c r="N101" s="23">
         <v>-128.3</v>
       </c>
       <c r="O101" s="20">
         <v>-86.35</v>
       </c>
-      <c r="P101" s="22">
+      <c r="P101" s="23">
         <v>-130.37</v>
       </c>
       <c r="Q101" s="20">
@@ -15235,10 +15284,10 @@
       <c r="O102" s="18"/>
       <c r="P102" s="18"/>
       <c r="Q102" s="18"/>
-      <c r="R102" s="22">
+      <c r="R102" s="23">
         <v>-119.95</v>
       </c>
-      <c r="S102" s="22">
+      <c r="S102" s="23">
         <v>-152.09</v>
       </c>
       <c r="T102" s="18"/>
@@ -18002,13 +18051,13 @@
       <c r="A20" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="23">
         <v>-873.55</v>
       </c>
       <c r="C20" s="19">
         <v>63.89</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="23">
         <v>-352.24</v>
       </c>
       <c r="E20" s="15">
@@ -18047,10 +18096,10 @@
       <c r="P20" s="20">
         <v>-9.85</v>
       </c>
-      <c r="Q20" s="22">
+      <c r="Q20" s="23">
         <v>-263.86</v>
       </c>
-      <c r="R20" s="22">
+      <c r="R20" s="23">
         <v>-240.7</v>
       </c>
       <c r="S20" s="19">
@@ -18152,7 +18201,7 @@
       <c r="B23" s="20">
         <v>-64.3</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="23">
         <v>-109.08</v>
       </c>
       <c r="D23" s="18"/>
@@ -18342,7 +18391,7 @@
       <c r="E28" s="20">
         <v>-78.72</v>
       </c>
-      <c r="F28" s="22">
+      <c r="F28" s="23">
         <v>-101.14</v>
       </c>
       <c r="G28" s="20">
@@ -18712,16 +18761,16 @@
       <c r="A36" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="B36" s="22">
+      <c r="B36" s="23">
         <v>-148.99</v>
       </c>
       <c r="C36" s="15">
         <v>350.6</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="23">
         <v>-179.18</v>
       </c>
-      <c r="E36" s="22">
+      <c r="E36" s="23">
         <v>-278.23</v>
       </c>
       <c r="F36" s="20">
@@ -18736,7 +18785,7 @@
       <c r="I36" s="19">
         <v>97.92</v>
       </c>
-      <c r="J36" s="22">
+      <c r="J36" s="23">
         <v>-102.14</v>
       </c>
       <c r="K36" s="20">
@@ -18996,7 +19045,7 @@
       <c r="B41" s="15">
         <v>969.22</v>
       </c>
-      <c r="C41" s="22">
+      <c r="C41" s="23">
         <v>-243.08</v>
       </c>
       <c r="D41" s="18"/>
@@ -19059,7 +19108,7 @@
       <c r="C43" s="17">
         <v>225.94</v>
       </c>
-      <c r="D43" s="24">
+      <c r="D43" s="26">
         <v>-320.07</v>
       </c>
       <c r="E43" s="17">
@@ -19089,28 +19138,28 @@
       <c r="M43" s="17">
         <v>100.65</v>
       </c>
-      <c r="N43" s="25">
+      <c r="N43" s="27">
         <v>60.99</v>
       </c>
-      <c r="O43" s="25">
+      <c r="O43" s="27">
         <v>44.65</v>
       </c>
-      <c r="P43" s="25">
+      <c r="P43" s="27">
         <v>44.93</v>
       </c>
-      <c r="Q43" s="25">
+      <c r="Q43" s="27">
         <v>49.93</v>
       </c>
-      <c r="R43" s="23">
+      <c r="R43" s="25">
         <v>-48.93</v>
       </c>
-      <c r="S43" s="25">
+      <c r="S43" s="27">
         <v>67.2</v>
       </c>
       <c r="T43" s="17">
         <v>286.61</v>
       </c>
-      <c r="U43" s="25">
+      <c r="U43" s="27">
         <v>64.64</v>
       </c>
       <c r="V43" s="17">
@@ -19136,16 +19185,16 @@
       <c r="E44" s="18">
         <v>0.0</v>
       </c>
-      <c r="F44" s="22">
+      <c r="F44" s="23">
         <v>-325.27</v>
       </c>
-      <c r="G44" s="22">
+      <c r="G44" s="23">
         <v>-103.6</v>
       </c>
-      <c r="H44" s="22">
+      <c r="H44" s="23">
         <v>-127.92</v>
       </c>
-      <c r="I44" s="22">
+      <c r="I44" s="23">
         <v>-947.02</v>
       </c>
       <c r="J44" s="20">
@@ -19176,7 +19225,7 @@
       <c r="U44" s="20">
         <v>-99.48</v>
       </c>
-      <c r="V44" s="22">
+      <c r="V44" s="23">
         <v>-152.43</v>
       </c>
       <c r="W44" s="18">
@@ -19187,34 +19236,34 @@
       <c r="A45" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="B45" s="22">
+      <c r="B45" s="23">
         <v>-199.18</v>
       </c>
-      <c r="C45" s="22">
+      <c r="C45" s="23">
         <v>-193.22</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="23">
         <v>-252.69</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="23">
         <v>-361.02</v>
       </c>
-      <c r="F45" s="22">
+      <c r="F45" s="23">
         <v>-269.24</v>
       </c>
-      <c r="G45" s="22">
+      <c r="G45" s="23">
         <v>-192.81</v>
       </c>
-      <c r="H45" s="22">
+      <c r="H45" s="23">
         <v>-166.17</v>
       </c>
-      <c r="I45" s="22">
+      <c r="I45" s="23">
         <v>-177.81</v>
       </c>
-      <c r="J45" s="22">
+      <c r="J45" s="23">
         <v>-137.92</v>
       </c>
-      <c r="K45" s="22">
+      <c r="K45" s="23">
         <v>-103.98</v>
       </c>
       <c r="L45" s="20">
@@ -19235,22 +19284,22 @@
       <c r="Q45" s="20">
         <v>-37.82</v>
       </c>
-      <c r="R45" s="22">
+      <c r="R45" s="23">
         <v>-122.66</v>
       </c>
-      <c r="S45" s="22">
+      <c r="S45" s="23">
         <v>-483.87</v>
       </c>
-      <c r="T45" s="22">
+      <c r="T45" s="23">
         <v>-282.9</v>
       </c>
-      <c r="U45" s="22">
+      <c r="U45" s="23">
         <v>-168.35</v>
       </c>
-      <c r="V45" s="22">
+      <c r="V45" s="23">
         <v>-131.31</v>
       </c>
-      <c r="W45" s="22">
+      <c r="W45" s="23">
         <v>-128.99</v>
       </c>
     </row>
@@ -19338,7 +19387,7 @@
       <c r="H47" s="18">
         <v>0.0</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47" s="23">
         <v>-134.0</v>
       </c>
       <c r="J47" s="18"/>
@@ -19490,70 +19539,70 @@
       <c r="A52" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="B52" s="24">
+      <c r="B52" s="26">
         <v>-207.02</v>
       </c>
       <c r="C52" s="17">
         <v>115.31</v>
       </c>
-      <c r="D52" s="24">
+      <c r="D52" s="26">
         <v>-209.81</v>
       </c>
-      <c r="E52" s="24">
+      <c r="E52" s="26">
         <v>-346.09</v>
       </c>
-      <c r="F52" s="24">
+      <c r="F52" s="26">
         <v>-583.58</v>
       </c>
-      <c r="G52" s="24">
+      <c r="G52" s="26">
         <v>-296.41</v>
       </c>
-      <c r="H52" s="24">
+      <c r="H52" s="26">
         <v>-138.47</v>
       </c>
-      <c r="I52" s="24">
+      <c r="I52" s="26">
         <v>-1253.67</v>
       </c>
-      <c r="J52" s="24">
+      <c r="J52" s="26">
         <v>-180.9</v>
       </c>
-      <c r="K52" s="23">
+      <c r="K52" s="25">
         <v>-93.56</v>
       </c>
-      <c r="L52" s="23">
+      <c r="L52" s="25">
         <v>-64.63</v>
       </c>
-      <c r="M52" s="23">
+      <c r="M52" s="25">
         <v>-33.02</v>
       </c>
-      <c r="N52" s="23">
+      <c r="N52" s="25">
         <v>-31.55</v>
       </c>
       <c r="O52" s="17">
         <v>104.52</v>
       </c>
-      <c r="P52" s="23">
+      <c r="P52" s="25">
         <v>-33.67</v>
       </c>
-      <c r="Q52" s="23">
+      <c r="Q52" s="25">
         <v>-34.23</v>
       </c>
-      <c r="R52" s="24">
+      <c r="R52" s="26">
         <v>-139.94</v>
       </c>
-      <c r="S52" s="24">
+      <c r="S52" s="26">
         <v>-526.95</v>
       </c>
-      <c r="T52" s="24">
+      <c r="T52" s="26">
         <v>-279.12</v>
       </c>
-      <c r="U52" s="24">
+      <c r="U52" s="26">
         <v>-265.86</v>
       </c>
-      <c r="V52" s="24">
+      <c r="V52" s="26">
         <v>-265.34</v>
       </c>
-      <c r="W52" s="23">
+      <c r="W52" s="25">
         <v>-49.94</v>
       </c>
     </row>
@@ -19819,10 +19868,10 @@
       <c r="H60" s="18"/>
       <c r="I60" s="18"/>
       <c r="J60" s="18"/>
-      <c r="K60" s="22">
+      <c r="K60" s="23">
         <v>-123.98</v>
       </c>
-      <c r="L60" s="22">
+      <c r="L60" s="23">
         <v>-133.1</v>
       </c>
       <c r="M60" s="20">
@@ -19831,10 +19880,10 @@
       <c r="N60" s="18">
         <v>0.0</v>
       </c>
-      <c r="O60" s="22">
+      <c r="O60" s="23">
         <v>-101.53</v>
       </c>
-      <c r="P60" s="22">
+      <c r="P60" s="23">
         <v>-277.32</v>
       </c>
       <c r="Q60" s="20">
@@ -19858,10 +19907,10 @@
       <c r="D61" s="20">
         <v>-3.06</v>
       </c>
-      <c r="E61" s="22">
+      <c r="E61" s="23">
         <v>-229.37</v>
       </c>
-      <c r="F61" s="22">
+      <c r="F61" s="23">
         <v>-129.84</v>
       </c>
       <c r="G61" s="20">
@@ -19892,7 +19941,7 @@
       <c r="R61" s="19">
         <v>0.99</v>
       </c>
-      <c r="S61" s="22">
+      <c r="S61" s="23">
         <v>-110.32</v>
       </c>
       <c r="T61" s="20">
@@ -19947,7 +19996,7 @@
       <c r="E63" s="18"/>
       <c r="F63" s="18"/>
       <c r="G63" s="18"/>
-      <c r="H63" s="22">
+      <c r="H63" s="23">
         <v>-125.29</v>
       </c>
       <c r="I63" s="18"/>
@@ -19959,7 +20008,7 @@
       <c r="O63" s="18"/>
       <c r="P63" s="18"/>
       <c r="Q63" s="18"/>
-      <c r="R63" s="22">
+      <c r="R63" s="23">
         <v>-314.99</v>
       </c>
       <c r="S63" s="15">
@@ -19971,7 +20020,7 @@
       <c r="U63" s="20">
         <v>-0.66</v>
       </c>
-      <c r="V63" s="22">
+      <c r="V63" s="23">
         <v>-135.04</v>
       </c>
       <c r="W63" s="20">
@@ -20073,7 +20122,7 @@
       <c r="R66" s="18">
         <v>0.0</v>
       </c>
-      <c r="S66" s="22">
+      <c r="S66" s="23">
         <v>-429.14</v>
       </c>
       <c r="T66" s="19">
@@ -20128,13 +20177,13 @@
       <c r="A68" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="B68" s="22">
+      <c r="B68" s="23">
         <v>-321.51</v>
       </c>
       <c r="C68" s="15">
         <v>218.15</v>
       </c>
-      <c r="D68" s="22">
+      <c r="D68" s="23">
         <v>-122.52</v>
       </c>
       <c r="E68" s="15">
@@ -20221,7 +20270,7 @@
       <c r="A71" s="16" t="s">
         <v>351</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B71" s="26">
         <v>-368.55</v>
       </c>
       <c r="C71" s="17">
@@ -20230,43 +20279,43 @@
       <c r="D71" s="17">
         <v>200.62</v>
       </c>
-      <c r="E71" s="24">
+      <c r="E71" s="26">
         <v>-108.58</v>
       </c>
-      <c r="F71" s="23">
+      <c r="F71" s="25">
         <v>-34.17</v>
       </c>
-      <c r="G71" s="25">
+      <c r="G71" s="27">
         <v>8.63</v>
       </c>
-      <c r="H71" s="24">
+      <c r="H71" s="26">
         <v>-172.76</v>
       </c>
       <c r="I71" s="17">
         <v>874.86</v>
       </c>
-      <c r="J71" s="25">
+      <c r="J71" s="27">
         <v>82.78</v>
       </c>
-      <c r="K71" s="24">
+      <c r="K71" s="26">
         <v>-130.92</v>
       </c>
-      <c r="L71" s="23">
+      <c r="L71" s="25">
         <v>-84.88</v>
       </c>
-      <c r="M71" s="23">
+      <c r="M71" s="25">
         <v>-14.52</v>
       </c>
-      <c r="N71" s="25">
+      <c r="N71" s="27">
         <v>26.62</v>
       </c>
-      <c r="O71" s="24">
+      <c r="O71" s="26">
         <v>-101.53</v>
       </c>
-      <c r="P71" s="25">
+      <c r="P71" s="27">
         <v>17.4</v>
       </c>
-      <c r="Q71" s="23">
+      <c r="Q71" s="25">
         <v>-10.54</v>
       </c>
       <c r="R71" s="17">
@@ -20275,16 +20324,16 @@
       <c r="S71" s="17">
         <v>456.64</v>
       </c>
-      <c r="T71" s="23">
+      <c r="T71" s="25">
         <v>-0.49</v>
       </c>
       <c r="U71" s="17">
         <v>115.0</v>
       </c>
-      <c r="V71" s="23">
+      <c r="V71" s="25">
         <v>-68.01</v>
       </c>
-      <c r="W71" s="23">
+      <c r="W71" s="25">
         <v>-33.98</v>
       </c>
     </row>
@@ -20345,25 +20394,25 @@
       <c r="I73" s="21">
         <v>0.0</v>
       </c>
-      <c r="J73" s="23">
+      <c r="J73" s="25">
         <v>-0.16</v>
       </c>
-      <c r="K73" s="23">
+      <c r="K73" s="25">
         <v>-5.73</v>
       </c>
-      <c r="L73" s="23">
+      <c r="L73" s="25">
         <v>-14.52</v>
       </c>
-      <c r="M73" s="23">
+      <c r="M73" s="25">
         <v>-16.04</v>
       </c>
-      <c r="N73" s="23">
+      <c r="N73" s="25">
         <v>-30.14</v>
       </c>
-      <c r="O73" s="23">
+      <c r="O73" s="25">
         <v>-55.82</v>
       </c>
-      <c r="P73" s="23">
+      <c r="P73" s="25">
         <v>-18.21</v>
       </c>
       <c r="Q73" s="21"/>
@@ -20618,7 +20667,7 @@
       <c r="A78" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="B78" s="22">
+      <c r="B78" s="23">
         <v>-464.22</v>
       </c>
       <c r="C78" s="15">
@@ -20686,19 +20735,19 @@
       <c r="A80" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B80" s="26">
         <v>-464.22</v>
       </c>
       <c r="C80" s="17">
         <v>503.3</v>
       </c>
-      <c r="D80" s="24">
+      <c r="D80" s="26">
         <v>-335.39</v>
       </c>
-      <c r="E80" s="23">
+      <c r="E80" s="25">
         <v>-32.57</v>
       </c>
-      <c r="F80" s="25">
+      <c r="F80" s="27">
         <v>24.6</v>
       </c>
       <c r="G80" s="17">
@@ -20710,43 +20759,43 @@
       <c r="I80" s="17">
         <v>154.62</v>
       </c>
-      <c r="J80" s="25">
+      <c r="J80" s="27">
         <v>6.02</v>
       </c>
-      <c r="K80" s="23">
+      <c r="K80" s="25">
         <v>-54.01</v>
       </c>
-      <c r="L80" s="23">
+      <c r="L80" s="25">
         <v>-24.73</v>
       </c>
-      <c r="M80" s="25">
+      <c r="M80" s="27">
         <v>35.97</v>
       </c>
-      <c r="N80" s="25">
+      <c r="N80" s="27">
         <v>25.77</v>
       </c>
-      <c r="O80" s="23">
+      <c r="O80" s="25">
         <v>-7.01</v>
       </c>
-      <c r="P80" s="25">
+      <c r="P80" s="27">
         <v>9.83</v>
       </c>
-      <c r="Q80" s="23">
+      <c r="Q80" s="25">
         <v>-4.91</v>
       </c>
-      <c r="R80" s="25">
+      <c r="R80" s="27">
         <v>11.59</v>
       </c>
-      <c r="S80" s="23">
+      <c r="S80" s="25">
         <v>-4.93</v>
       </c>
-      <c r="T80" s="25">
+      <c r="T80" s="27">
         <v>6.96</v>
       </c>
-      <c r="U80" s="23">
+      <c r="U80" s="25">
         <v>-86.08</v>
       </c>
-      <c r="V80" s="24">
+      <c r="V80" s="26">
         <v>-111.06</v>
       </c>
       <c r="W80" s="17">
@@ -20763,7 +20812,7 @@
       <c r="C81" s="15">
         <v>341.25</v>
       </c>
-      <c r="D81" s="22">
+      <c r="D81" s="23">
         <v>-529.88</v>
       </c>
       <c r="E81" s="19">
@@ -22515,3566 +22564,3566 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="29" t="s">
         <v>378</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="28"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="28"/>
-      <c r="AB20" s="28"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="28"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="31" t="s">
         <v>378</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="32">
         <v>3826.84</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="32">
         <v>3258.04</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="32">
         <v>3658.67</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="32">
         <v>3361.3</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="32">
         <v>6188.69</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="32">
         <v>3766.04</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="32">
         <v>3542.36</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="32">
         <v>2963.41</v>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="32">
         <v>2677.04</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="32">
         <v>1468.78</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="32">
         <v>1773.2</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="32">
         <v>1048.49</v>
       </c>
-      <c r="N21" s="30">
+      <c r="N21" s="32">
         <v>1117.44</v>
       </c>
-      <c r="O21" s="30">
+      <c r="O21" s="32">
         <v>781.31</v>
       </c>
-      <c r="P21" s="30">
+      <c r="P21" s="32">
         <v>1086.97</v>
       </c>
-      <c r="Q21" s="30">
+      <c r="Q21" s="32">
         <v>1184.74</v>
       </c>
-      <c r="R21" s="30">
+      <c r="R21" s="32">
         <v>691.25</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="32">
         <v>323.67</v>
       </c>
-      <c r="T21" s="30">
+      <c r="T21" s="32">
         <v>1738.33</v>
       </c>
-      <c r="U21" s="30">
+      <c r="U21" s="32">
         <v>2257.88</v>
       </c>
-      <c r="V21" s="30">
+      <c r="V21" s="32">
         <v>1467.4</v>
       </c>
-      <c r="W21" s="30">
+      <c r="W21" s="32">
         <v>1108.48</v>
       </c>
-      <c r="X21" s="30">
+      <c r="X21" s="32">
         <v>1343.85</v>
       </c>
-      <c r="Y21" s="30">
+      <c r="Y21" s="32">
         <v>764.97</v>
       </c>
-      <c r="Z21" s="30">
+      <c r="Z21" s="32">
         <v>743.6</v>
       </c>
-      <c r="AA21" s="30">
+      <c r="AA21" s="32">
         <v>1262.41</v>
       </c>
-      <c r="AB21" s="30">
+      <c r="AB21" s="32">
         <v>1164.89</v>
       </c>
-      <c r="AC21" s="30">
+      <c r="AC21" s="32">
         <v>915.47</v>
       </c>
-      <c r="AD21" s="30">
+      <c r="AD21" s="32">
         <v>911.45</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="31" t="s">
         <v>379</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="32">
         <v>4398.17</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="32">
         <v>4468.27</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="32">
         <v>4435.96</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="32">
         <v>4111.19</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="32">
         <v>3828.45</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="32">
         <v>3047.27</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="32">
         <v>2510.22</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="32">
         <v>2043.46</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="32">
         <v>1710.84</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="32">
         <v>1280.56</v>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="32">
         <v>1306.92</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="32">
         <v>1173.94</v>
       </c>
-      <c r="N22" s="30">
+      <c r="N22" s="32">
         <v>1026.58</v>
       </c>
-      <c r="O22" s="30">
+      <c r="O22" s="32">
         <v>755.98</v>
       </c>
-      <c r="P22" s="30">
+      <c r="P22" s="32">
         <v>974.07</v>
       </c>
-      <c r="Q22" s="30">
+      <c r="Q22" s="32">
         <v>1187.6</v>
       </c>
-      <c r="R22" s="30">
+      <c r="R22" s="32">
         <v>1319.54</v>
       </c>
-      <c r="S22" s="30">
+      <c r="S22" s="32">
         <v>1643.47</v>
       </c>
-      <c r="T22" s="30">
+      <c r="T22" s="32">
         <v>1541.24</v>
       </c>
-      <c r="U22" s="30">
+      <c r="U22" s="32">
         <v>1410.36</v>
       </c>
-      <c r="V22" s="30">
+      <c r="V22" s="32">
         <v>1078.88</v>
       </c>
-      <c r="W22" s="30">
+      <c r="W22" s="32">
         <v>1065.41</v>
       </c>
-      <c r="X22" s="30">
+      <c r="X22" s="32">
         <v>1099.74</v>
       </c>
-      <c r="Y22" s="30">
+      <c r="Y22" s="32">
         <v>872.99</v>
       </c>
-      <c r="Z22" s="30">
+      <c r="Z22" s="32">
         <v>969.17</v>
       </c>
-      <c r="AA22" s="31"/>
-      <c r="AB22" s="31"/>
-      <c r="AC22" s="31"/>
-      <c r="AD22" s="31"/>
+      <c r="AA22" s="33"/>
+      <c r="AB22" s="33"/>
+      <c r="AC22" s="33"/>
+      <c r="AD22" s="33"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="29" t="s">
         <v>380</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="28"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="28"/>
-      <c r="AA23" s="28"/>
-      <c r="AB23" s="28"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="28"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="31" t="s">
         <v>380</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="32">
         <v>2430.03</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="32">
         <v>2049.23</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="32">
         <v>2198.62</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="32">
         <v>2532.08</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="32">
         <v>5569.31</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="32">
         <v>3342.24</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="32">
         <v>2957.31</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="32">
         <v>2266.81</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="32">
         <v>2069.64</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="32">
         <v>996.08</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="32">
         <v>1200.63</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="32">
         <v>420.41</v>
       </c>
-      <c r="N24" s="30">
+      <c r="N24" s="32">
         <v>523.14</v>
       </c>
-      <c r="O24" s="30">
+      <c r="O24" s="32">
         <v>251.08</v>
       </c>
-      <c r="P24" s="30">
+      <c r="P24" s="32">
         <v>432.86</v>
       </c>
-      <c r="Q24" s="30">
+      <c r="Q24" s="32">
         <v>543.41</v>
       </c>
-      <c r="R24" s="30">
+      <c r="R24" s="32">
         <v>710.87</v>
       </c>
-      <c r="S24" s="30">
+      <c r="S24" s="32">
         <v>332.7</v>
       </c>
-      <c r="T24" s="30">
+      <c r="T24" s="32">
         <v>1333.18</v>
       </c>
-      <c r="U24" s="30">
+      <c r="U24" s="32">
         <v>1868.21</v>
       </c>
-      <c r="V24" s="30">
+      <c r="V24" s="32">
         <v>1334.93</v>
       </c>
-      <c r="W24" s="30">
+      <c r="W24" s="32">
         <v>1198.07</v>
       </c>
-      <c r="X24" s="30">
+      <c r="X24" s="32">
         <v>1316.4</v>
       </c>
-      <c r="Y24" s="30">
+      <c r="Y24" s="32">
         <v>604.05</v>
       </c>
-      <c r="Z24" s="30">
+      <c r="Z24" s="32">
         <v>630.51</v>
       </c>
-      <c r="AA24" s="30">
+      <c r="AA24" s="32">
         <v>997.29</v>
       </c>
-      <c r="AB24" s="30">
+      <c r="AB24" s="32">
         <v>658.53</v>
       </c>
-      <c r="AC24" s="30">
+      <c r="AC24" s="32">
         <v>440.62</v>
       </c>
-      <c r="AD24" s="30">
+      <c r="AD24" s="32">
         <v>450.78</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="31" t="s">
         <v>381</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="32">
         <v>3237.06</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="32">
         <v>3493.64</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="32">
         <v>3605.85</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="32">
         <v>3457.4</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="32">
         <v>3238.91</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="32">
         <v>2451.48</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="32">
         <v>1914.67</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="32">
         <v>1424.3</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="32">
         <v>1091.81</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="32">
         <v>688.94</v>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="32">
         <v>622.24</v>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="32">
         <v>486.87</v>
       </c>
-      <c r="N25" s="30">
+      <c r="N25" s="32">
         <v>513.49</v>
       </c>
-      <c r="O25" s="30">
+      <c r="O25" s="32">
         <v>410.21</v>
       </c>
-      <c r="P25" s="30">
+      <c r="P25" s="32">
         <v>641.38</v>
       </c>
-      <c r="Q25" s="30">
+      <c r="Q25" s="32">
         <v>911.06</v>
       </c>
-      <c r="R25" s="30">
+      <c r="R25" s="32">
         <v>1133.79</v>
       </c>
-      <c r="S25" s="30">
+      <c r="S25" s="32">
         <v>1442.59</v>
       </c>
-      <c r="T25" s="30">
+      <c r="T25" s="32">
         <v>1370.77</v>
       </c>
-      <c r="U25" s="30">
+      <c r="U25" s="32">
         <v>1281.35</v>
       </c>
-      <c r="V25" s="30">
+      <c r="V25" s="32">
         <v>1006.72</v>
       </c>
-      <c r="W25" s="30">
+      <c r="W25" s="32">
         <v>965.1</v>
       </c>
-      <c r="X25" s="30">
+      <c r="X25" s="32">
         <v>874.35</v>
       </c>
-      <c r="Y25" s="30">
+      <c r="Y25" s="32">
         <v>603.81</v>
       </c>
-      <c r="Z25" s="30">
+      <c r="Z25" s="32">
         <v>618.15</v>
       </c>
-      <c r="AA25" s="31"/>
-      <c r="AB25" s="31"/>
-      <c r="AC25" s="31"/>
-      <c r="AD25" s="31"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="33"/>
+      <c r="AC25" s="33"/>
+      <c r="AD25" s="33"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="29" t="s">
         <v>382</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
-      <c r="V26" s="28"/>
-      <c r="W26" s="28"/>
-      <c r="X26" s="28"/>
-      <c r="Y26" s="28"/>
-      <c r="Z26" s="28"/>
-      <c r="AA26" s="28"/>
-      <c r="AB26" s="28"/>
-      <c r="AC26" s="28"/>
-      <c r="AD26" s="28"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="31" t="s">
         <v>383</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="32">
         <v>147.27</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="32">
         <v>124.2</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="32">
         <v>133.25</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="32">
         <v>144.69</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="32">
         <v>309.69</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="32">
         <v>185.85</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="32">
         <v>164.45</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="32">
         <v>126.05</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="32">
         <v>160.62</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="34">
         <v>77.3</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="34">
         <v>93.18</v>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="34">
         <v>35.89</v>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="34">
         <v>44.66</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="34">
         <v>21.43</v>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="34">
         <v>36.95</v>
       </c>
-      <c r="Q27" s="32">
+      <c r="Q27" s="34">
         <v>46.39</v>
       </c>
-      <c r="R27" s="32">
+      <c r="R27" s="34">
         <v>60.68</v>
       </c>
-      <c r="S27" s="30">
+      <c r="S27" s="32">
         <v>118.36</v>
       </c>
-      <c r="T27" s="30">
+      <c r="T27" s="32">
         <v>438.2</v>
       </c>
-      <c r="U27" s="30">
+      <c r="U27" s="32">
         <v>614.06</v>
       </c>
-      <c r="V27" s="30">
+      <c r="V27" s="32">
         <v>438.78</v>
       </c>
-      <c r="W27" s="30">
+      <c r="W27" s="32">
         <v>393.79</v>
       </c>
-      <c r="X27" s="30">
+      <c r="X27" s="32">
         <v>432.68</v>
       </c>
-      <c r="Y27" s="30">
+      <c r="Y27" s="32">
         <v>198.55</v>
       </c>
-      <c r="Z27" s="30">
+      <c r="Z27" s="32">
         <v>207.24</v>
       </c>
-      <c r="AA27" s="30">
+      <c r="AA27" s="32">
         <v>301.56</v>
       </c>
-      <c r="AB27" s="30">
+      <c r="AB27" s="32">
         <v>186.92</v>
       </c>
-      <c r="AC27" s="30">
+      <c r="AC27" s="32">
         <v>126.42</v>
       </c>
-      <c r="AD27" s="30">
+      <c r="AD27" s="32">
         <v>130.19</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="31" t="s">
         <v>384</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="32">
         <v>187.68</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="32">
         <v>199.5</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="32">
         <v>203.54</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="32">
         <v>193.03</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="32">
         <v>189.38</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="32">
         <v>151.06</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="32">
         <v>125.68</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="32">
         <v>101.28</v>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="34">
         <v>86.4</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="34">
         <v>55.5</v>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="34">
         <v>51.25</v>
       </c>
-      <c r="M28" s="32">
+      <c r="M28" s="34">
         <v>41.56</v>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="34">
         <v>43.83</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="34">
         <v>48.59</v>
       </c>
-      <c r="P28" s="30">
+      <c r="P28" s="32">
         <v>132.56</v>
       </c>
-      <c r="Q28" s="30">
+      <c r="Q28" s="32">
         <v>242.02</v>
       </c>
-      <c r="R28" s="30">
+      <c r="R28" s="32">
         <v>339.61</v>
       </c>
-      <c r="S28" s="30">
+      <c r="S28" s="32">
         <v>475.96</v>
       </c>
-      <c r="T28" s="30">
+      <c r="T28" s="32">
         <v>450.56</v>
       </c>
-      <c r="U28" s="30">
+      <c r="U28" s="32">
         <v>421.16</v>
       </c>
-      <c r="V28" s="30">
+      <c r="V28" s="32">
         <v>330.9</v>
       </c>
-      <c r="W28" s="30">
+      <c r="W28" s="32">
         <v>311.97</v>
       </c>
-      <c r="X28" s="30">
+      <c r="X28" s="32">
         <v>275.92</v>
       </c>
-      <c r="Y28" s="30">
+      <c r="Y28" s="32">
         <v>185.47</v>
       </c>
-      <c r="Z28" s="30">
+      <c r="Z28" s="32">
         <v>185.38</v>
       </c>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31"/>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
+      <c r="AA28" s="33"/>
+      <c r="AB28" s="33"/>
+      <c r="AC28" s="33"/>
+      <c r="AD28" s="33"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="29" t="s">
         <v>385</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="28"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="28"/>
-      <c r="AB29" s="28"/>
-      <c r="AC29" s="28"/>
-      <c r="AD29" s="28"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="31" t="s">
         <v>386</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="35">
         <v>-3.68</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="36">
         <v>1.63</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="35">
         <v>-25.8</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="36">
         <v>2.76</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="36">
         <v>6.31</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="36">
         <v>12.32</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="36">
         <v>10.88</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="36">
         <v>9.33</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="35">
         <v>-1.71</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="36">
         <v>7.37</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="36">
         <v>5.62</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="36">
         <v>13.65</v>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="36">
         <v>4.78</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="36">
         <v>7.76</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="36">
         <v>1.46</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="36">
         <v>0.27</v>
       </c>
-      <c r="R30" s="33">
+      <c r="R30" s="35">
         <v>-63.92</v>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="35">
         <v>-115.28</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="36">
         <v>0.22</v>
       </c>
-      <c r="U30" s="33">
+      <c r="U30" s="35">
         <v>-4.55</v>
       </c>
-      <c r="V30" s="34">
+      <c r="V30" s="36">
         <v>5.43</v>
       </c>
-      <c r="W30" s="34">
+      <c r="W30" s="36">
         <v>3.73</v>
       </c>
-      <c r="X30" s="34">
+      <c r="X30" s="36">
         <v>11.98</v>
       </c>
-      <c r="Y30" s="34">
+      <c r="Y30" s="36">
         <v>7.87</v>
       </c>
-      <c r="Z30" s="33">
+      <c r="Z30" s="35">
         <v>-5.42</v>
       </c>
-      <c r="AA30" s="33">
+      <c r="AA30" s="35">
         <v>-5.82</v>
       </c>
-      <c r="AB30" s="34">
+      <c r="AB30" s="36">
         <v>12.51</v>
       </c>
-      <c r="AC30" s="34">
+      <c r="AC30" s="36">
         <v>20.09</v>
       </c>
-      <c r="AD30" s="34">
+      <c r="AD30" s="36">
         <v>0.07</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="31" t="s">
         <v>387</v>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="35">
         <v>-1.3</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="36">
         <v>1.9</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="36">
         <v>3.58</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="36">
         <v>8.19</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="36">
         <v>7.27</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="36">
         <v>7.7</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="36">
         <v>6.1</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="36">
         <v>5.12</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="36">
         <v>3.86</v>
       </c>
-      <c r="K31" s="34">
+      <c r="K31" s="36">
         <v>7.21</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="36">
         <v>6.14</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="36">
         <v>4.83</v>
       </c>
-      <c r="N31" s="33">
+      <c r="N31" s="35">
         <v>-15.59</v>
       </c>
-      <c r="O31" s="33">
+      <c r="O31" s="35">
         <v>-55.53</v>
       </c>
-      <c r="P31" s="33">
+      <c r="P31" s="35">
         <v>-21.64</v>
       </c>
-      <c r="Q31" s="33">
+      <c r="Q31" s="35">
         <v>-14.13</v>
       </c>
-      <c r="R31" s="33">
+      <c r="R31" s="35">
         <v>-9.29</v>
       </c>
-      <c r="S31" s="33">
+      <c r="S31" s="35">
         <v>-5.12</v>
       </c>
-      <c r="T31" s="34">
+      <c r="T31" s="36">
         <v>2.7</v>
       </c>
-      <c r="U31" s="34">
+      <c r="U31" s="36">
         <v>3.78</v>
       </c>
-      <c r="V31" s="34">
+      <c r="V31" s="36">
         <v>5.63</v>
       </c>
-      <c r="W31" s="34">
+      <c r="W31" s="36">
         <v>3.47</v>
       </c>
-      <c r="X31" s="34">
+      <c r="X31" s="36">
         <v>4.67</v>
       </c>
-      <c r="Y31" s="34">
+      <c r="Y31" s="36">
         <v>3.43</v>
       </c>
-      <c r="Z31" s="34">
+      <c r="Z31" s="36">
         <v>1.92</v>
       </c>
-      <c r="AA31" s="34"/>
-      <c r="AB31" s="34"/>
-      <c r="AC31" s="34"/>
-      <c r="AD31" s="34"/>
+      <c r="AA31" s="36"/>
+      <c r="AB31" s="36"/>
+      <c r="AC31" s="36"/>
+      <c r="AD31" s="36"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="29" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="28"/>
-      <c r="AB32" s="28"/>
-      <c r="AC32" s="28"/>
-      <c r="AD32" s="28"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="31" t="s">
         <v>389</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="36">
         <v>0.0</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="36">
         <v>0.0</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="36">
         <v>0.0</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="36">
         <v>0.0</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="36">
         <v>0.0</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="36">
         <v>0.0</v>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="36">
         <v>0.0</v>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="36">
         <v>0.0</v>
       </c>
-      <c r="J33" s="34">
+      <c r="J33" s="36">
         <v>0.0</v>
       </c>
-      <c r="K33" s="34">
+      <c r="K33" s="36">
         <v>0.0</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="36">
         <v>0.0</v>
       </c>
-      <c r="M33" s="34">
+      <c r="M33" s="36">
         <v>0.0</v>
       </c>
-      <c r="N33" s="34">
+      <c r="N33" s="36">
         <v>0.0</v>
       </c>
-      <c r="O33" s="34">
+      <c r="O33" s="36">
         <v>0.0</v>
       </c>
-      <c r="P33" s="34">
+      <c r="P33" s="36">
         <v>0.0</v>
       </c>
-      <c r="Q33" s="34">
+      <c r="Q33" s="36">
         <v>0.0</v>
       </c>
-      <c r="R33" s="34">
+      <c r="R33" s="36">
         <v>0.0</v>
       </c>
-      <c r="S33" s="34">
+      <c r="S33" s="36">
         <v>7.2</v>
       </c>
-      <c r="T33" s="34">
+      <c r="T33" s="36">
         <v>1.06</v>
       </c>
-      <c r="U33" s="34">
+      <c r="U33" s="36">
         <v>1.37</v>
       </c>
-      <c r="V33" s="34">
+      <c r="V33" s="36">
         <v>1.86</v>
       </c>
-      <c r="W33" s="34">
+      <c r="W33" s="36">
         <v>1.84</v>
       </c>
-      <c r="X33" s="34">
+      <c r="X33" s="36">
         <v>1.42</v>
       </c>
-      <c r="Y33" s="34">
+      <c r="Y33" s="36">
         <v>2.69</v>
       </c>
-      <c r="Z33" s="34">
+      <c r="Z33" s="36">
         <v>2.82</v>
       </c>
-      <c r="AA33" s="34">
+      <c r="AA33" s="36">
         <v>1.67</v>
       </c>
-      <c r="AB33" s="34">
+      <c r="AB33" s="36">
         <v>1.71</v>
       </c>
-      <c r="AC33" s="34">
+      <c r="AC33" s="36">
         <v>2.57</v>
       </c>
-      <c r="AD33" s="34">
+      <c r="AD33" s="36">
         <v>2.06</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="31" t="s">
         <v>390</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="36">
         <v>0.0</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="36">
         <v>0.0</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="36">
         <v>0.0</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E34" s="36">
         <v>0.0</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="36">
         <v>0.0</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="36">
         <v>0.0</v>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="36">
         <v>0.0</v>
       </c>
-      <c r="I34" s="34">
+      <c r="I34" s="36">
         <v>0.0</v>
       </c>
-      <c r="J34" s="34">
+      <c r="J34" s="36">
         <v>0.0</v>
       </c>
-      <c r="K34" s="34">
+      <c r="K34" s="36">
         <v>0.0</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="36">
         <v>0.0</v>
       </c>
-      <c r="M34" s="34">
+      <c r="M34" s="36">
         <v>0.0</v>
       </c>
-      <c r="N34" s="34">
+      <c r="N34" s="36">
         <v>0.0</v>
       </c>
-      <c r="O34" s="34">
+      <c r="O34" s="36">
         <v>2.65</v>
       </c>
-      <c r="P34" s="34">
+      <c r="P34" s="36">
         <v>1.71</v>
       </c>
-      <c r="Q34" s="34">
+      <c r="Q34" s="36">
         <v>1.6</v>
       </c>
-      <c r="R34" s="34">
+      <c r="R34" s="36">
         <v>1.72</v>
       </c>
-      <c r="S34" s="34">
+      <c r="S34" s="36">
         <v>1.79</v>
       </c>
-      <c r="T34" s="34">
+      <c r="T34" s="36">
         <v>1.49</v>
       </c>
-      <c r="U34" s="34">
+      <c r="U34" s="36">
         <v>1.71</v>
       </c>
-      <c r="V34" s="34">
+      <c r="V34" s="36">
         <v>1.97</v>
       </c>
-      <c r="W34" s="34">
+      <c r="W34" s="36">
         <v>1.95</v>
       </c>
-      <c r="X34" s="34">
+      <c r="X34" s="36">
         <v>1.94</v>
       </c>
-      <c r="Y34" s="34">
+      <c r="Y34" s="36">
         <v>2.23</v>
       </c>
-      <c r="Z34" s="34">
+      <c r="Z34" s="36">
         <v>2.1</v>
       </c>
-      <c r="AA34" s="34"/>
-      <c r="AB34" s="34"/>
-      <c r="AC34" s="34"/>
-      <c r="AD34" s="34"/>
+      <c r="AA34" s="36"/>
+      <c r="AB34" s="36"/>
+      <c r="AC34" s="36"/>
+      <c r="AD34" s="36"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="31" t="s">
         <v>391</v>
       </c>
-      <c r="B35" s="34">
+      <c r="B35" s="36">
         <v>0.0</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="36">
         <v>0.0</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="36">
         <v>0.0</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="36">
         <v>0.0</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="36">
         <v>0.0</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="36">
         <v>0.0</v>
       </c>
-      <c r="H35" s="34">
+      <c r="H35" s="36">
         <v>0.0</v>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="36">
         <v>0.0</v>
       </c>
-      <c r="J35" s="34">
+      <c r="J35" s="36">
         <v>0.0</v>
       </c>
-      <c r="K35" s="34">
+      <c r="K35" s="36">
         <v>0.0</v>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="36">
         <v>0.0</v>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="36">
         <v>0.0</v>
       </c>
-      <c r="N35" s="34">
+      <c r="N35" s="36">
         <v>0.0</v>
       </c>
-      <c r="O35" s="34">
+      <c r="O35" s="36">
         <v>0.0</v>
       </c>
-      <c r="P35" s="34">
+      <c r="P35" s="36">
         <v>0.0</v>
       </c>
-      <c r="Q35" s="34">
+      <c r="Q35" s="36">
         <v>0.0</v>
       </c>
-      <c r="R35" s="34">
+      <c r="R35" s="36">
         <v>0.0</v>
       </c>
-      <c r="S35" s="34">
+      <c r="S35" s="36">
         <v>10.0</v>
       </c>
-      <c r="T35" s="34">
+      <c r="T35" s="36">
         <v>1.47</v>
       </c>
-      <c r="U35" s="34">
+      <c r="U35" s="36">
         <v>1.9</v>
       </c>
-      <c r="V35" s="34">
+      <c r="V35" s="36">
         <v>2.58</v>
       </c>
-      <c r="W35" s="34">
+      <c r="W35" s="36">
         <v>2.55</v>
       </c>
-      <c r="X35" s="34">
+      <c r="X35" s="36">
         <v>1.97</v>
       </c>
-      <c r="Y35" s="34">
+      <c r="Y35" s="36">
         <v>3.73</v>
       </c>
-      <c r="Z35" s="34">
+      <c r="Z35" s="36">
         <v>3.91</v>
       </c>
-      <c r="AA35" s="34">
+      <c r="AA35" s="36">
         <v>2.22</v>
       </c>
-      <c r="AB35" s="34">
+      <c r="AB35" s="36">
         <v>2.28</v>
       </c>
-      <c r="AC35" s="34">
+      <c r="AC35" s="36">
         <v>3.43</v>
       </c>
-      <c r="AD35" s="34">
+      <c r="AD35" s="36">
         <v>2.75</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="31" t="s">
         <v>392</v>
       </c>
-      <c r="B36" s="34">
+      <c r="B36" s="36">
         <v>0.0</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="36">
         <v>0.0</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="36">
         <v>0.0</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="36">
         <v>0.0</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="36">
         <v>0.0</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="36">
         <v>0.0</v>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="36">
         <v>0.0</v>
       </c>
-      <c r="I36" s="34">
+      <c r="I36" s="36">
         <v>0.0</v>
       </c>
-      <c r="J36" s="34">
+      <c r="J36" s="36">
         <v>0.0</v>
       </c>
-      <c r="K36" s="34">
+      <c r="K36" s="36">
         <v>0.0</v>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="36">
         <v>0.0</v>
       </c>
-      <c r="M36" s="34">
+      <c r="M36" s="36">
         <v>0.0</v>
       </c>
-      <c r="N36" s="34">
+      <c r="N36" s="36">
         <v>0.0</v>
       </c>
-      <c r="O36" s="34">
+      <c r="O36" s="36">
         <v>3.68</v>
       </c>
-      <c r="P36" s="34">
+      <c r="P36" s="36">
         <v>2.37</v>
       </c>
-      <c r="Q36" s="34">
+      <c r="Q36" s="36">
         <v>2.22</v>
       </c>
-      <c r="R36" s="34">
+      <c r="R36" s="36">
         <v>2.38</v>
       </c>
-      <c r="S36" s="34">
+      <c r="S36" s="36">
         <v>2.49</v>
       </c>
-      <c r="T36" s="34">
+      <c r="T36" s="36">
         <v>2.07</v>
       </c>
-      <c r="U36" s="34">
+      <c r="U36" s="36">
         <v>2.38</v>
       </c>
-      <c r="V36" s="34">
+      <c r="V36" s="36">
         <v>2.74</v>
       </c>
-      <c r="W36" s="34">
+      <c r="W36" s="36">
         <v>2.69</v>
       </c>
-      <c r="X36" s="34">
+      <c r="X36" s="36">
         <v>2.67</v>
       </c>
-      <c r="Y36" s="34">
+      <c r="Y36" s="36">
         <v>3.04</v>
       </c>
-      <c r="Z36" s="34">
+      <c r="Z36" s="36">
         <v>2.83</v>
       </c>
-      <c r="AA36" s="34"/>
-      <c r="AB36" s="34"/>
-      <c r="AC36" s="34"/>
-      <c r="AD36" s="34"/>
+      <c r="AA36" s="36"/>
+      <c r="AB36" s="36"/>
+      <c r="AC36" s="36"/>
+      <c r="AD36" s="36"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="29" t="s">
         <v>393</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="28"/>
-      <c r="AC37" s="28"/>
-      <c r="AD37" s="28"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="31" t="s">
         <v>394</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="34">
         <v>1.65</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="34">
         <v>0.82</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="34">
         <v>0.91</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="34">
         <v>0.91</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="34">
         <v>2.35</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="34">
         <v>1.64</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="34">
         <v>1.67</v>
       </c>
-      <c r="I38" s="32">
+      <c r="I38" s="34">
         <v>1.7</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="34">
         <v>4.15</v>
       </c>
-      <c r="K38" s="32">
+      <c r="K38" s="34">
         <v>2.92</v>
       </c>
-      <c r="L38" s="32">
+      <c r="L38" s="34">
         <v>3.65</v>
       </c>
-      <c r="M38" s="32">
+      <c r="M38" s="34">
         <v>2.28</v>
       </c>
-      <c r="N38" s="32">
+      <c r="N38" s="34">
         <v>1.59</v>
       </c>
-      <c r="O38" s="32">
+      <c r="O38" s="34">
         <v>0.61</v>
       </c>
-      <c r="P38" s="32">
+      <c r="P38" s="34">
         <v>0.88</v>
       </c>
-      <c r="Q38" s="32">
+      <c r="Q38" s="34">
         <v>0.77</v>
       </c>
-      <c r="R38" s="32">
+      <c r="R38" s="34">
         <v>0.66</v>
       </c>
-      <c r="S38" s="32">
+      <c r="S38" s="34">
         <v>0.43</v>
       </c>
-      <c r="T38" s="32">
+      <c r="T38" s="34">
         <v>2.16</v>
       </c>
-      <c r="U38" s="32">
+      <c r="U38" s="34">
         <v>3.33</v>
       </c>
-      <c r="V38" s="32">
+      <c r="V38" s="34">
         <v>2.59</v>
       </c>
-      <c r="W38" s="32">
+      <c r="W38" s="34">
         <v>2.5</v>
       </c>
-      <c r="X38" s="32">
+      <c r="X38" s="34">
         <v>3.01</v>
       </c>
-      <c r="Y38" s="32">
+      <c r="Y38" s="34">
         <v>1.76</v>
       </c>
-      <c r="Z38" s="32">
+      <c r="Z38" s="34">
         <v>1.7</v>
       </c>
-      <c r="AA38" s="32">
+      <c r="AA38" s="34">
         <v>3.55</v>
       </c>
-      <c r="AB38" s="32">
+      <c r="AB38" s="34">
         <v>2.81</v>
       </c>
-      <c r="AC38" s="32">
+      <c r="AC38" s="34">
         <v>1.78</v>
       </c>
-      <c r="AD38" s="32">
+      <c r="AD38" s="34">
         <v>1.81</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="31" t="s">
         <v>395</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="34">
         <v>1.29</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="34">
         <v>1.3</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="34">
         <v>1.46</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="34">
         <v>1.62</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="34">
         <v>2.08</v>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="34">
         <v>2.05</v>
       </c>
-      <c r="H39" s="32">
+      <c r="H39" s="34">
         <v>2.37</v>
       </c>
-      <c r="I39" s="32">
+      <c r="I39" s="34">
         <v>2.73</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="34">
         <v>3.0</v>
       </c>
-      <c r="K39" s="32">
+      <c r="K39" s="34">
         <v>1.97</v>
       </c>
-      <c r="L39" s="32">
+      <c r="L39" s="34">
         <v>1.49</v>
       </c>
-      <c r="M39" s="32">
+      <c r="M39" s="34">
         <v>1.0</v>
       </c>
-      <c r="N39" s="32">
+      <c r="N39" s="34">
         <v>0.81</v>
       </c>
-      <c r="O39" s="32">
+      <c r="O39" s="34">
         <v>0.58</v>
       </c>
-      <c r="P39" s="32">
+      <c r="P39" s="34">
         <v>1.1</v>
       </c>
-      <c r="Q39" s="32">
+      <c r="Q39" s="34">
         <v>1.64</v>
       </c>
-      <c r="R39" s="32">
+      <c r="R39" s="34">
         <v>1.89</v>
       </c>
-      <c r="S39" s="32">
+      <c r="S39" s="34">
         <v>2.1</v>
       </c>
-      <c r="T39" s="32">
+      <c r="T39" s="34">
         <v>2.69</v>
       </c>
-      <c r="U39" s="32">
+      <c r="U39" s="34">
         <v>2.69</v>
       </c>
-      <c r="V39" s="32">
+      <c r="V39" s="34">
         <v>2.35</v>
       </c>
-      <c r="W39" s="32">
+      <c r="W39" s="34">
         <v>2.45</v>
       </c>
-      <c r="X39" s="32">
+      <c r="X39" s="34">
         <v>2.48</v>
       </c>
-      <c r="Y39" s="32">
+      <c r="Y39" s="34">
         <v>2.22</v>
       </c>
-      <c r="Z39" s="32">
+      <c r="Z39" s="34">
         <v>2.29</v>
       </c>
-      <c r="AA39" s="31"/>
-      <c r="AB39" s="31"/>
-      <c r="AC39" s="31"/>
-      <c r="AD39" s="31"/>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="33"/>
+      <c r="AC39" s="33"/>
+      <c r="AD39" s="33"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="29" t="s">
         <v>396</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="28"/>
-      <c r="X40" s="28"/>
-      <c r="Y40" s="28"/>
-      <c r="Z40" s="28"/>
-      <c r="AA40" s="28"/>
-      <c r="AB40" s="28"/>
-      <c r="AC40" s="28"/>
-      <c r="AD40" s="28"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+      <c r="AA40" s="30"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="30"/>
+      <c r="AD40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="31" t="s">
         <v>397</v>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="34">
         <v>3.05</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="34">
         <v>1.39</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="34">
         <v>1.56</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="34">
         <v>1.43</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="34">
         <v>3.84</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="34">
         <v>2.44</v>
       </c>
-      <c r="H41" s="32">
+      <c r="H41" s="34">
         <v>2.49</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="34">
         <v>2.9</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="34">
         <v>4.88</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="34">
         <v>3.64</v>
       </c>
-      <c r="L41" s="32">
+      <c r="L41" s="34">
         <v>4.65</v>
       </c>
-      <c r="M41" s="32">
+      <c r="M41" s="34">
         <v>3.59</v>
       </c>
-      <c r="N41" s="32">
+      <c r="N41" s="34">
         <v>2.02</v>
       </c>
-      <c r="O41" s="32">
+      <c r="O41" s="34">
         <v>0.73</v>
       </c>
-      <c r="P41" s="32">
+      <c r="P41" s="34">
         <v>1.1</v>
       </c>
-      <c r="Q41" s="32">
+      <c r="Q41" s="34">
         <v>0.94</v>
       </c>
-      <c r="R41" s="32">
+      <c r="R41" s="34">
         <v>0.66</v>
       </c>
-      <c r="S41" s="32">
+      <c r="S41" s="34">
         <v>0.44</v>
       </c>
-      <c r="T41" s="32">
+      <c r="T41" s="34">
         <v>1.53</v>
       </c>
-      <c r="U41" s="32">
+      <c r="U41" s="34">
         <v>2.39</v>
       </c>
-      <c r="V41" s="32">
+      <c r="V41" s="34">
         <v>1.81</v>
       </c>
-      <c r="W41" s="32">
+      <c r="W41" s="34">
         <v>1.65</v>
       </c>
-      <c r="X41" s="32">
+      <c r="X41" s="34">
         <v>2.0</v>
       </c>
-      <c r="Y41" s="32">
+      <c r="Y41" s="34">
         <v>1.18</v>
       </c>
-      <c r="Z41" s="32">
+      <c r="Z41" s="34">
         <v>1.25</v>
       </c>
-      <c r="AA41" s="32">
+      <c r="AA41" s="34">
         <v>2.65</v>
       </c>
-      <c r="AB41" s="32">
+      <c r="AB41" s="34">
         <v>2.12</v>
       </c>
-      <c r="AC41" s="32">
+      <c r="AC41" s="34">
         <v>1.34</v>
       </c>
-      <c r="AD41" s="32">
+      <c r="AD41" s="34">
         <v>1.36</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="31" t="s">
         <v>398</v>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="34">
         <v>2.15</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="34">
         <v>2.11</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="34">
         <v>2.32</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="34">
         <v>2.55</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="34">
         <v>3.17</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="34">
         <v>2.99</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="34">
         <v>3.39</v>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="34">
         <v>3.86</v>
       </c>
-      <c r="J42" s="32">
+      <c r="J42" s="34">
         <v>3.81</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="34">
         <v>2.5</v>
       </c>
-      <c r="L42" s="32">
+      <c r="L42" s="34">
         <v>1.89</v>
       </c>
-      <c r="M42" s="32">
+      <c r="M42" s="34">
         <v>1.25</v>
       </c>
-      <c r="N42" s="32">
+      <c r="N42" s="34">
         <v>0.93</v>
       </c>
-      <c r="O42" s="32">
+      <c r="O42" s="34">
         <v>0.62</v>
       </c>
-      <c r="P42" s="32">
+      <c r="P42" s="34">
         <v>1.0</v>
       </c>
-      <c r="Q42" s="32">
+      <c r="Q42" s="34">
         <v>1.38</v>
       </c>
-      <c r="R42" s="32">
+      <c r="R42" s="34">
         <v>1.5</v>
       </c>
-      <c r="S42" s="32">
+      <c r="S42" s="34">
         <v>1.59</v>
       </c>
-      <c r="T42" s="32">
+      <c r="T42" s="34">
         <v>1.86</v>
       </c>
-      <c r="U42" s="32">
+      <c r="U42" s="34">
         <v>1.84</v>
       </c>
-      <c r="V42" s="32">
+      <c r="V42" s="34">
         <v>1.61</v>
       </c>
-      <c r="W42" s="32">
+      <c r="W42" s="34">
         <v>1.68</v>
       </c>
-      <c r="X42" s="32">
+      <c r="X42" s="34">
         <v>1.74</v>
       </c>
-      <c r="Y42" s="32">
+      <c r="Y42" s="34">
         <v>1.6</v>
       </c>
-      <c r="Z42" s="32">
+      <c r="Z42" s="34">
         <v>1.71</v>
       </c>
-      <c r="AA42" s="31"/>
-      <c r="AB42" s="31"/>
-      <c r="AC42" s="31"/>
-      <c r="AD42" s="31"/>
+      <c r="AA42" s="33"/>
+      <c r="AB42" s="33"/>
+      <c r="AC42" s="33"/>
+      <c r="AD42" s="33"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="29" t="s">
         <v>399</v>
       </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
-      <c r="U43" s="28"/>
-      <c r="V43" s="28"/>
-      <c r="W43" s="28"/>
-      <c r="X43" s="28"/>
-      <c r="Y43" s="28"/>
-      <c r="Z43" s="28"/>
-      <c r="AA43" s="28"/>
-      <c r="AB43" s="28"/>
-      <c r="AC43" s="28"/>
-      <c r="AD43" s="28"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="30"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="30"/>
+      <c r="AD43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
+      <c r="A44" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="34">
         <v>0.55</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="34">
         <v>0.47</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="34">
         <v>0.54</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="34">
         <v>0.5</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="34">
         <v>1.35</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="34">
         <v>0.89</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="34">
         <v>0.79</v>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="34">
         <v>0.54</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="34">
         <v>0.96</v>
       </c>
-      <c r="K44" s="32">
+      <c r="K44" s="34">
         <v>0.5</v>
       </c>
-      <c r="L44" s="32">
+      <c r="L44" s="34">
         <v>0.56</v>
       </c>
-      <c r="M44" s="32">
+      <c r="M44" s="34">
         <v>0.25</v>
       </c>
-      <c r="N44" s="32">
+      <c r="N44" s="34">
         <v>0.37</v>
       </c>
-      <c r="O44" s="32">
+      <c r="O44" s="34">
         <v>0.21</v>
       </c>
-      <c r="P44" s="32">
+      <c r="P44" s="34">
         <v>0.32</v>
       </c>
-      <c r="Q44" s="32">
+      <c r="Q44" s="34">
         <v>0.44</v>
       </c>
-      <c r="R44" s="32">
+      <c r="R44" s="34">
         <v>0.21</v>
       </c>
-      <c r="S44" s="32">
+      <c r="S44" s="34">
         <v>0.23</v>
       </c>
-      <c r="T44" s="32">
+      <c r="T44" s="34">
         <v>0.85</v>
       </c>
-      <c r="U44" s="32">
+      <c r="U44" s="34">
         <v>1.27</v>
       </c>
-      <c r="V44" s="32">
+      <c r="V44" s="34">
         <v>1.15</v>
       </c>
-      <c r="W44" s="32">
+      <c r="W44" s="34">
         <v>0.98</v>
       </c>
-      <c r="X44" s="32">
+      <c r="X44" s="34">
         <v>0.93</v>
       </c>
-      <c r="Y44" s="32">
+      <c r="Y44" s="34">
         <v>0.56</v>
       </c>
-      <c r="Z44" s="32">
+      <c r="Z44" s="34">
         <v>0.62</v>
       </c>
-      <c r="AA44" s="32">
+      <c r="AA44" s="34">
         <v>0.69</v>
       </c>
-      <c r="AB44" s="32">
+      <c r="AB44" s="34">
         <v>0.36</v>
       </c>
-      <c r="AC44" s="32">
+      <c r="AC44" s="34">
         <v>0.24</v>
       </c>
-      <c r="AD44" s="32">
+      <c r="AD44" s="34">
         <v>0.24</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="29" t="s">
+      <c r="A45" s="31" t="s">
         <v>401</v>
       </c>
-      <c r="B45" s="32">
+      <c r="B45" s="34">
         <v>0.68</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="34">
         <v>0.74</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="34">
         <v>0.8</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="34">
         <v>0.8</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="34">
         <v>0.9</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="34">
         <v>0.73</v>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="34">
         <v>0.67</v>
       </c>
-      <c r="I45" s="32">
+      <c r="I45" s="34">
         <v>0.57</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="34">
         <v>0.54</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="34">
         <v>0.39</v>
       </c>
-      <c r="L45" s="32">
+      <c r="L45" s="34">
         <v>0.35</v>
       </c>
-      <c r="M45" s="32">
+      <c r="M45" s="34">
         <v>0.31</v>
       </c>
-      <c r="N45" s="32">
+      <c r="N45" s="34">
         <v>0.29</v>
       </c>
-      <c r="O45" s="32">
+      <c r="O45" s="34">
         <v>0.25</v>
       </c>
-      <c r="P45" s="32">
+      <c r="P45" s="34">
         <v>0.47</v>
       </c>
-      <c r="Q45" s="32">
+      <c r="Q45" s="34">
         <v>0.69</v>
       </c>
-      <c r="R45" s="32">
+      <c r="R45" s="34">
         <v>0.79</v>
       </c>
-      <c r="S45" s="32">
+      <c r="S45" s="34">
         <v>0.89</v>
       </c>
-      <c r="T45" s="32">
+      <c r="T45" s="34">
         <v>1.03</v>
       </c>
-      <c r="U45" s="32">
+      <c r="U45" s="34">
         <v>0.99</v>
       </c>
-      <c r="V45" s="32">
+      <c r="V45" s="34">
         <v>0.85</v>
       </c>
-      <c r="W45" s="32">
+      <c r="W45" s="34">
         <v>0.76</v>
       </c>
-      <c r="X45" s="32">
+      <c r="X45" s="34">
         <v>0.62</v>
       </c>
-      <c r="Y45" s="32">
+      <c r="Y45" s="34">
         <v>0.48</v>
       </c>
-      <c r="Z45" s="32">
+      <c r="Z45" s="34">
         <v>0.41</v>
       </c>
-      <c r="AA45" s="31"/>
-      <c r="AB45" s="31"/>
-      <c r="AC45" s="31"/>
-      <c r="AD45" s="31"/>
+      <c r="AA45" s="33"/>
+      <c r="AB45" s="33"/>
+      <c r="AC45" s="33"/>
+      <c r="AD45" s="33"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="27" t="s">
+      <c r="A46" s="29" t="s">
         <v>402</v>
       </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
-      <c r="U46" s="28"/>
-      <c r="V46" s="28"/>
-      <c r="W46" s="28"/>
-      <c r="X46" s="28"/>
-      <c r="Y46" s="28"/>
-      <c r="Z46" s="28"/>
-      <c r="AA46" s="28"/>
-      <c r="AB46" s="28"/>
-      <c r="AC46" s="28"/>
-      <c r="AD46" s="28"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
+      <c r="AD46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="31" t="s">
         <v>403</v>
       </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="32">
+      <c r="B47" s="33"/>
+      <c r="C47" s="34">
         <v>61.23</v>
       </c>
-      <c r="D47" s="31"/>
-      <c r="E47" s="32">
+      <c r="D47" s="33"/>
+      <c r="E47" s="34">
         <v>36.25</v>
       </c>
-      <c r="F47" s="32">
+      <c r="F47" s="34">
         <v>15.84</v>
       </c>
-      <c r="G47" s="32">
+      <c r="G47" s="34">
         <v>8.12</v>
       </c>
-      <c r="H47" s="32">
+      <c r="H47" s="34">
         <v>9.19</v>
       </c>
-      <c r="I47" s="32">
+      <c r="I47" s="34">
         <v>10.71</v>
       </c>
-      <c r="J47" s="31"/>
-      <c r="K47" s="32">
+      <c r="J47" s="33"/>
+      <c r="K47" s="34">
         <v>13.57</v>
       </c>
-      <c r="L47" s="32">
+      <c r="L47" s="34">
         <v>17.79</v>
       </c>
-      <c r="M47" s="32">
+      <c r="M47" s="34">
         <v>7.32</v>
       </c>
-      <c r="N47" s="32">
+      <c r="N47" s="34">
         <v>20.92</v>
       </c>
-      <c r="O47" s="32">
+      <c r="O47" s="34">
         <v>12.89</v>
       </c>
-      <c r="P47" s="32">
+      <c r="P47" s="34">
         <v>68.54</v>
       </c>
-      <c r="Q47" s="30">
+      <c r="Q47" s="32">
         <v>366.67</v>
       </c>
-      <c r="R47" s="31"/>
-      <c r="S47" s="31"/>
-      <c r="T47" s="30">
+      <c r="R47" s="33"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="32">
         <v>454.14</v>
       </c>
-      <c r="U47" s="31"/>
-      <c r="V47" s="32">
+      <c r="U47" s="33"/>
+      <c r="V47" s="34">
         <v>18.4</v>
       </c>
-      <c r="W47" s="32">
+      <c r="W47" s="34">
         <v>26.81</v>
       </c>
-      <c r="X47" s="32">
+      <c r="X47" s="34">
         <v>8.35</v>
       </c>
-      <c r="Y47" s="32">
+      <c r="Y47" s="34">
         <v>12.7</v>
       </c>
-      <c r="Z47" s="31"/>
-      <c r="AA47" s="31"/>
-      <c r="AB47" s="32">
+      <c r="Z47" s="33"/>
+      <c r="AA47" s="33"/>
+      <c r="AB47" s="34">
         <v>7.99</v>
       </c>
-      <c r="AC47" s="32">
+      <c r="AC47" s="34">
         <v>4.98</v>
       </c>
-      <c r="AD47" s="30">
+      <c r="AD47" s="32">
         <v>1514.77</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="29" t="s">
+      <c r="A48" s="31" t="s">
         <v>404</v>
       </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="32">
+      <c r="B48" s="33"/>
+      <c r="C48" s="34">
         <v>52.74</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="34">
         <v>27.93</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="34">
         <v>12.21</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="34">
         <v>13.75</v>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="34">
         <v>12.99</v>
       </c>
-      <c r="H48" s="32">
+      <c r="H48" s="34">
         <v>16.39</v>
       </c>
-      <c r="I48" s="32">
+      <c r="I48" s="34">
         <v>19.52</v>
       </c>
-      <c r="J48" s="32">
+      <c r="J48" s="34">
         <v>25.93</v>
       </c>
-      <c r="K48" s="32">
+      <c r="K48" s="34">
         <v>13.87</v>
       </c>
-      <c r="L48" s="32">
+      <c r="L48" s="34">
         <v>16.29</v>
       </c>
-      <c r="M48" s="32">
+      <c r="M48" s="34">
         <v>20.69</v>
       </c>
-      <c r="N48" s="31"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="31"/>
-      <c r="Q48" s="31"/>
-      <c r="R48" s="31"/>
-      <c r="S48" s="31"/>
-      <c r="T48" s="32">
+      <c r="N48" s="33"/>
+      <c r="O48" s="33"/>
+      <c r="P48" s="33"/>
+      <c r="Q48" s="33"/>
+      <c r="R48" s="33"/>
+      <c r="S48" s="33"/>
+      <c r="T48" s="34">
         <v>37.05</v>
       </c>
-      <c r="U48" s="32">
+      <c r="U48" s="34">
         <v>26.43</v>
       </c>
-      <c r="V48" s="32">
+      <c r="V48" s="34">
         <v>17.76</v>
       </c>
-      <c r="W48" s="32">
+      <c r="W48" s="34">
         <v>28.78</v>
       </c>
-      <c r="X48" s="32">
+      <c r="X48" s="34">
         <v>21.4</v>
       </c>
-      <c r="Y48" s="32">
+      <c r="Y48" s="34">
         <v>29.16</v>
       </c>
-      <c r="Z48" s="32">
+      <c r="Z48" s="34">
         <v>52.15</v>
       </c>
-      <c r="AA48" s="31"/>
-      <c r="AB48" s="31"/>
-      <c r="AC48" s="31"/>
-      <c r="AD48" s="31"/>
+      <c r="AA48" s="33"/>
+      <c r="AB48" s="33"/>
+      <c r="AC48" s="33"/>
+      <c r="AD48" s="33"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="27" t="s">
+      <c r="A49" s="29" t="s">
         <v>405</v>
       </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
-      <c r="N49" s="28"/>
-      <c r="O49" s="28"/>
-      <c r="P49" s="28"/>
-      <c r="Q49" s="28"/>
-      <c r="R49" s="28"/>
-      <c r="S49" s="28"/>
-      <c r="T49" s="28"/>
-      <c r="U49" s="28"/>
-      <c r="V49" s="28"/>
-      <c r="W49" s="28"/>
-      <c r="X49" s="28"/>
-      <c r="Y49" s="28"/>
-      <c r="Z49" s="28"/>
-      <c r="AA49" s="28"/>
-      <c r="AB49" s="28"/>
-      <c r="AC49" s="28"/>
-      <c r="AD49" s="28"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="29" t="s">
+      <c r="A50" s="31" t="s">
         <v>406</v>
       </c>
-      <c r="B50" s="31"/>
-      <c r="C50" s="32">
+      <c r="B50" s="33"/>
+      <c r="C50" s="34">
         <v>9.39</v>
       </c>
-      <c r="D50" s="31"/>
-      <c r="E50" s="32">
+      <c r="D50" s="33"/>
+      <c r="E50" s="34">
         <v>3.49</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="34">
         <v>8.08</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="34">
         <v>5.37</v>
       </c>
-      <c r="H50" s="32">
+      <c r="H50" s="34">
         <v>6.91</v>
       </c>
-      <c r="I50" s="32">
+      <c r="I50" s="34">
         <v>4.78</v>
       </c>
-      <c r="J50" s="32">
+      <c r="J50" s="34">
         <v>9.02</v>
       </c>
-      <c r="K50" s="32">
+      <c r="K50" s="34">
         <v>4.54</v>
       </c>
-      <c r="L50" s="32">
+      <c r="L50" s="34">
         <v>6.03</v>
       </c>
-      <c r="M50" s="32">
+      <c r="M50" s="34">
         <v>4.04</v>
       </c>
-      <c r="N50" s="32">
+      <c r="N50" s="34">
         <v>10.01</v>
       </c>
-      <c r="O50" s="32">
+      <c r="O50" s="34">
         <v>4.02</v>
       </c>
-      <c r="P50" s="32">
+      <c r="P50" s="34">
         <v>15.91</v>
       </c>
-      <c r="Q50" s="30">
+      <c r="Q50" s="32">
         <v>2100.58</v>
       </c>
-      <c r="R50" s="31"/>
-      <c r="S50" s="32">
+      <c r="R50" s="33"/>
+      <c r="S50" s="34">
         <v>2.89</v>
       </c>
-      <c r="T50" s="32">
+      <c r="T50" s="34">
         <v>6.78</v>
       </c>
-      <c r="U50" s="32">
+      <c r="U50" s="34">
         <v>15.63</v>
       </c>
-      <c r="V50" s="32">
+      <c r="V50" s="34">
         <v>11.06</v>
       </c>
-      <c r="W50" s="32">
+      <c r="W50" s="34">
         <v>8.02</v>
       </c>
-      <c r="X50" s="32">
+      <c r="X50" s="34">
         <v>9.59</v>
       </c>
-      <c r="Y50" s="32">
+      <c r="Y50" s="34">
         <v>6.83</v>
       </c>
-      <c r="Z50" s="32">
+      <c r="Z50" s="34">
         <v>2.69</v>
       </c>
-      <c r="AA50" s="32">
+      <c r="AA50" s="34">
         <v>5.17</v>
       </c>
-      <c r="AB50" s="32">
+      <c r="AB50" s="34">
         <v>5.89</v>
       </c>
-      <c r="AC50" s="32">
+      <c r="AC50" s="34">
         <v>3.15</v>
       </c>
-      <c r="AD50" s="32">
+      <c r="AD50" s="34">
         <v>4.75</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="29" t="s">
+      <c r="A51" s="31" t="s">
         <v>407</v>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="34">
         <v>18.05</v>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="34">
         <v>7.25</v>
       </c>
-      <c r="D51" s="32">
+      <c r="D51" s="34">
         <v>7.0</v>
       </c>
-      <c r="E51" s="32">
+      <c r="E51" s="34">
         <v>5.69</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="34">
         <v>6.73</v>
       </c>
-      <c r="G51" s="32">
+      <c r="G51" s="34">
         <v>5.97</v>
       </c>
-      <c r="H51" s="32">
+      <c r="H51" s="34">
         <v>6.17</v>
       </c>
-      <c r="I51" s="32">
+      <c r="I51" s="34">
         <v>5.73</v>
       </c>
-      <c r="J51" s="32">
+      <c r="J51" s="34">
         <v>6.44</v>
       </c>
-      <c r="K51" s="32">
+      <c r="K51" s="34">
         <v>5.32</v>
       </c>
-      <c r="L51" s="32">
+      <c r="L51" s="34">
         <v>6.43</v>
       </c>
-      <c r="M51" s="32">
+      <c r="M51" s="34">
         <v>9.02</v>
       </c>
-      <c r="N51" s="32">
+      <c r="N51" s="34">
         <v>36.2</v>
       </c>
-      <c r="O51" s="32">
+      <c r="O51" s="34">
         <v>7.51</v>
       </c>
-      <c r="P51" s="32">
+      <c r="P51" s="34">
         <v>7.22</v>
       </c>
-      <c r="Q51" s="32">
+      <c r="Q51" s="34">
         <v>9.52</v>
       </c>
-      <c r="R51" s="32">
+      <c r="R51" s="34">
         <v>9.6</v>
       </c>
-      <c r="S51" s="32">
+      <c r="S51" s="34">
         <v>8.72</v>
       </c>
-      <c r="T51" s="32">
+      <c r="T51" s="34">
         <v>9.72</v>
       </c>
-      <c r="U51" s="32">
+      <c r="U51" s="34">
         <v>10.22</v>
       </c>
-      <c r="V51" s="32">
+      <c r="V51" s="34">
         <v>6.93</v>
       </c>
-      <c r="W51" s="32">
+      <c r="W51" s="34">
         <v>5.9</v>
       </c>
-      <c r="X51" s="32">
+      <c r="X51" s="34">
         <v>5.48</v>
       </c>
-      <c r="Y51" s="32">
+      <c r="Y51" s="34">
         <v>4.36</v>
       </c>
-      <c r="Z51" s="32">
+      <c r="Z51" s="34">
         <v>4.06</v>
       </c>
-      <c r="AA51" s="31"/>
-      <c r="AB51" s="31"/>
-      <c r="AC51" s="31"/>
-      <c r="AD51" s="31"/>
+      <c r="AA51" s="33"/>
+      <c r="AB51" s="33"/>
+      <c r="AC51" s="33"/>
+      <c r="AD51" s="33"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="29" t="s">
         <v>408</v>
       </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="28"/>
-      <c r="S52" s="28"/>
-      <c r="T52" s="28"/>
-      <c r="U52" s="28"/>
-      <c r="V52" s="28"/>
-      <c r="W52" s="28"/>
-      <c r="X52" s="28"/>
-      <c r="Y52" s="28"/>
-      <c r="Z52" s="28"/>
-      <c r="AA52" s="28"/>
-      <c r="AB52" s="28"/>
-      <c r="AC52" s="28"/>
-      <c r="AD52" s="28"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
+      <c r="AA52" s="30"/>
+      <c r="AB52" s="30"/>
+      <c r="AC52" s="30"/>
+      <c r="AD52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
+      <c r="A53" s="31" t="s">
         <v>409</v>
       </c>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="32">
+      <c r="B53" s="33"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="34">
         <v>5.98</v>
       </c>
-      <c r="F53" s="32">
+      <c r="F53" s="34">
         <v>13.13</v>
       </c>
-      <c r="G53" s="32">
+      <c r="G53" s="34">
         <v>9.8</v>
       </c>
-      <c r="H53" s="32">
+      <c r="H53" s="34">
         <v>14.99</v>
       </c>
-      <c r="I53" s="32">
+      <c r="I53" s="34">
         <v>10.97</v>
       </c>
-      <c r="J53" s="32">
+      <c r="J53" s="34">
         <v>16.4</v>
       </c>
-      <c r="K53" s="32">
+      <c r="K53" s="34">
         <v>8.45</v>
       </c>
-      <c r="L53" s="32">
+      <c r="L53" s="34">
         <v>15.66</v>
       </c>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="31"/>
-      <c r="Q53" s="31"/>
-      <c r="R53" s="31"/>
-      <c r="S53" s="30">
+      <c r="M53" s="33"/>
+      <c r="N53" s="33"/>
+      <c r="O53" s="33"/>
+      <c r="P53" s="33"/>
+      <c r="Q53" s="33"/>
+      <c r="R53" s="33"/>
+      <c r="S53" s="32">
         <v>197.66</v>
       </c>
-      <c r="T53" s="32">
+      <c r="T53" s="34">
         <v>3.59</v>
       </c>
-      <c r="U53" s="32">
+      <c r="U53" s="34">
         <v>10.23</v>
       </c>
-      <c r="V53" s="32">
+      <c r="V53" s="34">
         <v>15.49</v>
       </c>
-      <c r="W53" s="32">
+      <c r="W53" s="34">
         <v>9.8</v>
       </c>
-      <c r="X53" s="32">
+      <c r="X53" s="34">
         <v>13.42</v>
       </c>
-      <c r="Y53" s="32">
+      <c r="Y53" s="34">
         <v>25.3</v>
       </c>
-      <c r="Z53" s="32">
+      <c r="Z53" s="34">
         <v>2.97</v>
       </c>
-      <c r="AA53" s="32">
+      <c r="AA53" s="34">
         <v>6.09</v>
       </c>
-      <c r="AB53" s="32">
+      <c r="AB53" s="34">
         <v>9.12</v>
       </c>
-      <c r="AC53" s="32">
+      <c r="AC53" s="34">
         <v>6.55</v>
       </c>
-      <c r="AD53" s="32">
+      <c r="AD53" s="34">
         <v>11.05</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="29" t="s">
+      <c r="A54" s="31" t="s">
         <v>410</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="32">
+      <c r="B54" s="33"/>
+      <c r="C54" s="34">
         <v>21.29</v>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="34">
         <v>16.44</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="34">
         <v>10.51</v>
       </c>
-      <c r="F54" s="32">
+      <c r="F54" s="34">
         <v>12.7</v>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="34">
         <v>11.83</v>
       </c>
-      <c r="H54" s="32">
+      <c r="H54" s="34">
         <v>13.07</v>
       </c>
-      <c r="I54" s="32">
+      <c r="I54" s="34">
         <v>13.83</v>
       </c>
-      <c r="J54" s="32">
+      <c r="J54" s="34">
         <v>21.08</v>
       </c>
-      <c r="K54" s="32">
+      <c r="K54" s="34">
         <v>45.95</v>
       </c>
-      <c r="L54" s="31"/>
-      <c r="M54" s="31"/>
-      <c r="N54" s="31"/>
-      <c r="O54" s="31"/>
-      <c r="P54" s="32">
+      <c r="L54" s="33"/>
+      <c r="M54" s="33"/>
+      <c r="N54" s="33"/>
+      <c r="O54" s="33"/>
+      <c r="P54" s="34">
         <v>20.62</v>
       </c>
-      <c r="Q54" s="32">
+      <c r="Q54" s="34">
         <v>12.62</v>
       </c>
-      <c r="R54" s="32">
+      <c r="R54" s="34">
         <v>10.83</v>
       </c>
-      <c r="S54" s="32">
+      <c r="S54" s="34">
         <v>7.85</v>
       </c>
-      <c r="T54" s="32">
+      <c r="T54" s="34">
         <v>8.13</v>
       </c>
-      <c r="U54" s="32">
+      <c r="U54" s="34">
         <v>12.41</v>
       </c>
-      <c r="V54" s="32">
+      <c r="V54" s="34">
         <v>9.39</v>
       </c>
-      <c r="W54" s="32">
+      <c r="W54" s="34">
         <v>7.7</v>
       </c>
-      <c r="X54" s="32">
+      <c r="X54" s="34">
         <v>7.4</v>
       </c>
-      <c r="Y54" s="32">
+      <c r="Y54" s="34">
         <v>6.19</v>
       </c>
-      <c r="Z54" s="32">
+      <c r="Z54" s="34">
         <v>5.55</v>
       </c>
-      <c r="AA54" s="31"/>
-      <c r="AB54" s="31"/>
-      <c r="AC54" s="31"/>
-      <c r="AD54" s="31"/>
+      <c r="AA54" s="33"/>
+      <c r="AB54" s="33"/>
+      <c r="AC54" s="33"/>
+      <c r="AD54" s="33"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="29" t="s">
         <v>411</v>
       </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
-      <c r="M55" s="28"/>
-      <c r="N55" s="28"/>
-      <c r="O55" s="28"/>
-      <c r="P55" s="28"/>
-      <c r="Q55" s="28"/>
-      <c r="R55" s="28"/>
-      <c r="S55" s="28"/>
-      <c r="T55" s="28"/>
-      <c r="U55" s="28"/>
-      <c r="V55" s="28"/>
-      <c r="W55" s="28"/>
-      <c r="X55" s="28"/>
-      <c r="Y55" s="28"/>
-      <c r="Z55" s="28"/>
-      <c r="AA55" s="28"/>
-      <c r="AB55" s="28"/>
-      <c r="AC55" s="28"/>
-      <c r="AD55" s="28"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="30"/>
+      <c r="X55" s="30"/>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30"/>
+      <c r="AA55" s="30"/>
+      <c r="AB55" s="30"/>
+      <c r="AC55" s="30"/>
+      <c r="AD55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="B56" s="30">
+      <c r="B56" s="32">
         <v>126.75</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="34">
         <v>10.12</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="34">
         <v>31.52</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="34">
         <v>5.24</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="34">
         <v>11.63</v>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="34">
         <v>9.6</v>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="34">
         <v>13.7</v>
       </c>
-      <c r="I56" s="32">
+      <c r="I56" s="34">
         <v>7.14</v>
       </c>
-      <c r="J56" s="32">
+      <c r="J56" s="34">
         <v>11.97</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="34">
         <v>7.59</v>
       </c>
-      <c r="L56" s="32">
+      <c r="L56" s="34">
         <v>84.24</v>
       </c>
-      <c r="M56" s="30">
+      <c r="M56" s="32">
         <v>667.27</v>
       </c>
-      <c r="N56" s="31"/>
-      <c r="O56" s="31"/>
-      <c r="P56" s="31"/>
-      <c r="Q56" s="31"/>
-      <c r="R56" s="31"/>
-      <c r="S56" s="31"/>
-      <c r="T56" s="32">
+      <c r="N56" s="33"/>
+      <c r="O56" s="33"/>
+      <c r="P56" s="33"/>
+      <c r="Q56" s="33"/>
+      <c r="R56" s="33"/>
+      <c r="S56" s="33"/>
+      <c r="T56" s="34">
         <v>13.67</v>
       </c>
-      <c r="U56" s="32">
+      <c r="U56" s="34">
         <v>70.55</v>
       </c>
-      <c r="V56" s="32">
+      <c r="V56" s="34">
         <v>29.37</v>
       </c>
-      <c r="W56" s="32">
+      <c r="W56" s="34">
         <v>15.65</v>
       </c>
-      <c r="X56" s="32">
+      <c r="X56" s="34">
         <v>24.32</v>
       </c>
-      <c r="Y56" s="32">
+      <c r="Y56" s="34">
         <v>25.3</v>
       </c>
-      <c r="Z56" s="32">
+      <c r="Z56" s="34">
         <v>10.27</v>
       </c>
-      <c r="AA56" s="32">
+      <c r="AA56" s="34">
         <v>16.15</v>
       </c>
-      <c r="AB56" s="32">
+      <c r="AB56" s="34">
         <v>23.05</v>
       </c>
-      <c r="AC56" s="32">
+      <c r="AC56" s="34">
         <v>8.56</v>
       </c>
-      <c r="AD56" s="32">
+      <c r="AD56" s="34">
         <v>22.55</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="29" t="s">
+      <c r="A57" s="31" t="s">
         <v>413</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="34">
         <v>1.29</v>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="34">
         <v>1.3</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="34">
         <v>1.46</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="34">
         <v>1.62</v>
       </c>
-      <c r="F57" s="32">
+      <c r="F57" s="34">
         <v>2.08</v>
       </c>
-      <c r="G57" s="32">
+      <c r="G57" s="34">
         <v>2.05</v>
       </c>
-      <c r="H57" s="32">
+      <c r="H57" s="34">
         <v>2.37</v>
       </c>
-      <c r="I57" s="32">
+      <c r="I57" s="34">
         <v>2.73</v>
       </c>
-      <c r="J57" s="32">
+      <c r="J57" s="34">
         <v>3.0</v>
       </c>
-      <c r="K57" s="32">
+      <c r="K57" s="34">
         <v>1.97</v>
       </c>
-      <c r="L57" s="32">
+      <c r="L57" s="34">
         <v>1.49</v>
       </c>
-      <c r="M57" s="32">
+      <c r="M57" s="34">
         <v>1.0</v>
       </c>
-      <c r="N57" s="32">
+      <c r="N57" s="34">
         <v>0.81</v>
       </c>
-      <c r="O57" s="32">
+      <c r="O57" s="34">
         <v>0.54</v>
       </c>
-      <c r="P57" s="32">
+      <c r="P57" s="34">
         <v>0.88</v>
       </c>
-      <c r="Q57" s="32">
+      <c r="Q57" s="34">
         <v>1.22</v>
       </c>
-      <c r="R57" s="32">
+      <c r="R57" s="34">
         <v>1.33</v>
       </c>
-      <c r="S57" s="32">
+      <c r="S57" s="34">
         <v>1.42</v>
       </c>
-      <c r="T57" s="32">
+      <c r="T57" s="34">
         <v>1.71</v>
       </c>
-      <c r="U57" s="32">
+      <c r="U57" s="34">
         <v>1.71</v>
       </c>
-      <c r="V57" s="32">
+      <c r="V57" s="34">
         <v>1.53</v>
       </c>
-      <c r="W57" s="32">
+      <c r="W57" s="34">
         <v>1.63</v>
       </c>
-      <c r="X57" s="32">
+      <c r="X57" s="34">
         <v>1.7</v>
       </c>
-      <c r="Y57" s="32">
+      <c r="Y57" s="34">
         <v>1.58</v>
       </c>
-      <c r="Z57" s="32">
+      <c r="Z57" s="34">
         <v>1.71</v>
       </c>
-      <c r="AA57" s="31"/>
-      <c r="AB57" s="31"/>
-      <c r="AC57" s="31"/>
-      <c r="AD57" s="31"/>
+      <c r="AA57" s="33"/>
+      <c r="AB57" s="33"/>
+      <c r="AC57" s="33"/>
+      <c r="AD57" s="33"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="27" t="s">
+      <c r="A58" s="29" t="s">
         <v>414</v>
       </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
-      <c r="M58" s="28"/>
-      <c r="N58" s="28"/>
-      <c r="O58" s="28"/>
-      <c r="P58" s="28"/>
-      <c r="Q58" s="28"/>
-      <c r="R58" s="28"/>
-      <c r="S58" s="28"/>
-      <c r="T58" s="28"/>
-      <c r="U58" s="28"/>
-      <c r="V58" s="28"/>
-      <c r="W58" s="28"/>
-      <c r="X58" s="28"/>
-      <c r="Y58" s="28"/>
-      <c r="Z58" s="28"/>
-      <c r="AA58" s="28"/>
-      <c r="AB58" s="28"/>
-      <c r="AC58" s="28"/>
-      <c r="AD58" s="28"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30"/>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
+      <c r="AA58" s="30"/>
+      <c r="AB58" s="30"/>
+      <c r="AC58" s="30"/>
+      <c r="AD58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="29" t="s">
+      <c r="A59" s="31" t="s">
         <v>415</v>
       </c>
-      <c r="B59" s="31"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="35">
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="37">
         <v>-2.92</v>
       </c>
-      <c r="F59" s="32">
+      <c r="F59" s="34">
         <v>0.44</v>
       </c>
-      <c r="G59" s="32">
+      <c r="G59" s="34">
         <v>0.16</v>
       </c>
-      <c r="H59" s="35">
+      <c r="H59" s="37">
         <v>-3.89</v>
       </c>
-      <c r="I59" s="32">
+      <c r="I59" s="34">
         <v>0.65</v>
       </c>
-      <c r="J59" s="35">
+      <c r="J59" s="37">
         <v>-16.71</v>
       </c>
-      <c r="K59" s="32">
+      <c r="K59" s="34">
         <v>0.14</v>
       </c>
-      <c r="L59" s="32">
+      <c r="L59" s="34">
         <v>0.02</v>
       </c>
-      <c r="M59" s="31"/>
-      <c r="N59" s="31"/>
-      <c r="O59" s="31"/>
-      <c r="P59" s="31"/>
-      <c r="Q59" s="31"/>
-      <c r="R59" s="31"/>
-      <c r="S59" s="35">
+      <c r="M59" s="33"/>
+      <c r="N59" s="33"/>
+      <c r="O59" s="33"/>
+      <c r="P59" s="33"/>
+      <c r="Q59" s="33"/>
+      <c r="R59" s="33"/>
+      <c r="S59" s="37">
         <v>-1.98</v>
       </c>
-      <c r="T59" s="32">
+      <c r="T59" s="34">
         <v>0.03</v>
       </c>
-      <c r="U59" s="32">
+      <c r="U59" s="34">
         <v>0.1</v>
       </c>
-      <c r="V59" s="35">
+      <c r="V59" s="37">
         <v>-0.57</v>
       </c>
-      <c r="W59" s="32">
+      <c r="W59" s="34">
         <v>0.37</v>
       </c>
-      <c r="X59" s="32">
+      <c r="X59" s="34">
         <v>0.05</v>
       </c>
-      <c r="Y59" s="35">
+      <c r="Y59" s="37">
         <v>-0.29</v>
       </c>
-      <c r="Z59" s="32">
+      <c r="Z59" s="34">
         <v>0.06</v>
       </c>
-      <c r="AA59" s="32">
+      <c r="AA59" s="34">
         <v>0.04</v>
       </c>
-      <c r="AB59" s="32">
+      <c r="AB59" s="34">
         <v>0.54</v>
       </c>
-      <c r="AC59" s="32">
+      <c r="AC59" s="34">
         <v>0.14</v>
       </c>
-      <c r="AD59" s="31"/>
+      <c r="AD59" s="33"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="29" t="s">
+      <c r="A60" s="31" t="s">
         <v>416</v>
       </c>
-      <c r="B60" s="31"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="32">
+      <c r="B60" s="33"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="34">
         <v>0.57</v>
       </c>
-      <c r="F60" s="32">
+      <c r="F60" s="34">
         <v>0.68</v>
       </c>
-      <c r="G60" s="32">
+      <c r="G60" s="34">
         <v>0.5</v>
       </c>
-      <c r="H60" s="31"/>
-      <c r="I60" s="31"/>
-      <c r="J60" s="31"/>
-      <c r="K60" s="31"/>
-      <c r="L60" s="31"/>
-      <c r="M60" s="31"/>
-      <c r="N60" s="31"/>
-      <c r="O60" s="31"/>
-      <c r="P60" s="31"/>
-      <c r="Q60" s="31"/>
-      <c r="R60" s="31"/>
-      <c r="S60" s="35">
+      <c r="H60" s="33"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
+      <c r="M60" s="33"/>
+      <c r="N60" s="33"/>
+      <c r="O60" s="33"/>
+      <c r="P60" s="33"/>
+      <c r="Q60" s="33"/>
+      <c r="R60" s="33"/>
+      <c r="S60" s="37">
         <v>-0.14</v>
       </c>
-      <c r="T60" s="32">
+      <c r="T60" s="34">
         <v>0.12</v>
       </c>
-      <c r="U60" s="35">
+      <c r="U60" s="37">
         <v>-3.49</v>
       </c>
-      <c r="V60" s="35">
+      <c r="V60" s="37">
         <v>-0.94</v>
       </c>
-      <c r="W60" s="32">
+      <c r="W60" s="34">
         <v>0.55</v>
       </c>
-      <c r="X60" s="32">
+      <c r="X60" s="34">
         <v>0.61</v>
       </c>
-      <c r="Y60" s="35">
+      <c r="Y60" s="37">
         <v>-1.02</v>
       </c>
-      <c r="Z60" s="31"/>
-      <c r="AA60" s="31"/>
-      <c r="AB60" s="31"/>
-      <c r="AC60" s="31"/>
-      <c r="AD60" s="31"/>
+      <c r="Z60" s="33"/>
+      <c r="AA60" s="33"/>
+      <c r="AB60" s="33"/>
+      <c r="AC60" s="33"/>
+      <c r="AD60" s="33"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="29" t="s">
         <v>417</v>
       </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="28"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="28"/>
-      <c r="M61" s="28"/>
-      <c r="N61" s="28"/>
-      <c r="O61" s="28"/>
-      <c r="P61" s="28"/>
-      <c r="Q61" s="28"/>
-      <c r="R61" s="28"/>
-      <c r="S61" s="28"/>
-      <c r="T61" s="28"/>
-      <c r="U61" s="28"/>
-      <c r="V61" s="28"/>
-      <c r="W61" s="28"/>
-      <c r="X61" s="28"/>
-      <c r="Y61" s="28"/>
-      <c r="Z61" s="28"/>
-      <c r="AA61" s="28"/>
-      <c r="AB61" s="28"/>
-      <c r="AC61" s="28"/>
-      <c r="AD61" s="28"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="30"/>
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
+      <c r="AA61" s="30"/>
+      <c r="AB61" s="30"/>
+      <c r="AC61" s="30"/>
+      <c r="AD61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="29" t="s">
+      <c r="A62" s="31" t="s">
         <v>418</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="34">
         <v>0.88</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="34">
         <v>0.75</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="34">
         <v>0.91</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="34">
         <v>0.66</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="34">
         <v>1.52</v>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="34">
         <v>1.01</v>
       </c>
-      <c r="H62" s="32">
+      <c r="H62" s="34">
         <v>0.95</v>
       </c>
-      <c r="I62" s="32">
+      <c r="I62" s="34">
         <v>0.89</v>
       </c>
-      <c r="J62" s="32">
+      <c r="J62" s="34">
         <v>1.25</v>
       </c>
-      <c r="K62" s="32">
+      <c r="K62" s="34">
         <v>0.75</v>
       </c>
-      <c r="L62" s="32">
+      <c r="L62" s="34">
         <v>0.85</v>
       </c>
-      <c r="M62" s="32">
+      <c r="M62" s="34">
         <v>0.63</v>
       </c>
-      <c r="N62" s="32">
+      <c r="N62" s="34">
         <v>0.79</v>
       </c>
-      <c r="O62" s="32">
+      <c r="O62" s="34">
         <v>0.65</v>
       </c>
-      <c r="P62" s="32">
+      <c r="P62" s="34">
         <v>0.8</v>
       </c>
-      <c r="Q62" s="32">
+      <c r="Q62" s="34">
         <v>0.96</v>
       </c>
-      <c r="R62" s="32">
+      <c r="R62" s="34">
         <v>0.58</v>
       </c>
-      <c r="S62" s="32">
+      <c r="S62" s="34">
         <v>0.17</v>
       </c>
-      <c r="T62" s="32">
+      <c r="T62" s="34">
         <v>0.88</v>
       </c>
-      <c r="U62" s="32">
+      <c r="U62" s="34">
         <v>1.23</v>
       </c>
-      <c r="V62" s="32">
+      <c r="V62" s="34">
         <v>1.01</v>
       </c>
-      <c r="W62" s="32">
+      <c r="W62" s="34">
         <v>0.73</v>
       </c>
-      <c r="X62" s="32">
+      <c r="X62" s="34">
         <v>0.75</v>
       </c>
-      <c r="Y62" s="32">
+      <c r="Y62" s="34">
         <v>0.56</v>
       </c>
-      <c r="Z62" s="32">
+      <c r="Z62" s="34">
         <v>0.57</v>
       </c>
-      <c r="AA62" s="32">
+      <c r="AA62" s="34">
         <v>0.68</v>
       </c>
-      <c r="AB62" s="32">
+      <c r="AB62" s="34">
         <v>0.52</v>
       </c>
-      <c r="AC62" s="32">
+      <c r="AC62" s="34">
         <v>0.41</v>
       </c>
-      <c r="AD62" s="32">
+      <c r="AD62" s="34">
         <v>0.44</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="29" t="s">
+      <c r="A63" s="31" t="s">
         <v>419</v>
       </c>
-      <c r="B63" s="32">
+      <c r="B63" s="34">
         <v>0.94</v>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="34">
         <v>0.96</v>
       </c>
-      <c r="D63" s="32">
+      <c r="D63" s="34">
         <v>1.0</v>
       </c>
-      <c r="E63" s="32">
+      <c r="E63" s="34">
         <v>1.0</v>
       </c>
-      <c r="F63" s="32">
+      <c r="F63" s="34">
         <v>1.12</v>
       </c>
-      <c r="G63" s="32">
+      <c r="G63" s="34">
         <v>0.96</v>
       </c>
-      <c r="H63" s="32">
+      <c r="H63" s="34">
         <v>0.93</v>
       </c>
-      <c r="I63" s="32">
+      <c r="I63" s="34">
         <v>0.88</v>
       </c>
-      <c r="J63" s="32">
+      <c r="J63" s="34">
         <v>0.86</v>
       </c>
-      <c r="K63" s="32">
+      <c r="K63" s="34">
         <v>0.74</v>
       </c>
-      <c r="L63" s="32">
+      <c r="L63" s="34">
         <v>0.75</v>
       </c>
-      <c r="M63" s="32">
+      <c r="M63" s="34">
         <v>0.76</v>
       </c>
-      <c r="N63" s="32">
+      <c r="N63" s="34">
         <v>0.76</v>
       </c>
-      <c r="O63" s="32">
+      <c r="O63" s="34">
         <v>0.62</v>
       </c>
-      <c r="P63" s="32">
+      <c r="P63" s="34">
         <v>0.68</v>
       </c>
-      <c r="Q63" s="32">
+      <c r="Q63" s="34">
         <v>0.79</v>
       </c>
-      <c r="R63" s="32">
+      <c r="R63" s="34">
         <v>0.8</v>
       </c>
-      <c r="S63" s="32">
+      <c r="S63" s="34">
         <v>0.82</v>
       </c>
-      <c r="T63" s="32">
+      <c r="T63" s="34">
         <v>0.93</v>
       </c>
-      <c r="U63" s="32">
+      <c r="U63" s="34">
         <v>0.87</v>
       </c>
-      <c r="V63" s="32">
+      <c r="V63" s="34">
         <v>0.73</v>
       </c>
-      <c r="W63" s="32">
+      <c r="W63" s="34">
         <v>0.66</v>
       </c>
-      <c r="X63" s="32">
+      <c r="X63" s="34">
         <v>0.61</v>
       </c>
-      <c r="Y63" s="32">
+      <c r="Y63" s="34">
         <v>0.54</v>
       </c>
-      <c r="Z63" s="32">
+      <c r="Z63" s="34">
         <v>0.52</v>
       </c>
-      <c r="AA63" s="31"/>
-      <c r="AB63" s="31"/>
-      <c r="AC63" s="31"/>
-      <c r="AD63" s="31"/>
+      <c r="AA63" s="33"/>
+      <c r="AB63" s="33"/>
+      <c r="AC63" s="33"/>
+      <c r="AD63" s="33"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="27" t="s">
+      <c r="A64" s="29" t="s">
         <v>420</v>
       </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="28"/>
-      <c r="K64" s="28"/>
-      <c r="L64" s="28"/>
-      <c r="M64" s="28"/>
-      <c r="N64" s="28"/>
-      <c r="O64" s="28"/>
-      <c r="P64" s="28"/>
-      <c r="Q64" s="28"/>
-      <c r="R64" s="28"/>
-      <c r="S64" s="28"/>
-      <c r="T64" s="28"/>
-      <c r="U64" s="28"/>
-      <c r="V64" s="28"/>
-      <c r="W64" s="28"/>
-      <c r="X64" s="28"/>
-      <c r="Y64" s="28"/>
-      <c r="Z64" s="28"/>
-      <c r="AA64" s="28"/>
-      <c r="AB64" s="28"/>
-      <c r="AC64" s="28"/>
-      <c r="AD64" s="28"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="30"/>
+      <c r="Y64" s="30"/>
+      <c r="Z64" s="30"/>
+      <c r="AA64" s="30"/>
+      <c r="AB64" s="30"/>
+      <c r="AC64" s="30"/>
+      <c r="AD64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="29" t="s">
+      <c r="A65" s="31" t="s">
         <v>421</v>
       </c>
-      <c r="B65" s="32">
+      <c r="B65" s="34">
         <v>8.4</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="34">
         <v>8.53</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="34">
         <v>10.93</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="34">
         <v>3.71</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="34">
         <v>7.83</v>
       </c>
-      <c r="G65" s="32">
+      <c r="G65" s="34">
         <v>5.22</v>
       </c>
-      <c r="H65" s="32">
+      <c r="H65" s="34">
         <v>5.02</v>
       </c>
-      <c r="I65" s="32">
+      <c r="I65" s="34">
         <v>6.31</v>
       </c>
-      <c r="J65" s="32">
+      <c r="J65" s="34">
         <v>8.22</v>
       </c>
-      <c r="K65" s="32">
+      <c r="K65" s="34">
         <v>5.93</v>
       </c>
-      <c r="L65" s="32">
+      <c r="L65" s="34">
         <v>9.29</v>
       </c>
-      <c r="M65" s="32">
+      <c r="M65" s="34">
         <v>6.1</v>
       </c>
-      <c r="N65" s="32">
+      <c r="N65" s="34">
         <v>11.63</v>
       </c>
-      <c r="O65" s="32">
+      <c r="O65" s="34">
         <v>8.18</v>
       </c>
-      <c r="P65" s="32">
+      <c r="P65" s="34">
         <v>12.07</v>
       </c>
-      <c r="Q65" s="31"/>
-      <c r="R65" s="32">
+      <c r="Q65" s="33"/>
+      <c r="R65" s="34">
         <v>7.23</v>
       </c>
-      <c r="S65" s="31"/>
-      <c r="T65" s="32">
+      <c r="S65" s="33"/>
+      <c r="T65" s="34">
         <v>4.6</v>
       </c>
-      <c r="U65" s="31"/>
-      <c r="V65" s="32">
+      <c r="U65" s="33"/>
+      <c r="V65" s="34">
         <v>5.98</v>
       </c>
-      <c r="W65" s="31"/>
-      <c r="X65" s="32">
+      <c r="W65" s="33"/>
+      <c r="X65" s="34">
         <v>4.56</v>
       </c>
-      <c r="Y65" s="32">
+      <c r="Y65" s="34">
         <v>5.86</v>
       </c>
-      <c r="Z65" s="32">
+      <c r="Z65" s="34">
         <v>3.93</v>
       </c>
-      <c r="AA65" s="32">
+      <c r="AA65" s="34">
         <v>6.14</v>
       </c>
-      <c r="AB65" s="32">
+      <c r="AB65" s="34">
         <v>4.15</v>
       </c>
-      <c r="AC65" s="32">
+      <c r="AC65" s="34">
         <v>4.2</v>
       </c>
-      <c r="AD65" s="32">
+      <c r="AD65" s="34">
         <v>4.52</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="31" t="s">
         <v>422</v>
       </c>
-      <c r="B66" s="32">
+      <c r="B66" s="34">
         <v>7.01</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="34">
         <v>6.42</v>
       </c>
-      <c r="D66" s="32">
+      <c r="D66" s="34">
         <v>5.91</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="34">
         <v>5.54</v>
       </c>
-      <c r="F66" s="32">
+      <c r="F66" s="34">
         <v>6.36</v>
       </c>
-      <c r="G66" s="32">
+      <c r="G66" s="34">
         <v>5.85</v>
       </c>
-      <c r="H66" s="32">
+      <c r="H66" s="34">
         <v>6.4</v>
       </c>
-      <c r="I66" s="32">
+      <c r="I66" s="34">
         <v>7.05</v>
       </c>
-      <c r="J66" s="32">
+      <c r="J66" s="34">
         <v>7.84</v>
       </c>
-      <c r="K66" s="32">
+      <c r="K66" s="34">
         <v>7.75</v>
       </c>
-      <c r="L66" s="32">
+      <c r="L66" s="34">
         <v>9.08</v>
       </c>
-      <c r="M66" s="31"/>
-      <c r="N66" s="31"/>
-      <c r="O66" s="31"/>
-      <c r="P66" s="31"/>
-      <c r="Q66" s="31"/>
-      <c r="R66" s="31"/>
-      <c r="S66" s="31"/>
-      <c r="T66" s="30">
+      <c r="M66" s="33"/>
+      <c r="N66" s="33"/>
+      <c r="O66" s="33"/>
+      <c r="P66" s="33"/>
+      <c r="Q66" s="33"/>
+      <c r="R66" s="33"/>
+      <c r="S66" s="33"/>
+      <c r="T66" s="32">
         <v>470.63</v>
       </c>
-      <c r="U66" s="31"/>
-      <c r="V66" s="32">
+      <c r="U66" s="33"/>
+      <c r="V66" s="34">
         <v>8.66</v>
       </c>
-      <c r="W66" s="32">
+      <c r="W66" s="34">
         <v>8.93</v>
       </c>
-      <c r="X66" s="32">
+      <c r="X66" s="34">
         <v>4.81</v>
       </c>
-      <c r="Y66" s="32">
+      <c r="Y66" s="34">
         <v>4.76</v>
       </c>
-      <c r="Z66" s="32">
+      <c r="Z66" s="34">
         <v>4.56</v>
       </c>
-      <c r="AA66" s="31"/>
-      <c r="AB66" s="31"/>
-      <c r="AC66" s="31"/>
-      <c r="AD66" s="31"/>
+      <c r="AA66" s="33"/>
+      <c r="AB66" s="33"/>
+      <c r="AC66" s="33"/>
+      <c r="AD66" s="33"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="27" t="s">
+      <c r="A67" s="29" t="s">
         <v>423</v>
       </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="28"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="28"/>
-      <c r="M67" s="28"/>
-      <c r="N67" s="28"/>
-      <c r="O67" s="28"/>
-      <c r="P67" s="28"/>
-      <c r="Q67" s="28"/>
-      <c r="R67" s="28"/>
-      <c r="S67" s="28"/>
-      <c r="T67" s="28"/>
-      <c r="U67" s="28"/>
-      <c r="V67" s="28"/>
-      <c r="W67" s="28"/>
-      <c r="X67" s="28"/>
-      <c r="Y67" s="28"/>
-      <c r="Z67" s="28"/>
-      <c r="AA67" s="28"/>
-      <c r="AB67" s="28"/>
-      <c r="AC67" s="28"/>
-      <c r="AD67" s="28"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
+      <c r="V67" s="30"/>
+      <c r="W67" s="30"/>
+      <c r="X67" s="30"/>
+      <c r="Y67" s="30"/>
+      <c r="Z67" s="30"/>
+      <c r="AA67" s="30"/>
+      <c r="AB67" s="30"/>
+      <c r="AC67" s="30"/>
+      <c r="AD67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="31" t="s">
         <v>424</v>
       </c>
-      <c r="B68" s="32">
+      <c r="B68" s="34">
         <v>34.07</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="34">
         <v>14.24</v>
       </c>
-      <c r="D68" s="31"/>
-      <c r="E68" s="32">
+      <c r="D68" s="33"/>
+      <c r="E68" s="34">
         <v>7.54</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="34">
         <v>10.12</v>
       </c>
-      <c r="G68" s="32">
+      <c r="G68" s="34">
         <v>6.29</v>
       </c>
-      <c r="H68" s="32">
+      <c r="H68" s="34">
         <v>7.29</v>
       </c>
-      <c r="I68" s="32">
+      <c r="I68" s="34">
         <v>6.04</v>
       </c>
-      <c r="J68" s="32">
+      <c r="J68" s="34">
         <v>24.3</v>
       </c>
-      <c r="K68" s="32">
+      <c r="K68" s="34">
         <v>8.4</v>
       </c>
-      <c r="L68" s="32">
+      <c r="L68" s="34">
         <v>12.3</v>
       </c>
-      <c r="M68" s="32">
+      <c r="M68" s="34">
         <v>9.62</v>
       </c>
-      <c r="N68" s="32">
+      <c r="N68" s="34">
         <v>17.16</v>
       </c>
-      <c r="O68" s="32">
+      <c r="O68" s="34">
         <v>17.86</v>
       </c>
-      <c r="P68" s="32">
+      <c r="P68" s="34">
         <v>24.32</v>
       </c>
-      <c r="Q68" s="32">
+      <c r="Q68" s="34">
         <v>30.98</v>
       </c>
-      <c r="R68" s="31"/>
-      <c r="S68" s="32">
+      <c r="R68" s="33"/>
+      <c r="S68" s="34">
         <v>4.08</v>
       </c>
-      <c r="T68" s="32">
+      <c r="T68" s="34">
         <v>6.13</v>
       </c>
-      <c r="U68" s="32">
+      <c r="U68" s="34">
         <v>34.15</v>
       </c>
-      <c r="V68" s="32">
+      <c r="V68" s="34">
         <v>6.63</v>
       </c>
-      <c r="W68" s="32">
+      <c r="W68" s="34">
         <v>6.08</v>
       </c>
-      <c r="X68" s="32">
+      <c r="X68" s="34">
         <v>4.92</v>
       </c>
-      <c r="Y68" s="32">
+      <c r="Y68" s="34">
         <v>6.28</v>
       </c>
-      <c r="Z68" s="32">
+      <c r="Z68" s="34">
         <v>4.3</v>
       </c>
-      <c r="AA68" s="32">
+      <c r="AA68" s="34">
         <v>8.55</v>
       </c>
-      <c r="AB68" s="32">
+      <c r="AB68" s="34">
         <v>4.86</v>
       </c>
-      <c r="AC68" s="32">
+      <c r="AC68" s="34">
         <v>3.32</v>
       </c>
-      <c r="AD68" s="32">
+      <c r="AD68" s="34">
         <v>9.25</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="31" t="s">
         <v>425</v>
       </c>
-      <c r="B69" s="32">
+      <c r="B69" s="34">
         <v>17.89</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="34">
         <v>12.52</v>
       </c>
-      <c r="D69" s="32">
+      <c r="D69" s="34">
         <v>10.91</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="34">
         <v>7.54</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="34">
         <v>8.36</v>
       </c>
-      <c r="G69" s="32">
+      <c r="G69" s="34">
         <v>7.78</v>
       </c>
-      <c r="H69" s="32">
+      <c r="H69" s="34">
         <v>8.84</v>
       </c>
-      <c r="I69" s="32">
+      <c r="I69" s="34">
         <v>9.65</v>
       </c>
-      <c r="J69" s="32">
+      <c r="J69" s="34">
         <v>13.29</v>
       </c>
-      <c r="K69" s="32">
+      <c r="K69" s="34">
         <v>11.7</v>
       </c>
-      <c r="L69" s="32">
+      <c r="L69" s="34">
         <v>14.62</v>
       </c>
-      <c r="M69" s="32">
+      <c r="M69" s="34">
         <v>17.78</v>
       </c>
-      <c r="N69" s="32">
+      <c r="N69" s="34">
         <v>32.68</v>
       </c>
-      <c r="O69" s="32">
+      <c r="O69" s="34">
         <v>26.84</v>
       </c>
-      <c r="P69" s="32">
+      <c r="P69" s="34">
         <v>12.82</v>
       </c>
-      <c r="Q69" s="32">
+      <c r="Q69" s="34">
         <v>14.87</v>
       </c>
-      <c r="R69" s="32">
+      <c r="R69" s="34">
         <v>10.72</v>
       </c>
-      <c r="S69" s="32">
+      <c r="S69" s="34">
         <v>8.31</v>
       </c>
-      <c r="T69" s="32">
+      <c r="T69" s="34">
         <v>7.7</v>
       </c>
-      <c r="U69" s="32">
+      <c r="U69" s="34">
         <v>8.01</v>
       </c>
-      <c r="V69" s="32">
+      <c r="V69" s="34">
         <v>5.6</v>
       </c>
-      <c r="W69" s="32">
+      <c r="W69" s="34">
         <v>5.82</v>
       </c>
-      <c r="X69" s="32">
+      <c r="X69" s="34">
         <v>5.53</v>
       </c>
-      <c r="Y69" s="32">
+      <c r="Y69" s="34">
         <v>5.11</v>
       </c>
-      <c r="Z69" s="32">
+      <c r="Z69" s="34">
         <v>5.39</v>
       </c>
-      <c r="AA69" s="31"/>
-      <c r="AB69" s="31"/>
-      <c r="AC69" s="31"/>
-      <c r="AD69" s="31"/>
+      <c r="AA69" s="33"/>
+      <c r="AB69" s="33"/>
+      <c r="AC69" s="33"/>
+      <c r="AD69" s="33"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="27" t="s">
+      <c r="A70" s="29" t="s">
         <v>426</v>
       </c>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="28"/>
-      <c r="L70" s="28"/>
-      <c r="M70" s="28"/>
-      <c r="N70" s="28"/>
-      <c r="O70" s="28"/>
-      <c r="P70" s="28"/>
-      <c r="Q70" s="28"/>
-      <c r="R70" s="28"/>
-      <c r="S70" s="28"/>
-      <c r="T70" s="28"/>
-      <c r="U70" s="28"/>
-      <c r="V70" s="28"/>
-      <c r="W70" s="28"/>
-      <c r="X70" s="28"/>
-      <c r="Y70" s="28"/>
-      <c r="Z70" s="28"/>
-      <c r="AA70" s="28"/>
-      <c r="AB70" s="28"/>
-      <c r="AC70" s="28"/>
-      <c r="AD70" s="28"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+      <c r="S70" s="30"/>
+      <c r="T70" s="30"/>
+      <c r="U70" s="30"/>
+      <c r="V70" s="30"/>
+      <c r="W70" s="30"/>
+      <c r="X70" s="30"/>
+      <c r="Y70" s="30"/>
+      <c r="Z70" s="30"/>
+      <c r="AA70" s="30"/>
+      <c r="AB70" s="30"/>
+      <c r="AC70" s="30"/>
+      <c r="AD70" s="30"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="29" t="s">
+      <c r="A71" s="31" t="s">
         <v>427</v>
       </c>
-      <c r="B71" s="31"/>
-      <c r="C71" s="32">
+      <c r="B71" s="33"/>
+      <c r="C71" s="34">
         <v>98.31</v>
       </c>
-      <c r="D71" s="31"/>
-      <c r="E71" s="32">
+      <c r="D71" s="33"/>
+      <c r="E71" s="34">
         <v>47.67</v>
       </c>
-      <c r="F71" s="32">
+      <c r="F71" s="34">
         <v>17.88</v>
       </c>
-      <c r="G71" s="32">
+      <c r="G71" s="34">
         <v>9.19</v>
       </c>
-      <c r="H71" s="32">
+      <c r="H71" s="34">
         <v>11.06</v>
       </c>
-      <c r="I71" s="32">
+      <c r="I71" s="34">
         <v>17.45</v>
       </c>
-      <c r="J71" s="31"/>
-      <c r="K71" s="32">
+      <c r="J71" s="33"/>
+      <c r="K71" s="34">
         <v>20.11</v>
       </c>
-      <c r="L71" s="32">
+      <c r="L71" s="34">
         <v>26.81</v>
       </c>
-      <c r="M71" s="32">
+      <c r="M71" s="34">
         <v>18.3</v>
       </c>
-      <c r="N71" s="32">
+      <c r="N71" s="34">
         <v>44.77</v>
       </c>
-      <c r="O71" s="32">
+      <c r="O71" s="34">
         <v>40.19</v>
       </c>
-      <c r="P71" s="30">
+      <c r="P71" s="32">
         <v>172.47</v>
       </c>
-      <c r="Q71" s="30">
+      <c r="Q71" s="32">
         <v>801.08</v>
       </c>
-      <c r="R71" s="31"/>
-      <c r="S71" s="31"/>
-      <c r="T71" s="30">
+      <c r="R71" s="33"/>
+      <c r="S71" s="33"/>
+      <c r="T71" s="32">
         <v>473.85</v>
       </c>
-      <c r="U71" s="31"/>
-      <c r="V71" s="32">
+      <c r="U71" s="33"/>
+      <c r="V71" s="34">
         <v>16.23</v>
       </c>
-      <c r="W71" s="32">
+      <c r="W71" s="34">
         <v>20.02</v>
       </c>
-      <c r="X71" s="32">
+      <c r="X71" s="34">
         <v>6.76</v>
       </c>
-      <c r="Y71" s="32">
+      <c r="Y71" s="34">
         <v>12.76</v>
       </c>
-      <c r="Z71" s="31"/>
-      <c r="AA71" s="31"/>
-      <c r="AB71" s="32">
+      <c r="Z71" s="33"/>
+      <c r="AA71" s="33"/>
+      <c r="AB71" s="34">
         <v>11.59</v>
       </c>
-      <c r="AC71" s="32">
+      <c r="AC71" s="34">
         <v>8.45</v>
       </c>
-      <c r="AD71" s="30">
+      <c r="AD71" s="32">
         <v>2758.27</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="29" t="s">
+      <c r="A72" s="31" t="s">
         <v>428</v>
       </c>
-      <c r="B72" s="31"/>
-      <c r="C72" s="32">
+      <c r="B72" s="33"/>
+      <c r="C72" s="34">
         <v>57.78</v>
       </c>
-      <c r="D72" s="32">
+      <c r="D72" s="34">
         <v>31.65</v>
       </c>
-      <c r="E72" s="32">
+      <c r="E72" s="34">
         <v>15.04</v>
       </c>
-      <c r="F72" s="32">
+      <c r="F72" s="34">
         <v>15.93</v>
       </c>
-      <c r="G72" s="32">
+      <c r="G72" s="34">
         <v>15.57</v>
       </c>
-      <c r="H72" s="32">
+      <c r="H72" s="34">
         <v>20.91</v>
       </c>
-      <c r="I72" s="32">
+      <c r="I72" s="34">
         <v>29.65</v>
       </c>
-      <c r="J72" s="32">
+      <c r="J72" s="34">
         <v>41.99</v>
       </c>
-      <c r="K72" s="32">
+      <c r="K72" s="34">
         <v>26.13</v>
       </c>
-      <c r="L72" s="32">
+      <c r="L72" s="34">
         <v>34.62</v>
       </c>
-      <c r="M72" s="32">
+      <c r="M72" s="34">
         <v>49.98</v>
       </c>
-      <c r="N72" s="31"/>
-      <c r="O72" s="31"/>
-      <c r="P72" s="31"/>
-      <c r="Q72" s="31"/>
-      <c r="R72" s="31"/>
-      <c r="S72" s="31"/>
-      <c r="T72" s="32">
+      <c r="N72" s="33"/>
+      <c r="O72" s="33"/>
+      <c r="P72" s="33"/>
+      <c r="Q72" s="33"/>
+      <c r="R72" s="33"/>
+      <c r="S72" s="33"/>
+      <c r="T72" s="34">
         <v>33.19</v>
       </c>
-      <c r="U72" s="32">
+      <c r="U72" s="34">
         <v>23.15</v>
       </c>
-      <c r="V72" s="32">
+      <c r="V72" s="34">
         <v>15.19</v>
       </c>
-      <c r="W72" s="32">
+      <c r="W72" s="34">
         <v>26.63</v>
       </c>
-      <c r="X72" s="32">
+      <c r="X72" s="34">
         <v>21.86</v>
       </c>
-      <c r="Y72" s="32">
+      <c r="Y72" s="34">
         <v>32.41</v>
       </c>
-      <c r="Z72" s="32">
+      <c r="Z72" s="34">
         <v>59.06</v>
       </c>
-      <c r="AA72" s="31"/>
-      <c r="AB72" s="31"/>
-      <c r="AC72" s="31"/>
-      <c r="AD72" s="31"/>
+      <c r="AA72" s="33"/>
+      <c r="AB72" s="33"/>
+      <c r="AC72" s="33"/>
+      <c r="AD72" s="33"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>

--- a/data/cox_xlsx/HHDC.CO.xlsx
+++ b/data/cox_xlsx/HHDC.CO.xlsx
@@ -1317,7 +1317,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="[&gt;=100]#,###0.0\%;[&lt;=-100]-#,###0.0\%;#,###0.0\%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -1373,6 +1373,11 @@
       <sz val="10.0"/>
       <color rgb="FFF5475B"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1437,7 +1442,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1525,6 +1530,7 @@
     <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -12384,7 +12390,10 @@
       <c r="G44" s="15">
         <v>2165.45</v>
       </c>
-      <c r="H44" s="18"/>
+      <c r="H44" s="18">
+        <f>H45+H48+H51+H54</f>
+        <v>2052.95</v>
+      </c>
       <c r="I44" s="15">
         <v>1889.43</v>
       </c>
@@ -12416,9 +12425,18 @@
         <v>1495.31</v>
       </c>
       <c r="S44" s="18"/>
-      <c r="T44" s="18"/>
-      <c r="U44" s="18"/>
-      <c r="V44" s="18"/>
+      <c r="T44" s="18">
+        <f t="shared" ref="T44:V44" si="1">T45+T48+T52+T54</f>
+        <v>1372.82</v>
+      </c>
+      <c r="U44" s="18">
+        <f t="shared" si="1"/>
+        <v>1285.1</v>
+      </c>
+      <c r="V44" s="18">
+        <f t="shared" si="1"/>
+        <v>1056.56</v>
+      </c>
       <c r="W44" s="18"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
@@ -12597,6 +12615,9 @@
         <v>-67.38</v>
       </c>
       <c r="W47" s="18"/>
+      <c r="X47" s="29"/>
+      <c r="Y47" s="29"/>
+      <c r="Z47" s="29"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
@@ -22564,3566 +22585,3566 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
-      <c r="AC20" s="30"/>
-      <c r="AD20" s="30"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="31"/>
+      <c r="AC20" s="31"/>
+      <c r="AD20" s="31"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="32" t="s">
         <v>378</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="33">
         <v>3826.84</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="33">
         <v>3258.04</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="33">
         <v>3658.67</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="33">
         <v>3361.3</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="33">
         <v>6188.69</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <v>3766.04</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="33">
         <v>3542.36</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="33">
         <v>2963.41</v>
       </c>
-      <c r="J21" s="32">
+      <c r="J21" s="33">
         <v>2677.04</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="33">
         <v>1468.78</v>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="33">
         <v>1773.2</v>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="33">
         <v>1048.49</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="33">
         <v>1117.44</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="33">
         <v>781.31</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="33">
         <v>1086.97</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="33">
         <v>1184.74</v>
       </c>
-      <c r="R21" s="32">
+      <c r="R21" s="33">
         <v>691.25</v>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="33">
         <v>323.67</v>
       </c>
-      <c r="T21" s="32">
+      <c r="T21" s="33">
         <v>1738.33</v>
       </c>
-      <c r="U21" s="32">
+      <c r="U21" s="33">
         <v>2257.88</v>
       </c>
-      <c r="V21" s="32">
+      <c r="V21" s="33">
         <v>1467.4</v>
       </c>
-      <c r="W21" s="32">
+      <c r="W21" s="33">
         <v>1108.48</v>
       </c>
-      <c r="X21" s="32">
+      <c r="X21" s="33">
         <v>1343.85</v>
       </c>
-      <c r="Y21" s="32">
+      <c r="Y21" s="33">
         <v>764.97</v>
       </c>
-      <c r="Z21" s="32">
+      <c r="Z21" s="33">
         <v>743.6</v>
       </c>
-      <c r="AA21" s="32">
+      <c r="AA21" s="33">
         <v>1262.41</v>
       </c>
-      <c r="AB21" s="32">
+      <c r="AB21" s="33">
         <v>1164.89</v>
       </c>
-      <c r="AC21" s="32">
+      <c r="AC21" s="33">
         <v>915.47</v>
       </c>
-      <c r="AD21" s="32">
+      <c r="AD21" s="33">
         <v>911.45</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="32" t="s">
         <v>379</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="33">
         <v>4398.17</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <v>4468.27</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="33">
         <v>4435.96</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="33">
         <v>4111.19</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <v>3828.45</v>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="33">
         <v>3047.27</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="33">
         <v>2510.22</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="33">
         <v>2043.46</v>
       </c>
-      <c r="J22" s="32">
+      <c r="J22" s="33">
         <v>1710.84</v>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="33">
         <v>1280.56</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="33">
         <v>1306.92</v>
       </c>
-      <c r="M22" s="32">
+      <c r="M22" s="33">
         <v>1173.94</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="33">
         <v>1026.58</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="33">
         <v>755.98</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="33">
         <v>974.07</v>
       </c>
-      <c r="Q22" s="32">
+      <c r="Q22" s="33">
         <v>1187.6</v>
       </c>
-      <c r="R22" s="32">
+      <c r="R22" s="33">
         <v>1319.54</v>
       </c>
-      <c r="S22" s="32">
+      <c r="S22" s="33">
         <v>1643.47</v>
       </c>
-      <c r="T22" s="32">
+      <c r="T22" s="33">
         <v>1541.24</v>
       </c>
-      <c r="U22" s="32">
+      <c r="U22" s="33">
         <v>1410.36</v>
       </c>
-      <c r="V22" s="32">
+      <c r="V22" s="33">
         <v>1078.88</v>
       </c>
-      <c r="W22" s="32">
+      <c r="W22" s="33">
         <v>1065.41</v>
       </c>
-      <c r="X22" s="32">
+      <c r="X22" s="33">
         <v>1099.74</v>
       </c>
-      <c r="Y22" s="32">
+      <c r="Y22" s="33">
         <v>872.99</v>
       </c>
-      <c r="Z22" s="32">
+      <c r="Z22" s="33">
         <v>969.17</v>
       </c>
-      <c r="AA22" s="33"/>
-      <c r="AB22" s="33"/>
-      <c r="AC22" s="33"/>
-      <c r="AD22" s="33"/>
+      <c r="AA22" s="34"/>
+      <c r="AB22" s="34"/>
+      <c r="AC22" s="34"/>
+      <c r="AD22" s="34"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="30" t="s">
         <v>380</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="30"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="31"/>
+      <c r="AB23" s="31"/>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="31"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="33">
         <v>2430.03</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="33">
         <v>2049.23</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="33">
         <v>2198.62</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="33">
         <v>2532.08</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="33">
         <v>5569.31</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="33">
         <v>3342.24</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="33">
         <v>2957.31</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="33">
         <v>2266.81</v>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="33">
         <v>2069.64</v>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="33">
         <v>996.08</v>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="33">
         <v>1200.63</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="33">
         <v>420.41</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="33">
         <v>523.14</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="33">
         <v>251.08</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <v>432.86</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="33">
         <v>543.41</v>
       </c>
-      <c r="R24" s="32">
+      <c r="R24" s="33">
         <v>710.87</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="33">
         <v>332.7</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="33">
         <v>1333.18</v>
       </c>
-      <c r="U24" s="32">
+      <c r="U24" s="33">
         <v>1868.21</v>
       </c>
-      <c r="V24" s="32">
+      <c r="V24" s="33">
         <v>1334.93</v>
       </c>
-      <c r="W24" s="32">
+      <c r="W24" s="33">
         <v>1198.07</v>
       </c>
-      <c r="X24" s="32">
+      <c r="X24" s="33">
         <v>1316.4</v>
       </c>
-      <c r="Y24" s="32">
+      <c r="Y24" s="33">
         <v>604.05</v>
       </c>
-      <c r="Z24" s="32">
+      <c r="Z24" s="33">
         <v>630.51</v>
       </c>
-      <c r="AA24" s="32">
+      <c r="AA24" s="33">
         <v>997.29</v>
       </c>
-      <c r="AB24" s="32">
+      <c r="AB24" s="33">
         <v>658.53</v>
       </c>
-      <c r="AC24" s="32">
+      <c r="AC24" s="33">
         <v>440.62</v>
       </c>
-      <c r="AD24" s="32">
+      <c r="AD24" s="33">
         <v>450.78</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="32" t="s">
         <v>381</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="33">
         <v>3237.06</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <v>3493.64</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="33">
         <v>3605.85</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="33">
         <v>3457.4</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="33">
         <v>3238.91</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="33">
         <v>2451.48</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="33">
         <v>1914.67</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="33">
         <v>1424.3</v>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="33">
         <v>1091.81</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="33">
         <v>688.94</v>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="33">
         <v>622.24</v>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="33">
         <v>486.87</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="33">
         <v>513.49</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="33">
         <v>410.21</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="33">
         <v>641.38</v>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="33">
         <v>911.06</v>
       </c>
-      <c r="R25" s="32">
+      <c r="R25" s="33">
         <v>1133.79</v>
       </c>
-      <c r="S25" s="32">
+      <c r="S25" s="33">
         <v>1442.59</v>
       </c>
-      <c r="T25" s="32">
+      <c r="T25" s="33">
         <v>1370.77</v>
       </c>
-      <c r="U25" s="32">
+      <c r="U25" s="33">
         <v>1281.35</v>
       </c>
-      <c r="V25" s="32">
+      <c r="V25" s="33">
         <v>1006.72</v>
       </c>
-      <c r="W25" s="32">
+      <c r="W25" s="33">
         <v>965.1</v>
       </c>
-      <c r="X25" s="32">
+      <c r="X25" s="33">
         <v>874.35</v>
       </c>
-      <c r="Y25" s="32">
+      <c r="Y25" s="33">
         <v>603.81</v>
       </c>
-      <c r="Z25" s="32">
+      <c r="Z25" s="33">
         <v>618.15</v>
       </c>
-      <c r="AA25" s="33"/>
-      <c r="AB25" s="33"/>
-      <c r="AC25" s="33"/>
-      <c r="AD25" s="33"/>
+      <c r="AA25" s="34"/>
+      <c r="AB25" s="34"/>
+      <c r="AC25" s="34"/>
+      <c r="AD25" s="34"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="30" t="s">
         <v>382</v>
       </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="31"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="32" t="s">
         <v>383</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="33">
         <v>147.27</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>124.2</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>133.25</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>144.69</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="33">
         <v>309.69</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="33">
         <v>185.85</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="33">
         <v>164.45</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="33">
         <v>126.05</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="33">
         <v>160.62</v>
       </c>
-      <c r="K27" s="34">
+      <c r="K27" s="35">
         <v>77.3</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="35">
         <v>93.18</v>
       </c>
-      <c r="M27" s="34">
+      <c r="M27" s="35">
         <v>35.89</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="35">
         <v>44.66</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="35">
         <v>21.43</v>
       </c>
-      <c r="P27" s="34">
+      <c r="P27" s="35">
         <v>36.95</v>
       </c>
-      <c r="Q27" s="34">
+      <c r="Q27" s="35">
         <v>46.39</v>
       </c>
-      <c r="R27" s="34">
+      <c r="R27" s="35">
         <v>60.68</v>
       </c>
-      <c r="S27" s="32">
+      <c r="S27" s="33">
         <v>118.36</v>
       </c>
-      <c r="T27" s="32">
+      <c r="T27" s="33">
         <v>438.2</v>
       </c>
-      <c r="U27" s="32">
+      <c r="U27" s="33">
         <v>614.06</v>
       </c>
-      <c r="V27" s="32">
+      <c r="V27" s="33">
         <v>438.78</v>
       </c>
-      <c r="W27" s="32">
+      <c r="W27" s="33">
         <v>393.79</v>
       </c>
-      <c r="X27" s="32">
+      <c r="X27" s="33">
         <v>432.68</v>
       </c>
-      <c r="Y27" s="32">
+      <c r="Y27" s="33">
         <v>198.55</v>
       </c>
-      <c r="Z27" s="32">
+      <c r="Z27" s="33">
         <v>207.24</v>
       </c>
-      <c r="AA27" s="32">
+      <c r="AA27" s="33">
         <v>301.56</v>
       </c>
-      <c r="AB27" s="32">
+      <c r="AB27" s="33">
         <v>186.92</v>
       </c>
-      <c r="AC27" s="32">
+      <c r="AC27" s="33">
         <v>126.42</v>
       </c>
-      <c r="AD27" s="32">
+      <c r="AD27" s="33">
         <v>130.19</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="32" t="s">
         <v>384</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="33">
         <v>187.68</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>199.5</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>203.54</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="33">
         <v>193.03</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <v>189.38</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="33">
         <v>151.06</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="33">
         <v>125.68</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="33">
         <v>101.28</v>
       </c>
-      <c r="J28" s="34">
+      <c r="J28" s="35">
         <v>86.4</v>
       </c>
-      <c r="K28" s="34">
+      <c r="K28" s="35">
         <v>55.5</v>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="35">
         <v>51.25</v>
       </c>
-      <c r="M28" s="34">
+      <c r="M28" s="35">
         <v>41.56</v>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="35">
         <v>43.83</v>
       </c>
-      <c r="O28" s="34">
+      <c r="O28" s="35">
         <v>48.59</v>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="33">
         <v>132.56</v>
       </c>
-      <c r="Q28" s="32">
+      <c r="Q28" s="33">
         <v>242.02</v>
       </c>
-      <c r="R28" s="32">
+      <c r="R28" s="33">
         <v>339.61</v>
       </c>
-      <c r="S28" s="32">
+      <c r="S28" s="33">
         <v>475.96</v>
       </c>
-      <c r="T28" s="32">
+      <c r="T28" s="33">
         <v>450.56</v>
       </c>
-      <c r="U28" s="32">
+      <c r="U28" s="33">
         <v>421.16</v>
       </c>
-      <c r="V28" s="32">
+      <c r="V28" s="33">
         <v>330.9</v>
       </c>
-      <c r="W28" s="32">
+      <c r="W28" s="33">
         <v>311.97</v>
       </c>
-      <c r="X28" s="32">
+      <c r="X28" s="33">
         <v>275.92</v>
       </c>
-      <c r="Y28" s="32">
+      <c r="Y28" s="33">
         <v>185.47</v>
       </c>
-      <c r="Z28" s="32">
+      <c r="Z28" s="33">
         <v>185.38</v>
       </c>
-      <c r="AA28" s="33"/>
-      <c r="AB28" s="33"/>
-      <c r="AC28" s="33"/>
-      <c r="AD28" s="33"/>
+      <c r="AA28" s="34"/>
+      <c r="AB28" s="34"/>
+      <c r="AC28" s="34"/>
+      <c r="AD28" s="34"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="30" t="s">
         <v>385</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="31"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="32" t="s">
         <v>386</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="36">
         <v>-3.68</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="37">
         <v>1.63</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="36">
         <v>-25.8</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="37">
         <v>2.76</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="37">
         <v>6.31</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="37">
         <v>12.32</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="37">
         <v>10.88</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="37">
         <v>9.33</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="36">
         <v>-1.71</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="37">
         <v>7.37</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="37">
         <v>5.62</v>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="37">
         <v>13.65</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="37">
         <v>4.78</v>
       </c>
-      <c r="O30" s="36">
+      <c r="O30" s="37">
         <v>7.76</v>
       </c>
-      <c r="P30" s="36">
+      <c r="P30" s="37">
         <v>1.46</v>
       </c>
-      <c r="Q30" s="36">
+      <c r="Q30" s="37">
         <v>0.27</v>
       </c>
-      <c r="R30" s="35">
+      <c r="R30" s="36">
         <v>-63.92</v>
       </c>
-      <c r="S30" s="35">
+      <c r="S30" s="36">
         <v>-115.28</v>
       </c>
-      <c r="T30" s="36">
+      <c r="T30" s="37">
         <v>0.22</v>
       </c>
-      <c r="U30" s="35">
+      <c r="U30" s="36">
         <v>-4.55</v>
       </c>
-      <c r="V30" s="36">
+      <c r="V30" s="37">
         <v>5.43</v>
       </c>
-      <c r="W30" s="36">
+      <c r="W30" s="37">
         <v>3.73</v>
       </c>
-      <c r="X30" s="36">
+      <c r="X30" s="37">
         <v>11.98</v>
       </c>
-      <c r="Y30" s="36">
+      <c r="Y30" s="37">
         <v>7.87</v>
       </c>
-      <c r="Z30" s="35">
+      <c r="Z30" s="36">
         <v>-5.42</v>
       </c>
-      <c r="AA30" s="35">
+      <c r="AA30" s="36">
         <v>-5.82</v>
       </c>
-      <c r="AB30" s="36">
+      <c r="AB30" s="37">
         <v>12.51</v>
       </c>
-      <c r="AC30" s="36">
+      <c r="AC30" s="37">
         <v>20.09</v>
       </c>
-      <c r="AD30" s="36">
+      <c r="AD30" s="37">
         <v>0.07</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="32" t="s">
         <v>387</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="36">
         <v>-1.3</v>
       </c>
-      <c r="C31" s="36">
+      <c r="C31" s="37">
         <v>1.9</v>
       </c>
-      <c r="D31" s="36">
+      <c r="D31" s="37">
         <v>3.58</v>
       </c>
-      <c r="E31" s="36">
+      <c r="E31" s="37">
         <v>8.19</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="37">
         <v>7.27</v>
       </c>
-      <c r="G31" s="36">
+      <c r="G31" s="37">
         <v>7.7</v>
       </c>
-      <c r="H31" s="36">
+      <c r="H31" s="37">
         <v>6.1</v>
       </c>
-      <c r="I31" s="36">
+      <c r="I31" s="37">
         <v>5.12</v>
       </c>
-      <c r="J31" s="36">
+      <c r="J31" s="37">
         <v>3.86</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="37">
         <v>7.21</v>
       </c>
-      <c r="L31" s="36">
+      <c r="L31" s="37">
         <v>6.14</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="37">
         <v>4.83</v>
       </c>
-      <c r="N31" s="35">
+      <c r="N31" s="36">
         <v>-15.59</v>
       </c>
-      <c r="O31" s="35">
+      <c r="O31" s="36">
         <v>-55.53</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="36">
         <v>-21.64</v>
       </c>
-      <c r="Q31" s="35">
+      <c r="Q31" s="36">
         <v>-14.13</v>
       </c>
-      <c r="R31" s="35">
+      <c r="R31" s="36">
         <v>-9.29</v>
       </c>
-      <c r="S31" s="35">
+      <c r="S31" s="36">
         <v>-5.12</v>
       </c>
-      <c r="T31" s="36">
+      <c r="T31" s="37">
         <v>2.7</v>
       </c>
-      <c r="U31" s="36">
+      <c r="U31" s="37">
         <v>3.78</v>
       </c>
-      <c r="V31" s="36">
+      <c r="V31" s="37">
         <v>5.63</v>
       </c>
-      <c r="W31" s="36">
+      <c r="W31" s="37">
         <v>3.47</v>
       </c>
-      <c r="X31" s="36">
+      <c r="X31" s="37">
         <v>4.67</v>
       </c>
-      <c r="Y31" s="36">
+      <c r="Y31" s="37">
         <v>3.43</v>
       </c>
-      <c r="Z31" s="36">
+      <c r="Z31" s="37">
         <v>1.92</v>
       </c>
-      <c r="AA31" s="36"/>
-      <c r="AB31" s="36"/>
-      <c r="AC31" s="36"/>
-      <c r="AD31" s="36"/>
+      <c r="AA31" s="37"/>
+      <c r="AB31" s="37"/>
+      <c r="AC31" s="37"/>
+      <c r="AD31" s="37"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="30" t="s">
         <v>388</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
-      <c r="AC32" s="30"/>
-      <c r="AD32" s="30"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="31"/>
+      <c r="AB32" s="31"/>
+      <c r="AC32" s="31"/>
+      <c r="AD32" s="31"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="32" t="s">
         <v>389</v>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="37">
         <v>0.0</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="37">
         <v>0.0</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="37">
         <v>0.0</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="37">
         <v>0.0</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="37">
         <v>0.0</v>
       </c>
-      <c r="G33" s="36">
+      <c r="G33" s="37">
         <v>0.0</v>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="37">
         <v>0.0</v>
       </c>
-      <c r="I33" s="36">
+      <c r="I33" s="37">
         <v>0.0</v>
       </c>
-      <c r="J33" s="36">
+      <c r="J33" s="37">
         <v>0.0</v>
       </c>
-      <c r="K33" s="36">
+      <c r="K33" s="37">
         <v>0.0</v>
       </c>
-      <c r="L33" s="36">
+      <c r="L33" s="37">
         <v>0.0</v>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="37">
         <v>0.0</v>
       </c>
-      <c r="N33" s="36">
+      <c r="N33" s="37">
         <v>0.0</v>
       </c>
-      <c r="O33" s="36">
+      <c r="O33" s="37">
         <v>0.0</v>
       </c>
-      <c r="P33" s="36">
+      <c r="P33" s="37">
         <v>0.0</v>
       </c>
-      <c r="Q33" s="36">
+      <c r="Q33" s="37">
         <v>0.0</v>
       </c>
-      <c r="R33" s="36">
+      <c r="R33" s="37">
         <v>0.0</v>
       </c>
-      <c r="S33" s="36">
+      <c r="S33" s="37">
         <v>7.2</v>
       </c>
-      <c r="T33" s="36">
+      <c r="T33" s="37">
         <v>1.06</v>
       </c>
-      <c r="U33" s="36">
+      <c r="U33" s="37">
         <v>1.37</v>
       </c>
-      <c r="V33" s="36">
+      <c r="V33" s="37">
         <v>1.86</v>
       </c>
-      <c r="W33" s="36">
+      <c r="W33" s="37">
         <v>1.84</v>
       </c>
-      <c r="X33" s="36">
+      <c r="X33" s="37">
         <v>1.42</v>
       </c>
-      <c r="Y33" s="36">
+      <c r="Y33" s="37">
         <v>2.69</v>
       </c>
-      <c r="Z33" s="36">
+      <c r="Z33" s="37">
         <v>2.82</v>
       </c>
-      <c r="AA33" s="36">
+      <c r="AA33" s="37">
         <v>1.67</v>
       </c>
-      <c r="AB33" s="36">
+      <c r="AB33" s="37">
         <v>1.71</v>
       </c>
-      <c r="AC33" s="36">
+      <c r="AC33" s="37">
         <v>2.57</v>
       </c>
-      <c r="AD33" s="36">
+      <c r="AD33" s="37">
         <v>2.06</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="32" t="s">
         <v>390</v>
       </c>
-      <c r="B34" s="36">
+      <c r="B34" s="37">
         <v>0.0</v>
       </c>
-      <c r="C34" s="36">
+      <c r="C34" s="37">
         <v>0.0</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="37">
         <v>0.0</v>
       </c>
-      <c r="E34" s="36">
+      <c r="E34" s="37">
         <v>0.0</v>
       </c>
-      <c r="F34" s="36">
+      <c r="F34" s="37">
         <v>0.0</v>
       </c>
-      <c r="G34" s="36">
+      <c r="G34" s="37">
         <v>0.0</v>
       </c>
-      <c r="H34" s="36">
+      <c r="H34" s="37">
         <v>0.0</v>
       </c>
-      <c r="I34" s="36">
+      <c r="I34" s="37">
         <v>0.0</v>
       </c>
-      <c r="J34" s="36">
+      <c r="J34" s="37">
         <v>0.0</v>
       </c>
-      <c r="K34" s="36">
+      <c r="K34" s="37">
         <v>0.0</v>
       </c>
-      <c r="L34" s="36">
+      <c r="L34" s="37">
         <v>0.0</v>
       </c>
-      <c r="M34" s="36">
+      <c r="M34" s="37">
         <v>0.0</v>
       </c>
-      <c r="N34" s="36">
+      <c r="N34" s="37">
         <v>0.0</v>
       </c>
-      <c r="O34" s="36">
+      <c r="O34" s="37">
         <v>2.65</v>
       </c>
-      <c r="P34" s="36">
+      <c r="P34" s="37">
         <v>1.71</v>
       </c>
-      <c r="Q34" s="36">
+      <c r="Q34" s="37">
         <v>1.6</v>
       </c>
-      <c r="R34" s="36">
+      <c r="R34" s="37">
         <v>1.72</v>
       </c>
-      <c r="S34" s="36">
+      <c r="S34" s="37">
         <v>1.79</v>
       </c>
-      <c r="T34" s="36">
+      <c r="T34" s="37">
         <v>1.49</v>
       </c>
-      <c r="U34" s="36">
+      <c r="U34" s="37">
         <v>1.71</v>
       </c>
-      <c r="V34" s="36">
+      <c r="V34" s="37">
         <v>1.97</v>
       </c>
-      <c r="W34" s="36">
+      <c r="W34" s="37">
         <v>1.95</v>
       </c>
-      <c r="X34" s="36">
+      <c r="X34" s="37">
         <v>1.94</v>
       </c>
-      <c r="Y34" s="36">
+      <c r="Y34" s="37">
         <v>2.23</v>
       </c>
-      <c r="Z34" s="36">
+      <c r="Z34" s="37">
         <v>2.1</v>
       </c>
-      <c r="AA34" s="36"/>
-      <c r="AB34" s="36"/>
-      <c r="AC34" s="36"/>
-      <c r="AD34" s="36"/>
+      <c r="AA34" s="37"/>
+      <c r="AB34" s="37"/>
+      <c r="AC34" s="37"/>
+      <c r="AD34" s="37"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="32" t="s">
         <v>391</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="37">
         <v>0.0</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="37">
         <v>0.0</v>
       </c>
-      <c r="D35" s="36">
+      <c r="D35" s="37">
         <v>0.0</v>
       </c>
-      <c r="E35" s="36">
+      <c r="E35" s="37">
         <v>0.0</v>
       </c>
-      <c r="F35" s="36">
+      <c r="F35" s="37">
         <v>0.0</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <v>0.0</v>
       </c>
-      <c r="H35" s="36">
+      <c r="H35" s="37">
         <v>0.0</v>
       </c>
-      <c r="I35" s="36">
+      <c r="I35" s="37">
         <v>0.0</v>
       </c>
-      <c r="J35" s="36">
+      <c r="J35" s="37">
         <v>0.0</v>
       </c>
-      <c r="K35" s="36">
+      <c r="K35" s="37">
         <v>0.0</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <v>0.0</v>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="37">
         <v>0.0</v>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="37">
         <v>0.0</v>
       </c>
-      <c r="O35" s="36">
+      <c r="O35" s="37">
         <v>0.0</v>
       </c>
-      <c r="P35" s="36">
+      <c r="P35" s="37">
         <v>0.0</v>
       </c>
-      <c r="Q35" s="36">
+      <c r="Q35" s="37">
         <v>0.0</v>
       </c>
-      <c r="R35" s="36">
+      <c r="R35" s="37">
         <v>0.0</v>
       </c>
-      <c r="S35" s="36">
+      <c r="S35" s="37">
         <v>10.0</v>
       </c>
-      <c r="T35" s="36">
+      <c r="T35" s="37">
         <v>1.47</v>
       </c>
-      <c r="U35" s="36">
+      <c r="U35" s="37">
         <v>1.9</v>
       </c>
-      <c r="V35" s="36">
+      <c r="V35" s="37">
         <v>2.58</v>
       </c>
-      <c r="W35" s="36">
+      <c r="W35" s="37">
         <v>2.55</v>
       </c>
-      <c r="X35" s="36">
+      <c r="X35" s="37">
         <v>1.97</v>
       </c>
-      <c r="Y35" s="36">
+      <c r="Y35" s="37">
         <v>3.73</v>
       </c>
-      <c r="Z35" s="36">
+      <c r="Z35" s="37">
         <v>3.91</v>
       </c>
-      <c r="AA35" s="36">
+      <c r="AA35" s="37">
         <v>2.22</v>
       </c>
-      <c r="AB35" s="36">
+      <c r="AB35" s="37">
         <v>2.28</v>
       </c>
-      <c r="AC35" s="36">
+      <c r="AC35" s="37">
         <v>3.43</v>
       </c>
-      <c r="AD35" s="36">
+      <c r="AD35" s="37">
         <v>2.75</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="32" t="s">
         <v>392</v>
       </c>
-      <c r="B36" s="36">
+      <c r="B36" s="37">
         <v>0.0</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="37">
         <v>0.0</v>
       </c>
-      <c r="D36" s="36">
+      <c r="D36" s="37">
         <v>0.0</v>
       </c>
-      <c r="E36" s="36">
+      <c r="E36" s="37">
         <v>0.0</v>
       </c>
-      <c r="F36" s="36">
+      <c r="F36" s="37">
         <v>0.0</v>
       </c>
-      <c r="G36" s="36">
+      <c r="G36" s="37">
         <v>0.0</v>
       </c>
-      <c r="H36" s="36">
+      <c r="H36" s="37">
         <v>0.0</v>
       </c>
-      <c r="I36" s="36">
+      <c r="I36" s="37">
         <v>0.0</v>
       </c>
-      <c r="J36" s="36">
+      <c r="J36" s="37">
         <v>0.0</v>
       </c>
-      <c r="K36" s="36">
+      <c r="K36" s="37">
         <v>0.0</v>
       </c>
-      <c r="L36" s="36">
+      <c r="L36" s="37">
         <v>0.0</v>
       </c>
-      <c r="M36" s="36">
+      <c r="M36" s="37">
         <v>0.0</v>
       </c>
-      <c r="N36" s="36">
+      <c r="N36" s="37">
         <v>0.0</v>
       </c>
-      <c r="O36" s="36">
+      <c r="O36" s="37">
         <v>3.68</v>
       </c>
-      <c r="P36" s="36">
+      <c r="P36" s="37">
         <v>2.37</v>
       </c>
-      <c r="Q36" s="36">
+      <c r="Q36" s="37">
         <v>2.22</v>
       </c>
-      <c r="R36" s="36">
+      <c r="R36" s="37">
         <v>2.38</v>
       </c>
-      <c r="S36" s="36">
+      <c r="S36" s="37">
         <v>2.49</v>
       </c>
-      <c r="T36" s="36">
+      <c r="T36" s="37">
         <v>2.07</v>
       </c>
-      <c r="U36" s="36">
+      <c r="U36" s="37">
         <v>2.38</v>
       </c>
-      <c r="V36" s="36">
+      <c r="V36" s="37">
         <v>2.74</v>
       </c>
-      <c r="W36" s="36">
+      <c r="W36" s="37">
         <v>2.69</v>
       </c>
-      <c r="X36" s="36">
+      <c r="X36" s="37">
         <v>2.67</v>
       </c>
-      <c r="Y36" s="36">
+      <c r="Y36" s="37">
         <v>3.04</v>
       </c>
-      <c r="Z36" s="36">
+      <c r="Z36" s="37">
         <v>2.83</v>
       </c>
-      <c r="AA36" s="36"/>
-      <c r="AB36" s="36"/>
-      <c r="AC36" s="36"/>
-      <c r="AD36" s="36"/>
+      <c r="AA36" s="37"/>
+      <c r="AB36" s="37"/>
+      <c r="AC36" s="37"/>
+      <c r="AD36" s="37"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="30" t="s">
         <v>393</v>
       </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
-      <c r="AD37" s="30"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="31"/>
+      <c r="Y37" s="31"/>
+      <c r="Z37" s="31"/>
+      <c r="AA37" s="31"/>
+      <c r="AB37" s="31"/>
+      <c r="AC37" s="31"/>
+      <c r="AD37" s="31"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="32" t="s">
         <v>394</v>
       </c>
-      <c r="B38" s="34">
+      <c r="B38" s="35">
         <v>1.65</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="35">
         <v>0.82</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="35">
         <v>0.91</v>
       </c>
-      <c r="E38" s="34">
+      <c r="E38" s="35">
         <v>0.91</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="35">
         <v>2.35</v>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="35">
         <v>1.64</v>
       </c>
-      <c r="H38" s="34">
+      <c r="H38" s="35">
         <v>1.67</v>
       </c>
-      <c r="I38" s="34">
+      <c r="I38" s="35">
         <v>1.7</v>
       </c>
-      <c r="J38" s="34">
+      <c r="J38" s="35">
         <v>4.15</v>
       </c>
-      <c r="K38" s="34">
+      <c r="K38" s="35">
         <v>2.92</v>
       </c>
-      <c r="L38" s="34">
+      <c r="L38" s="35">
         <v>3.65</v>
       </c>
-      <c r="M38" s="34">
+      <c r="M38" s="35">
         <v>2.28</v>
       </c>
-      <c r="N38" s="34">
+      <c r="N38" s="35">
         <v>1.59</v>
       </c>
-      <c r="O38" s="34">
+      <c r="O38" s="35">
         <v>0.61</v>
       </c>
-      <c r="P38" s="34">
+      <c r="P38" s="35">
         <v>0.88</v>
       </c>
-      <c r="Q38" s="34">
+      <c r="Q38" s="35">
         <v>0.77</v>
       </c>
-      <c r="R38" s="34">
+      <c r="R38" s="35">
         <v>0.66</v>
       </c>
-      <c r="S38" s="34">
+      <c r="S38" s="35">
         <v>0.43</v>
       </c>
-      <c r="T38" s="34">
+      <c r="T38" s="35">
         <v>2.16</v>
       </c>
-      <c r="U38" s="34">
+      <c r="U38" s="35">
         <v>3.33</v>
       </c>
-      <c r="V38" s="34">
+      <c r="V38" s="35">
         <v>2.59</v>
       </c>
-      <c r="W38" s="34">
+      <c r="W38" s="35">
         <v>2.5</v>
       </c>
-      <c r="X38" s="34">
+      <c r="X38" s="35">
         <v>3.01</v>
       </c>
-      <c r="Y38" s="34">
+      <c r="Y38" s="35">
         <v>1.76</v>
       </c>
-      <c r="Z38" s="34">
+      <c r="Z38" s="35">
         <v>1.7</v>
       </c>
-      <c r="AA38" s="34">
+      <c r="AA38" s="35">
         <v>3.55</v>
       </c>
-      <c r="AB38" s="34">
+      <c r="AB38" s="35">
         <v>2.81</v>
       </c>
-      <c r="AC38" s="34">
+      <c r="AC38" s="35">
         <v>1.78</v>
       </c>
-      <c r="AD38" s="34">
+      <c r="AD38" s="35">
         <v>1.81</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="32" t="s">
         <v>395</v>
       </c>
-      <c r="B39" s="34">
+      <c r="B39" s="35">
         <v>1.29</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="35">
         <v>1.3</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="35">
         <v>1.46</v>
       </c>
-      <c r="E39" s="34">
+      <c r="E39" s="35">
         <v>1.62</v>
       </c>
-      <c r="F39" s="34">
+      <c r="F39" s="35">
         <v>2.08</v>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="35">
         <v>2.05</v>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="35">
         <v>2.37</v>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="35">
         <v>2.73</v>
       </c>
-      <c r="J39" s="34">
+      <c r="J39" s="35">
         <v>3.0</v>
       </c>
-      <c r="K39" s="34">
+      <c r="K39" s="35">
         <v>1.97</v>
       </c>
-      <c r="L39" s="34">
+      <c r="L39" s="35">
         <v>1.49</v>
       </c>
-      <c r="M39" s="34">
+      <c r="M39" s="35">
         <v>1.0</v>
       </c>
-      <c r="N39" s="34">
+      <c r="N39" s="35">
         <v>0.81</v>
       </c>
-      <c r="O39" s="34">
+      <c r="O39" s="35">
         <v>0.58</v>
       </c>
-      <c r="P39" s="34">
+      <c r="P39" s="35">
         <v>1.1</v>
       </c>
-      <c r="Q39" s="34">
+      <c r="Q39" s="35">
         <v>1.64</v>
       </c>
-      <c r="R39" s="34">
+      <c r="R39" s="35">
         <v>1.89</v>
       </c>
-      <c r="S39" s="34">
+      <c r="S39" s="35">
         <v>2.1</v>
       </c>
-      <c r="T39" s="34">
+      <c r="T39" s="35">
         <v>2.69</v>
       </c>
-      <c r="U39" s="34">
+      <c r="U39" s="35">
         <v>2.69</v>
       </c>
-      <c r="V39" s="34">
+      <c r="V39" s="35">
         <v>2.35</v>
       </c>
-      <c r="W39" s="34">
+      <c r="W39" s="35">
         <v>2.45</v>
       </c>
-      <c r="X39" s="34">
+      <c r="X39" s="35">
         <v>2.48</v>
       </c>
-      <c r="Y39" s="34">
+      <c r="Y39" s="35">
         <v>2.22</v>
       </c>
-      <c r="Z39" s="34">
+      <c r="Z39" s="35">
         <v>2.29</v>
       </c>
-      <c r="AA39" s="33"/>
-      <c r="AB39" s="33"/>
-      <c r="AC39" s="33"/>
-      <c r="AD39" s="33"/>
+      <c r="AA39" s="34"/>
+      <c r="AB39" s="34"/>
+      <c r="AC39" s="34"/>
+      <c r="AD39" s="34"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="30" t="s">
         <v>396</v>
       </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="30"/>
-      <c r="W40" s="30"/>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
-      <c r="AA40" s="30"/>
-      <c r="AB40" s="30"/>
-      <c r="AC40" s="30"/>
-      <c r="AD40" s="30"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="31"/>
+      <c r="AA40" s="31"/>
+      <c r="AB40" s="31"/>
+      <c r="AC40" s="31"/>
+      <c r="AD40" s="31"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="32" t="s">
         <v>397</v>
       </c>
-      <c r="B41" s="34">
+      <c r="B41" s="35">
         <v>3.05</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="35">
         <v>1.39</v>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="35">
         <v>1.56</v>
       </c>
-      <c r="E41" s="34">
+      <c r="E41" s="35">
         <v>1.43</v>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="35">
         <v>3.84</v>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="35">
         <v>2.44</v>
       </c>
-      <c r="H41" s="34">
+      <c r="H41" s="35">
         <v>2.49</v>
       </c>
-      <c r="I41" s="34">
+      <c r="I41" s="35">
         <v>2.9</v>
       </c>
-      <c r="J41" s="34">
+      <c r="J41" s="35">
         <v>4.88</v>
       </c>
-      <c r="K41" s="34">
+      <c r="K41" s="35">
         <v>3.64</v>
       </c>
-      <c r="L41" s="34">
+      <c r="L41" s="35">
         <v>4.65</v>
       </c>
-      <c r="M41" s="34">
+      <c r="M41" s="35">
         <v>3.59</v>
       </c>
-      <c r="N41" s="34">
+      <c r="N41" s="35">
         <v>2.02</v>
       </c>
-      <c r="O41" s="34">
+      <c r="O41" s="35">
         <v>0.73</v>
       </c>
-      <c r="P41" s="34">
+      <c r="P41" s="35">
         <v>1.1</v>
       </c>
-      <c r="Q41" s="34">
+      <c r="Q41" s="35">
         <v>0.94</v>
       </c>
-      <c r="R41" s="34">
+      <c r="R41" s="35">
         <v>0.66</v>
       </c>
-      <c r="S41" s="34">
+      <c r="S41" s="35">
         <v>0.44</v>
       </c>
-      <c r="T41" s="34">
+      <c r="T41" s="35">
         <v>1.53</v>
       </c>
-      <c r="U41" s="34">
+      <c r="U41" s="35">
         <v>2.39</v>
       </c>
-      <c r="V41" s="34">
+      <c r="V41" s="35">
         <v>1.81</v>
       </c>
-      <c r="W41" s="34">
+      <c r="W41" s="35">
         <v>1.65</v>
       </c>
-      <c r="X41" s="34">
+      <c r="X41" s="35">
         <v>2.0</v>
       </c>
-      <c r="Y41" s="34">
+      <c r="Y41" s="35">
         <v>1.18</v>
       </c>
-      <c r="Z41" s="34">
+      <c r="Z41" s="35">
         <v>1.25</v>
       </c>
-      <c r="AA41" s="34">
+      <c r="AA41" s="35">
         <v>2.65</v>
       </c>
-      <c r="AB41" s="34">
+      <c r="AB41" s="35">
         <v>2.12</v>
       </c>
-      <c r="AC41" s="34">
+      <c r="AC41" s="35">
         <v>1.34</v>
       </c>
-      <c r="AD41" s="34">
+      <c r="AD41" s="35">
         <v>1.36</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="32" t="s">
         <v>398</v>
       </c>
-      <c r="B42" s="34">
+      <c r="B42" s="35">
         <v>2.15</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="35">
         <v>2.11</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="35">
         <v>2.32</v>
       </c>
-      <c r="E42" s="34">
+      <c r="E42" s="35">
         <v>2.55</v>
       </c>
-      <c r="F42" s="34">
+      <c r="F42" s="35">
         <v>3.17</v>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="35">
         <v>2.99</v>
       </c>
-      <c r="H42" s="34">
+      <c r="H42" s="35">
         <v>3.39</v>
       </c>
-      <c r="I42" s="34">
+      <c r="I42" s="35">
         <v>3.86</v>
       </c>
-      <c r="J42" s="34">
+      <c r="J42" s="35">
         <v>3.81</v>
       </c>
-      <c r="K42" s="34">
+      <c r="K42" s="35">
         <v>2.5</v>
       </c>
-      <c r="L42" s="34">
+      <c r="L42" s="35">
         <v>1.89</v>
       </c>
-      <c r="M42" s="34">
+      <c r="M42" s="35">
         <v>1.25</v>
       </c>
-      <c r="N42" s="34">
+      <c r="N42" s="35">
         <v>0.93</v>
       </c>
-      <c r="O42" s="34">
+      <c r="O42" s="35">
         <v>0.62</v>
       </c>
-      <c r="P42" s="34">
+      <c r="P42" s="35">
         <v>1.0</v>
       </c>
-      <c r="Q42" s="34">
+      <c r="Q42" s="35">
         <v>1.38</v>
       </c>
-      <c r="R42" s="34">
+      <c r="R42" s="35">
         <v>1.5</v>
       </c>
-      <c r="S42" s="34">
+      <c r="S42" s="35">
         <v>1.59</v>
       </c>
-      <c r="T42" s="34">
+      <c r="T42" s="35">
         <v>1.86</v>
       </c>
-      <c r="U42" s="34">
+      <c r="U42" s="35">
         <v>1.84</v>
       </c>
-      <c r="V42" s="34">
+      <c r="V42" s="35">
         <v>1.61</v>
       </c>
-      <c r="W42" s="34">
+      <c r="W42" s="35">
         <v>1.68</v>
       </c>
-      <c r="X42" s="34">
+      <c r="X42" s="35">
         <v>1.74</v>
       </c>
-      <c r="Y42" s="34">
+      <c r="Y42" s="35">
         <v>1.6</v>
       </c>
-      <c r="Z42" s="34">
+      <c r="Z42" s="35">
         <v>1.71</v>
       </c>
-      <c r="AA42" s="33"/>
-      <c r="AB42" s="33"/>
-      <c r="AC42" s="33"/>
-      <c r="AD42" s="33"/>
+      <c r="AA42" s="34"/>
+      <c r="AB42" s="34"/>
+      <c r="AC42" s="34"/>
+      <c r="AD42" s="34"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="30" t="s">
         <v>399</v>
       </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="30"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
-      <c r="W43" s="30"/>
-      <c r="X43" s="30"/>
-      <c r="Y43" s="30"/>
-      <c r="Z43" s="30"/>
-      <c r="AA43" s="30"/>
-      <c r="AB43" s="30"/>
-      <c r="AC43" s="30"/>
-      <c r="AD43" s="30"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="31"/>
+      <c r="V43" s="31"/>
+      <c r="W43" s="31"/>
+      <c r="X43" s="31"/>
+      <c r="Y43" s="31"/>
+      <c r="Z43" s="31"/>
+      <c r="AA43" s="31"/>
+      <c r="AB43" s="31"/>
+      <c r="AC43" s="31"/>
+      <c r="AD43" s="31"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="32" t="s">
         <v>400</v>
       </c>
-      <c r="B44" s="34">
+      <c r="B44" s="35">
         <v>0.55</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="35">
         <v>0.47</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="35">
         <v>0.54</v>
       </c>
-      <c r="E44" s="34">
+      <c r="E44" s="35">
         <v>0.5</v>
       </c>
-      <c r="F44" s="34">
+      <c r="F44" s="35">
         <v>1.35</v>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="35">
         <v>0.89</v>
       </c>
-      <c r="H44" s="34">
+      <c r="H44" s="35">
         <v>0.79</v>
       </c>
-      <c r="I44" s="34">
+      <c r="I44" s="35">
         <v>0.54</v>
       </c>
-      <c r="J44" s="34">
+      <c r="J44" s="35">
         <v>0.96</v>
       </c>
-      <c r="K44" s="34">
+      <c r="K44" s="35">
         <v>0.5</v>
       </c>
-      <c r="L44" s="34">
+      <c r="L44" s="35">
         <v>0.56</v>
       </c>
-      <c r="M44" s="34">
+      <c r="M44" s="35">
         <v>0.25</v>
       </c>
-      <c r="N44" s="34">
+      <c r="N44" s="35">
         <v>0.37</v>
       </c>
-      <c r="O44" s="34">
+      <c r="O44" s="35">
         <v>0.21</v>
       </c>
-      <c r="P44" s="34">
+      <c r="P44" s="35">
         <v>0.32</v>
       </c>
-      <c r="Q44" s="34">
+      <c r="Q44" s="35">
         <v>0.44</v>
       </c>
-      <c r="R44" s="34">
+      <c r="R44" s="35">
         <v>0.21</v>
       </c>
-      <c r="S44" s="34">
+      <c r="S44" s="35">
         <v>0.23</v>
       </c>
-      <c r="T44" s="34">
+      <c r="T44" s="35">
         <v>0.85</v>
       </c>
-      <c r="U44" s="34">
+      <c r="U44" s="35">
         <v>1.27</v>
       </c>
-      <c r="V44" s="34">
+      <c r="V44" s="35">
         <v>1.15</v>
       </c>
-      <c r="W44" s="34">
+      <c r="W44" s="35">
         <v>0.98</v>
       </c>
-      <c r="X44" s="34">
+      <c r="X44" s="35">
         <v>0.93</v>
       </c>
-      <c r="Y44" s="34">
+      <c r="Y44" s="35">
         <v>0.56</v>
       </c>
-      <c r="Z44" s="34">
+      <c r="Z44" s="35">
         <v>0.62</v>
       </c>
-      <c r="AA44" s="34">
+      <c r="AA44" s="35">
         <v>0.69</v>
       </c>
-      <c r="AB44" s="34">
+      <c r="AB44" s="35">
         <v>0.36</v>
       </c>
-      <c r="AC44" s="34">
+      <c r="AC44" s="35">
         <v>0.24</v>
       </c>
-      <c r="AD44" s="34">
+      <c r="AD44" s="35">
         <v>0.24</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="32" t="s">
         <v>401</v>
       </c>
-      <c r="B45" s="34">
+      <c r="B45" s="35">
         <v>0.68</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="35">
         <v>0.74</v>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="35">
         <v>0.8</v>
       </c>
-      <c r="E45" s="34">
+      <c r="E45" s="35">
         <v>0.8</v>
       </c>
-      <c r="F45" s="34">
+      <c r="F45" s="35">
         <v>0.9</v>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="35">
         <v>0.73</v>
       </c>
-      <c r="H45" s="34">
+      <c r="H45" s="35">
         <v>0.67</v>
       </c>
-      <c r="I45" s="34">
+      <c r="I45" s="35">
         <v>0.57</v>
       </c>
-      <c r="J45" s="34">
+      <c r="J45" s="35">
         <v>0.54</v>
       </c>
-      <c r="K45" s="34">
+      <c r="K45" s="35">
         <v>0.39</v>
       </c>
-      <c r="L45" s="34">
+      <c r="L45" s="35">
         <v>0.35</v>
       </c>
-      <c r="M45" s="34">
+      <c r="M45" s="35">
         <v>0.31</v>
       </c>
-      <c r="N45" s="34">
+      <c r="N45" s="35">
         <v>0.29</v>
       </c>
-      <c r="O45" s="34">
+      <c r="O45" s="35">
         <v>0.25</v>
       </c>
-      <c r="P45" s="34">
+      <c r="P45" s="35">
         <v>0.47</v>
       </c>
-      <c r="Q45" s="34">
+      <c r="Q45" s="35">
         <v>0.69</v>
       </c>
-      <c r="R45" s="34">
+      <c r="R45" s="35">
         <v>0.79</v>
       </c>
-      <c r="S45" s="34">
+      <c r="S45" s="35">
         <v>0.89</v>
       </c>
-      <c r="T45" s="34">
+      <c r="T45" s="35">
         <v>1.03</v>
       </c>
-      <c r="U45" s="34">
+      <c r="U45" s="35">
         <v>0.99</v>
       </c>
-      <c r="V45" s="34">
+      <c r="V45" s="35">
         <v>0.85</v>
       </c>
-      <c r="W45" s="34">
+      <c r="W45" s="35">
         <v>0.76</v>
       </c>
-      <c r="X45" s="34">
+      <c r="X45" s="35">
         <v>0.62</v>
       </c>
-      <c r="Y45" s="34">
+      <c r="Y45" s="35">
         <v>0.48</v>
       </c>
-      <c r="Z45" s="34">
+      <c r="Z45" s="35">
         <v>0.41</v>
       </c>
-      <c r="AA45" s="33"/>
-      <c r="AB45" s="33"/>
-      <c r="AC45" s="33"/>
-      <c r="AD45" s="33"/>
+      <c r="AA45" s="34"/>
+      <c r="AB45" s="34"/>
+      <c r="AC45" s="34"/>
+      <c r="AD45" s="34"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30"/>
-      <c r="AA46" s="30"/>
-      <c r="AB46" s="30"/>
-      <c r="AC46" s="30"/>
-      <c r="AD46" s="30"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="31"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
+      <c r="S46" s="31"/>
+      <c r="T46" s="31"/>
+      <c r="U46" s="31"/>
+      <c r="V46" s="31"/>
+      <c r="W46" s="31"/>
+      <c r="X46" s="31"/>
+      <c r="Y46" s="31"/>
+      <c r="Z46" s="31"/>
+      <c r="AA46" s="31"/>
+      <c r="AB46" s="31"/>
+      <c r="AC46" s="31"/>
+      <c r="AD46" s="31"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="32" t="s">
         <v>403</v>
       </c>
-      <c r="B47" s="33"/>
-      <c r="C47" s="34">
+      <c r="B47" s="34"/>
+      <c r="C47" s="35">
         <v>61.23</v>
       </c>
-      <c r="D47" s="33"/>
-      <c r="E47" s="34">
+      <c r="D47" s="34"/>
+      <c r="E47" s="35">
         <v>36.25</v>
       </c>
-      <c r="F47" s="34">
+      <c r="F47" s="35">
         <v>15.84</v>
       </c>
-      <c r="G47" s="34">
+      <c r="G47" s="35">
         <v>8.12</v>
       </c>
-      <c r="H47" s="34">
+      <c r="H47" s="35">
         <v>9.19</v>
       </c>
-      <c r="I47" s="34">
+      <c r="I47" s="35">
         <v>10.71</v>
       </c>
-      <c r="J47" s="33"/>
-      <c r="K47" s="34">
+      <c r="J47" s="34"/>
+      <c r="K47" s="35">
         <v>13.57</v>
       </c>
-      <c r="L47" s="34">
+      <c r="L47" s="35">
         <v>17.79</v>
       </c>
-      <c r="M47" s="34">
+      <c r="M47" s="35">
         <v>7.32</v>
       </c>
-      <c r="N47" s="34">
+      <c r="N47" s="35">
         <v>20.92</v>
       </c>
-      <c r="O47" s="34">
+      <c r="O47" s="35">
         <v>12.89</v>
       </c>
-      <c r="P47" s="34">
+      <c r="P47" s="35">
         <v>68.54</v>
       </c>
-      <c r="Q47" s="32">
+      <c r="Q47" s="33">
         <v>366.67</v>
       </c>
-      <c r="R47" s="33"/>
-      <c r="S47" s="33"/>
-      <c r="T47" s="32">
+      <c r="R47" s="34"/>
+      <c r="S47" s="34"/>
+      <c r="T47" s="33">
         <v>454.14</v>
       </c>
-      <c r="U47" s="33"/>
-      <c r="V47" s="34">
+      <c r="U47" s="34"/>
+      <c r="V47" s="35">
         <v>18.4</v>
       </c>
-      <c r="W47" s="34">
+      <c r="W47" s="35">
         <v>26.81</v>
       </c>
-      <c r="X47" s="34">
+      <c r="X47" s="35">
         <v>8.35</v>
       </c>
-      <c r="Y47" s="34">
+      <c r="Y47" s="35">
         <v>12.7</v>
       </c>
-      <c r="Z47" s="33"/>
-      <c r="AA47" s="33"/>
-      <c r="AB47" s="34">
+      <c r="Z47" s="34"/>
+      <c r="AA47" s="34"/>
+      <c r="AB47" s="35">
         <v>7.99</v>
       </c>
-      <c r="AC47" s="34">
+      <c r="AC47" s="35">
         <v>4.98</v>
       </c>
-      <c r="AD47" s="32">
+      <c r="AD47" s="33">
         <v>1514.77</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="32" t="s">
         <v>404</v>
       </c>
-      <c r="B48" s="33"/>
-      <c r="C48" s="34">
+      <c r="B48" s="34"/>
+      <c r="C48" s="35">
         <v>52.74</v>
       </c>
-      <c r="D48" s="34">
+      <c r="D48" s="35">
         <v>27.93</v>
       </c>
-      <c r="E48" s="34">
+      <c r="E48" s="35">
         <v>12.21</v>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="35">
         <v>13.75</v>
       </c>
-      <c r="G48" s="34">
+      <c r="G48" s="35">
         <v>12.99</v>
       </c>
-      <c r="H48" s="34">
+      <c r="H48" s="35">
         <v>16.39</v>
       </c>
-      <c r="I48" s="34">
+      <c r="I48" s="35">
         <v>19.52</v>
       </c>
-      <c r="J48" s="34">
+      <c r="J48" s="35">
         <v>25.93</v>
       </c>
-      <c r="K48" s="34">
+      <c r="K48" s="35">
         <v>13.87</v>
       </c>
-      <c r="L48" s="34">
+      <c r="L48" s="35">
         <v>16.29</v>
       </c>
-      <c r="M48" s="34">
+      <c r="M48" s="35">
         <v>20.69</v>
       </c>
-      <c r="N48" s="33"/>
-      <c r="O48" s="33"/>
-      <c r="P48" s="33"/>
-      <c r="Q48" s="33"/>
-      <c r="R48" s="33"/>
-      <c r="S48" s="33"/>
-      <c r="T48" s="34">
+      <c r="N48" s="34"/>
+      <c r="O48" s="34"/>
+      <c r="P48" s="34"/>
+      <c r="Q48" s="34"/>
+      <c r="R48" s="34"/>
+      <c r="S48" s="34"/>
+      <c r="T48" s="35">
         <v>37.05</v>
       </c>
-      <c r="U48" s="34">
+      <c r="U48" s="35">
         <v>26.43</v>
       </c>
-      <c r="V48" s="34">
+      <c r="V48" s="35">
         <v>17.76</v>
       </c>
-      <c r="W48" s="34">
+      <c r="W48" s="35">
         <v>28.78</v>
       </c>
-      <c r="X48" s="34">
+      <c r="X48" s="35">
         <v>21.4</v>
       </c>
-      <c r="Y48" s="34">
+      <c r="Y48" s="35">
         <v>29.16</v>
       </c>
-      <c r="Z48" s="34">
+      <c r="Z48" s="35">
         <v>52.15</v>
       </c>
-      <c r="AA48" s="33"/>
-      <c r="AB48" s="33"/>
-      <c r="AC48" s="33"/>
-      <c r="AD48" s="33"/>
+      <c r="AA48" s="34"/>
+      <c r="AB48" s="34"/>
+      <c r="AC48" s="34"/>
+      <c r="AD48" s="34"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="29" t="s">
+      <c r="A49" s="30" t="s">
         <v>405</v>
       </c>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
-      <c r="W49" s="30"/>
-      <c r="X49" s="30"/>
-      <c r="Y49" s="30"/>
-      <c r="Z49" s="30"/>
-      <c r="AA49" s="30"/>
-      <c r="AB49" s="30"/>
-      <c r="AC49" s="30"/>
-      <c r="AD49" s="30"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="31"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="31"/>
+      <c r="S49" s="31"/>
+      <c r="T49" s="31"/>
+      <c r="U49" s="31"/>
+      <c r="V49" s="31"/>
+      <c r="W49" s="31"/>
+      <c r="X49" s="31"/>
+      <c r="Y49" s="31"/>
+      <c r="Z49" s="31"/>
+      <c r="AA49" s="31"/>
+      <c r="AB49" s="31"/>
+      <c r="AC49" s="31"/>
+      <c r="AD49" s="31"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="32" t="s">
         <v>406</v>
       </c>
-      <c r="B50" s="33"/>
-      <c r="C50" s="34">
+      <c r="B50" s="34"/>
+      <c r="C50" s="35">
         <v>9.39</v>
       </c>
-      <c r="D50" s="33"/>
-      <c r="E50" s="34">
+      <c r="D50" s="34"/>
+      <c r="E50" s="35">
         <v>3.49</v>
       </c>
-      <c r="F50" s="34">
+      <c r="F50" s="35">
         <v>8.08</v>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="35">
         <v>5.37</v>
       </c>
-      <c r="H50" s="34">
+      <c r="H50" s="35">
         <v>6.91</v>
       </c>
-      <c r="I50" s="34">
+      <c r="I50" s="35">
         <v>4.78</v>
       </c>
-      <c r="J50" s="34">
+      <c r="J50" s="35">
         <v>9.02</v>
       </c>
-      <c r="K50" s="34">
+      <c r="K50" s="35">
         <v>4.54</v>
       </c>
-      <c r="L50" s="34">
+      <c r="L50" s="35">
         <v>6.03</v>
       </c>
-      <c r="M50" s="34">
+      <c r="M50" s="35">
         <v>4.04</v>
       </c>
-      <c r="N50" s="34">
+      <c r="N50" s="35">
         <v>10.01</v>
       </c>
-      <c r="O50" s="34">
+      <c r="O50" s="35">
         <v>4.02</v>
       </c>
-      <c r="P50" s="34">
+      <c r="P50" s="35">
         <v>15.91</v>
       </c>
-      <c r="Q50" s="32">
+      <c r="Q50" s="33">
         <v>2100.58</v>
       </c>
-      <c r="R50" s="33"/>
-      <c r="S50" s="34">
+      <c r="R50" s="34"/>
+      <c r="S50" s="35">
         <v>2.89</v>
       </c>
-      <c r="T50" s="34">
+      <c r="T50" s="35">
         <v>6.78</v>
       </c>
-      <c r="U50" s="34">
+      <c r="U50" s="35">
         <v>15.63</v>
       </c>
-      <c r="V50" s="34">
+      <c r="V50" s="35">
         <v>11.06</v>
       </c>
-      <c r="W50" s="34">
+      <c r="W50" s="35">
         <v>8.02</v>
       </c>
-      <c r="X50" s="34">
+      <c r="X50" s="35">
         <v>9.59</v>
       </c>
-      <c r="Y50" s="34">
+      <c r="Y50" s="35">
         <v>6.83</v>
       </c>
-      <c r="Z50" s="34">
+      <c r="Z50" s="35">
         <v>2.69</v>
       </c>
-      <c r="AA50" s="34">
+      <c r="AA50" s="35">
         <v>5.17</v>
       </c>
-      <c r="AB50" s="34">
+      <c r="AB50" s="35">
         <v>5.89</v>
       </c>
-      <c r="AC50" s="34">
+      <c r="AC50" s="35">
         <v>3.15</v>
       </c>
-      <c r="AD50" s="34">
+      <c r="AD50" s="35">
         <v>4.75</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="32" t="s">
         <v>407</v>
       </c>
-      <c r="B51" s="34">
+      <c r="B51" s="35">
         <v>18.05</v>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="35">
         <v>7.25</v>
       </c>
-      <c r="D51" s="34">
+      <c r="D51" s="35">
         <v>7.0</v>
       </c>
-      <c r="E51" s="34">
+      <c r="E51" s="35">
         <v>5.69</v>
       </c>
-      <c r="F51" s="34">
+      <c r="F51" s="35">
         <v>6.73</v>
       </c>
-      <c r="G51" s="34">
+      <c r="G51" s="35">
         <v>5.97</v>
       </c>
-      <c r="H51" s="34">
+      <c r="H51" s="35">
         <v>6.17</v>
       </c>
-      <c r="I51" s="34">
+      <c r="I51" s="35">
         <v>5.73</v>
       </c>
-      <c r="J51" s="34">
+      <c r="J51" s="35">
         <v>6.44</v>
       </c>
-      <c r="K51" s="34">
+      <c r="K51" s="35">
         <v>5.32</v>
       </c>
-      <c r="L51" s="34">
+      <c r="L51" s="35">
         <v>6.43</v>
       </c>
-      <c r="M51" s="34">
+      <c r="M51" s="35">
         <v>9.02</v>
       </c>
-      <c r="N51" s="34">
+      <c r="N51" s="35">
         <v>36.2</v>
       </c>
-      <c r="O51" s="34">
+      <c r="O51" s="35">
         <v>7.51</v>
       </c>
-      <c r="P51" s="34">
+      <c r="P51" s="35">
         <v>7.22</v>
       </c>
-      <c r="Q51" s="34">
+      <c r="Q51" s="35">
         <v>9.52</v>
       </c>
-      <c r="R51" s="34">
+      <c r="R51" s="35">
         <v>9.6</v>
       </c>
-      <c r="S51" s="34">
+      <c r="S51" s="35">
         <v>8.72</v>
       </c>
-      <c r="T51" s="34">
+      <c r="T51" s="35">
         <v>9.72</v>
       </c>
-      <c r="U51" s="34">
+      <c r="U51" s="35">
         <v>10.22</v>
       </c>
-      <c r="V51" s="34">
+      <c r="V51" s="35">
         <v>6.93</v>
       </c>
-      <c r="W51" s="34">
+      <c r="W51" s="35">
         <v>5.9</v>
       </c>
-      <c r="X51" s="34">
+      <c r="X51" s="35">
         <v>5.48</v>
       </c>
-      <c r="Y51" s="34">
+      <c r="Y51" s="35">
         <v>4.36</v>
       </c>
-      <c r="Z51" s="34">
+      <c r="Z51" s="35">
         <v>4.06</v>
       </c>
-      <c r="AA51" s="33"/>
-      <c r="AB51" s="33"/>
-      <c r="AC51" s="33"/>
-      <c r="AD51" s="33"/>
+      <c r="AA51" s="34"/>
+      <c r="AB51" s="34"/>
+      <c r="AC51" s="34"/>
+      <c r="AD51" s="34"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="30" t="s">
         <v>408</v>
       </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
-      <c r="J52" s="30"/>
-      <c r="K52" s="30"/>
-      <c r="L52" s="30"/>
-      <c r="M52" s="30"/>
-      <c r="N52" s="30"/>
-      <c r="O52" s="30"/>
-      <c r="P52" s="30"/>
-      <c r="Q52" s="30"/>
-      <c r="R52" s="30"/>
-      <c r="S52" s="30"/>
-      <c r="T52" s="30"/>
-      <c r="U52" s="30"/>
-      <c r="V52" s="30"/>
-      <c r="W52" s="30"/>
-      <c r="X52" s="30"/>
-      <c r="Y52" s="30"/>
-      <c r="Z52" s="30"/>
-      <c r="AA52" s="30"/>
-      <c r="AB52" s="30"/>
-      <c r="AC52" s="30"/>
-      <c r="AD52" s="30"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="31"/>
+      <c r="K52" s="31"/>
+      <c r="L52" s="31"/>
+      <c r="M52" s="31"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
+      <c r="Q52" s="31"/>
+      <c r="R52" s="31"/>
+      <c r="S52" s="31"/>
+      <c r="T52" s="31"/>
+      <c r="U52" s="31"/>
+      <c r="V52" s="31"/>
+      <c r="W52" s="31"/>
+      <c r="X52" s="31"/>
+      <c r="Y52" s="31"/>
+      <c r="Z52" s="31"/>
+      <c r="AA52" s="31"/>
+      <c r="AB52" s="31"/>
+      <c r="AC52" s="31"/>
+      <c r="AD52" s="31"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="32" t="s">
         <v>409</v>
       </c>
-      <c r="B53" s="33"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="34">
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="35">
         <v>5.98</v>
       </c>
-      <c r="F53" s="34">
+      <c r="F53" s="35">
         <v>13.13</v>
       </c>
-      <c r="G53" s="34">
+      <c r="G53" s="35">
         <v>9.8</v>
       </c>
-      <c r="H53" s="34">
+      <c r="H53" s="35">
         <v>14.99</v>
       </c>
-      <c r="I53" s="34">
+      <c r="I53" s="35">
         <v>10.97</v>
       </c>
-      <c r="J53" s="34">
+      <c r="J53" s="35">
         <v>16.4</v>
       </c>
-      <c r="K53" s="34">
+      <c r="K53" s="35">
         <v>8.45</v>
       </c>
-      <c r="L53" s="34">
+      <c r="L53" s="35">
         <v>15.66</v>
       </c>
-      <c r="M53" s="33"/>
-      <c r="N53" s="33"/>
-      <c r="O53" s="33"/>
-      <c r="P53" s="33"/>
-      <c r="Q53" s="33"/>
-      <c r="R53" s="33"/>
-      <c r="S53" s="32">
+      <c r="M53" s="34"/>
+      <c r="N53" s="34"/>
+      <c r="O53" s="34"/>
+      <c r="P53" s="34"/>
+      <c r="Q53" s="34"/>
+      <c r="R53" s="34"/>
+      <c r="S53" s="33">
         <v>197.66</v>
       </c>
-      <c r="T53" s="34">
+      <c r="T53" s="35">
         <v>3.59</v>
       </c>
-      <c r="U53" s="34">
+      <c r="U53" s="35">
         <v>10.23</v>
       </c>
-      <c r="V53" s="34">
+      <c r="V53" s="35">
         <v>15.49</v>
       </c>
-      <c r="W53" s="34">
+      <c r="W53" s="35">
         <v>9.8</v>
       </c>
-      <c r="X53" s="34">
+      <c r="X53" s="35">
         <v>13.42</v>
       </c>
-      <c r="Y53" s="34">
+      <c r="Y53" s="35">
         <v>25.3</v>
       </c>
-      <c r="Z53" s="34">
+      <c r="Z53" s="35">
         <v>2.97</v>
       </c>
-      <c r="AA53" s="34">
+      <c r="AA53" s="35">
         <v>6.09</v>
       </c>
-      <c r="AB53" s="34">
+      <c r="AB53" s="35">
         <v>9.12</v>
       </c>
-      <c r="AC53" s="34">
+      <c r="AC53" s="35">
         <v>6.55</v>
       </c>
-      <c r="AD53" s="34">
+      <c r="AD53" s="35">
         <v>11.05</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="B54" s="33"/>
-      <c r="C54" s="34">
+      <c r="B54" s="34"/>
+      <c r="C54" s="35">
         <v>21.29</v>
       </c>
-      <c r="D54" s="34">
+      <c r="D54" s="35">
         <v>16.44</v>
       </c>
-      <c r="E54" s="34">
+      <c r="E54" s="35">
         <v>10.51</v>
       </c>
-      <c r="F54" s="34">
+      <c r="F54" s="35">
         <v>12.7</v>
       </c>
-      <c r="G54" s="34">
+      <c r="G54" s="35">
         <v>11.83</v>
       </c>
-      <c r="H54" s="34">
+      <c r="H54" s="35">
         <v>13.07</v>
       </c>
-      <c r="I54" s="34">
+      <c r="I54" s="35">
         <v>13.83</v>
       </c>
-      <c r="J54" s="34">
+      <c r="J54" s="35">
         <v>21.08</v>
       </c>
-      <c r="K54" s="34">
+      <c r="K54" s="35">
         <v>45.95</v>
       </c>
-      <c r="L54" s="33"/>
-      <c r="M54" s="33"/>
-      <c r="N54" s="33"/>
-      <c r="O54" s="33"/>
-      <c r="P54" s="34">
+      <c r="L54" s="34"/>
+      <c r="M54" s="34"/>
+      <c r="N54" s="34"/>
+      <c r="O54" s="34"/>
+      <c r="P54" s="35">
         <v>20.62</v>
       </c>
-      <c r="Q54" s="34">
+      <c r="Q54" s="35">
         <v>12.62</v>
       </c>
-      <c r="R54" s="34">
+      <c r="R54" s="35">
         <v>10.83</v>
       </c>
-      <c r="S54" s="34">
+      <c r="S54" s="35">
         <v>7.85</v>
       </c>
-      <c r="T54" s="34">
+      <c r="T54" s="35">
         <v>8.13</v>
       </c>
-      <c r="U54" s="34">
+      <c r="U54" s="35">
         <v>12.41</v>
       </c>
-      <c r="V54" s="34">
+      <c r="V54" s="35">
         <v>9.39</v>
       </c>
-      <c r="W54" s="34">
+      <c r="W54" s="35">
         <v>7.7</v>
       </c>
-      <c r="X54" s="34">
+      <c r="X54" s="35">
         <v>7.4</v>
       </c>
-      <c r="Y54" s="34">
+      <c r="Y54" s="35">
         <v>6.19</v>
       </c>
-      <c r="Z54" s="34">
+      <c r="Z54" s="35">
         <v>5.55</v>
       </c>
-      <c r="AA54" s="33"/>
-      <c r="AB54" s="33"/>
-      <c r="AC54" s="33"/>
-      <c r="AD54" s="33"/>
+      <c r="AA54" s="34"/>
+      <c r="AB54" s="34"/>
+      <c r="AC54" s="34"/>
+      <c r="AD54" s="34"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="30" t="s">
         <v>411</v>
       </c>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="30"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="30"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="30"/>
-      <c r="O55" s="30"/>
-      <c r="P55" s="30"/>
-      <c r="Q55" s="30"/>
-      <c r="R55" s="30"/>
-      <c r="S55" s="30"/>
-      <c r="T55" s="30"/>
-      <c r="U55" s="30"/>
-      <c r="V55" s="30"/>
-      <c r="W55" s="30"/>
-      <c r="X55" s="30"/>
-      <c r="Y55" s="30"/>
-      <c r="Z55" s="30"/>
-      <c r="AA55" s="30"/>
-      <c r="AB55" s="30"/>
-      <c r="AC55" s="30"/>
-      <c r="AD55" s="30"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="31"/>
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
+      <c r="P55" s="31"/>
+      <c r="Q55" s="31"/>
+      <c r="R55" s="31"/>
+      <c r="S55" s="31"/>
+      <c r="T55" s="31"/>
+      <c r="U55" s="31"/>
+      <c r="V55" s="31"/>
+      <c r="W55" s="31"/>
+      <c r="X55" s="31"/>
+      <c r="Y55" s="31"/>
+      <c r="Z55" s="31"/>
+      <c r="AA55" s="31"/>
+      <c r="AB55" s="31"/>
+      <c r="AC55" s="31"/>
+      <c r="AD55" s="31"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="32" t="s">
         <v>412</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="33">
         <v>126.75</v>
       </c>
-      <c r="C56" s="34">
+      <c r="C56" s="35">
         <v>10.12</v>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="35">
         <v>31.52</v>
       </c>
-      <c r="E56" s="34">
+      <c r="E56" s="35">
         <v>5.24</v>
       </c>
-      <c r="F56" s="34">
+      <c r="F56" s="35">
         <v>11.63</v>
       </c>
-      <c r="G56" s="34">
+      <c r="G56" s="35">
         <v>9.6</v>
       </c>
-      <c r="H56" s="34">
+      <c r="H56" s="35">
         <v>13.7</v>
       </c>
-      <c r="I56" s="34">
+      <c r="I56" s="35">
         <v>7.14</v>
       </c>
-      <c r="J56" s="34">
+      <c r="J56" s="35">
         <v>11.97</v>
       </c>
-      <c r="K56" s="34">
+      <c r="K56" s="35">
         <v>7.59</v>
       </c>
-      <c r="L56" s="34">
+      <c r="L56" s="35">
         <v>84.24</v>
       </c>
-      <c r="M56" s="32">
+      <c r="M56" s="33">
         <v>667.27</v>
       </c>
-      <c r="N56" s="33"/>
-      <c r="O56" s="33"/>
-      <c r="P56" s="33"/>
-      <c r="Q56" s="33"/>
-      <c r="R56" s="33"/>
-      <c r="S56" s="33"/>
-      <c r="T56" s="34">
+      <c r="N56" s="34"/>
+      <c r="O56" s="34"/>
+      <c r="P56" s="34"/>
+      <c r="Q56" s="34"/>
+      <c r="R56" s="34"/>
+      <c r="S56" s="34"/>
+      <c r="T56" s="35">
         <v>13.67</v>
       </c>
-      <c r="U56" s="34">
+      <c r="U56" s="35">
         <v>70.55</v>
       </c>
-      <c r="V56" s="34">
+      <c r="V56" s="35">
         <v>29.37</v>
       </c>
-      <c r="W56" s="34">
+      <c r="W56" s="35">
         <v>15.65</v>
       </c>
-      <c r="X56" s="34">
+      <c r="X56" s="35">
         <v>24.32</v>
       </c>
-      <c r="Y56" s="34">
+      <c r="Y56" s="35">
         <v>25.3</v>
       </c>
-      <c r="Z56" s="34">
+      <c r="Z56" s="35">
         <v>10.27</v>
       </c>
-      <c r="AA56" s="34">
+      <c r="AA56" s="35">
         <v>16.15</v>
       </c>
-      <c r="AB56" s="34">
+      <c r="AB56" s="35">
         <v>23.05</v>
       </c>
-      <c r="AC56" s="34">
+      <c r="AC56" s="35">
         <v>8.56</v>
       </c>
-      <c r="AD56" s="34">
+      <c r="AD56" s="35">
         <v>22.55</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="31" t="s">
+      <c r="A57" s="32" t="s">
         <v>413</v>
       </c>
-      <c r="B57" s="34">
+      <c r="B57" s="35">
         <v>1.29</v>
       </c>
-      <c r="C57" s="34">
+      <c r="C57" s="35">
         <v>1.3</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="35">
         <v>1.46</v>
       </c>
-      <c r="E57" s="34">
+      <c r="E57" s="35">
         <v>1.62</v>
       </c>
-      <c r="F57" s="34">
+      <c r="F57" s="35">
         <v>2.08</v>
       </c>
-      <c r="G57" s="34">
+      <c r="G57" s="35">
         <v>2.05</v>
       </c>
-      <c r="H57" s="34">
+      <c r="H57" s="35">
         <v>2.37</v>
       </c>
-      <c r="I57" s="34">
+      <c r="I57" s="35">
         <v>2.73</v>
       </c>
-      <c r="J57" s="34">
+      <c r="J57" s="35">
         <v>3.0</v>
       </c>
-      <c r="K57" s="34">
+      <c r="K57" s="35">
         <v>1.97</v>
       </c>
-      <c r="L57" s="34">
+      <c r="L57" s="35">
         <v>1.49</v>
       </c>
-      <c r="M57" s="34">
+      <c r="M57" s="35">
         <v>1.0</v>
       </c>
-      <c r="N57" s="34">
+      <c r="N57" s="35">
         <v>0.81</v>
       </c>
-      <c r="O57" s="34">
+      <c r="O57" s="35">
         <v>0.54</v>
       </c>
-      <c r="P57" s="34">
+      <c r="P57" s="35">
         <v>0.88</v>
       </c>
-      <c r="Q57" s="34">
+      <c r="Q57" s="35">
         <v>1.22</v>
       </c>
-      <c r="R57" s="34">
+      <c r="R57" s="35">
         <v>1.33</v>
       </c>
-      <c r="S57" s="34">
+      <c r="S57" s="35">
         <v>1.42</v>
       </c>
-      <c r="T57" s="34">
+      <c r="T57" s="35">
         <v>1.71</v>
       </c>
-      <c r="U57" s="34">
+      <c r="U57" s="35">
         <v>1.71</v>
       </c>
-      <c r="V57" s="34">
+      <c r="V57" s="35">
         <v>1.53</v>
       </c>
-      <c r="W57" s="34">
+      <c r="W57" s="35">
         <v>1.63</v>
       </c>
-      <c r="X57" s="34">
+      <c r="X57" s="35">
         <v>1.7</v>
       </c>
-      <c r="Y57" s="34">
+      <c r="Y57" s="35">
         <v>1.58</v>
       </c>
-      <c r="Z57" s="34">
+      <c r="Z57" s="35">
         <v>1.71</v>
       </c>
-      <c r="AA57" s="33"/>
-      <c r="AB57" s="33"/>
-      <c r="AC57" s="33"/>
-      <c r="AD57" s="33"/>
+      <c r="AA57" s="34"/>
+      <c r="AB57" s="34"/>
+      <c r="AC57" s="34"/>
+      <c r="AD57" s="34"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="30" t="s">
         <v>414</v>
       </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="30"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30"/>
-      <c r="O58" s="30"/>
-      <c r="P58" s="30"/>
-      <c r="Q58" s="30"/>
-      <c r="R58" s="30"/>
-      <c r="S58" s="30"/>
-      <c r="T58" s="30"/>
-      <c r="U58" s="30"/>
-      <c r="V58" s="30"/>
-      <c r="W58" s="30"/>
-      <c r="X58" s="30"/>
-      <c r="Y58" s="30"/>
-      <c r="Z58" s="30"/>
-      <c r="AA58" s="30"/>
-      <c r="AB58" s="30"/>
-      <c r="AC58" s="30"/>
-      <c r="AD58" s="30"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+      <c r="R58" s="31"/>
+      <c r="S58" s="31"/>
+      <c r="T58" s="31"/>
+      <c r="U58" s="31"/>
+      <c r="V58" s="31"/>
+      <c r="W58" s="31"/>
+      <c r="X58" s="31"/>
+      <c r="Y58" s="31"/>
+      <c r="Z58" s="31"/>
+      <c r="AA58" s="31"/>
+      <c r="AB58" s="31"/>
+      <c r="AC58" s="31"/>
+      <c r="AD58" s="31"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="31" t="s">
+      <c r="A59" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="B59" s="33"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="37">
+      <c r="B59" s="34"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="38">
         <v>-2.92</v>
       </c>
-      <c r="F59" s="34">
+      <c r="F59" s="35">
         <v>0.44</v>
       </c>
-      <c r="G59" s="34">
+      <c r="G59" s="35">
         <v>0.16</v>
       </c>
-      <c r="H59" s="37">
+      <c r="H59" s="38">
         <v>-3.89</v>
       </c>
-      <c r="I59" s="34">
+      <c r="I59" s="35">
         <v>0.65</v>
       </c>
-      <c r="J59" s="37">
+      <c r="J59" s="38">
         <v>-16.71</v>
       </c>
-      <c r="K59" s="34">
+      <c r="K59" s="35">
         <v>0.14</v>
       </c>
-      <c r="L59" s="34">
+      <c r="L59" s="35">
         <v>0.02</v>
       </c>
-      <c r="M59" s="33"/>
-      <c r="N59" s="33"/>
-      <c r="O59" s="33"/>
-      <c r="P59" s="33"/>
-      <c r="Q59" s="33"/>
-      <c r="R59" s="33"/>
-      <c r="S59" s="37">
+      <c r="M59" s="34"/>
+      <c r="N59" s="34"/>
+      <c r="O59" s="34"/>
+      <c r="P59" s="34"/>
+      <c r="Q59" s="34"/>
+      <c r="R59" s="34"/>
+      <c r="S59" s="38">
         <v>-1.98</v>
       </c>
-      <c r="T59" s="34">
+      <c r="T59" s="35">
         <v>0.03</v>
       </c>
-      <c r="U59" s="34">
+      <c r="U59" s="35">
         <v>0.1</v>
       </c>
-      <c r="V59" s="37">
+      <c r="V59" s="38">
         <v>-0.57</v>
       </c>
-      <c r="W59" s="34">
+      <c r="W59" s="35">
         <v>0.37</v>
       </c>
-      <c r="X59" s="34">
+      <c r="X59" s="35">
         <v>0.05</v>
       </c>
-      <c r="Y59" s="37">
+      <c r="Y59" s="38">
         <v>-0.29</v>
       </c>
-      <c r="Z59" s="34">
+      <c r="Z59" s="35">
         <v>0.06</v>
       </c>
-      <c r="AA59" s="34">
+      <c r="AA59" s="35">
         <v>0.04</v>
       </c>
-      <c r="AB59" s="34">
+      <c r="AB59" s="35">
         <v>0.54</v>
       </c>
-      <c r="AC59" s="34">
+      <c r="AC59" s="35">
         <v>0.14</v>
       </c>
-      <c r="AD59" s="33"/>
+      <c r="AD59" s="34"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="31" t="s">
+      <c r="A60" s="32" t="s">
         <v>416</v>
       </c>
-      <c r="B60" s="33"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="34">
+      <c r="B60" s="34"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="35">
         <v>0.57</v>
       </c>
-      <c r="F60" s="34">
+      <c r="F60" s="35">
         <v>0.68</v>
       </c>
-      <c r="G60" s="34">
+      <c r="G60" s="35">
         <v>0.5</v>
       </c>
-      <c r="H60" s="33"/>
-      <c r="I60" s="33"/>
-      <c r="J60" s="33"/>
-      <c r="K60" s="33"/>
-      <c r="L60" s="33"/>
-      <c r="M60" s="33"/>
-      <c r="N60" s="33"/>
-      <c r="O60" s="33"/>
-      <c r="P60" s="33"/>
-      <c r="Q60" s="33"/>
-      <c r="R60" s="33"/>
-      <c r="S60" s="37">
+      <c r="H60" s="34"/>
+      <c r="I60" s="34"/>
+      <c r="J60" s="34"/>
+      <c r="K60" s="34"/>
+      <c r="L60" s="34"/>
+      <c r="M60" s="34"/>
+      <c r="N60" s="34"/>
+      <c r="O60" s="34"/>
+      <c r="P60" s="34"/>
+      <c r="Q60" s="34"/>
+      <c r="R60" s="34"/>
+      <c r="S60" s="38">
         <v>-0.14</v>
       </c>
-      <c r="T60" s="34">
+      <c r="T60" s="35">
         <v>0.12</v>
       </c>
-      <c r="U60" s="37">
+      <c r="U60" s="38">
         <v>-3.49</v>
       </c>
-      <c r="V60" s="37">
+      <c r="V60" s="38">
         <v>-0.94</v>
       </c>
-      <c r="W60" s="34">
+      <c r="W60" s="35">
         <v>0.55</v>
       </c>
-      <c r="X60" s="34">
+      <c r="X60" s="35">
         <v>0.61</v>
       </c>
-      <c r="Y60" s="37">
+      <c r="Y60" s="38">
         <v>-1.02</v>
       </c>
-      <c r="Z60" s="33"/>
-      <c r="AA60" s="33"/>
-      <c r="AB60" s="33"/>
-      <c r="AC60" s="33"/>
-      <c r="AD60" s="33"/>
+      <c r="Z60" s="34"/>
+      <c r="AA60" s="34"/>
+      <c r="AB60" s="34"/>
+      <c r="AC60" s="34"/>
+      <c r="AD60" s="34"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="30" t="s">
         <v>417</v>
       </c>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="30"/>
-      <c r="P61" s="30"/>
-      <c r="Q61" s="30"/>
-      <c r="R61" s="30"/>
-      <c r="S61" s="30"/>
-      <c r="T61" s="30"/>
-      <c r="U61" s="30"/>
-      <c r="V61" s="30"/>
-      <c r="W61" s="30"/>
-      <c r="X61" s="30"/>
-      <c r="Y61" s="30"/>
-      <c r="Z61" s="30"/>
-      <c r="AA61" s="30"/>
-      <c r="AB61" s="30"/>
-      <c r="AC61" s="30"/>
-      <c r="AD61" s="30"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="31"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="31"/>
+      <c r="M61" s="31"/>
+      <c r="N61" s="31"/>
+      <c r="O61" s="31"/>
+      <c r="P61" s="31"/>
+      <c r="Q61" s="31"/>
+      <c r="R61" s="31"/>
+      <c r="S61" s="31"/>
+      <c r="T61" s="31"/>
+      <c r="U61" s="31"/>
+      <c r="V61" s="31"/>
+      <c r="W61" s="31"/>
+      <c r="X61" s="31"/>
+      <c r="Y61" s="31"/>
+      <c r="Z61" s="31"/>
+      <c r="AA61" s="31"/>
+      <c r="AB61" s="31"/>
+      <c r="AC61" s="31"/>
+      <c r="AD61" s="31"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="31" t="s">
+      <c r="A62" s="32" t="s">
         <v>418</v>
       </c>
-      <c r="B62" s="34">
+      <c r="B62" s="35">
         <v>0.88</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="35">
         <v>0.75</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="35">
         <v>0.91</v>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="35">
         <v>0.66</v>
       </c>
-      <c r="F62" s="34">
+      <c r="F62" s="35">
         <v>1.52</v>
       </c>
-      <c r="G62" s="34">
+      <c r="G62" s="35">
         <v>1.01</v>
       </c>
-      <c r="H62" s="34">
+      <c r="H62" s="35">
         <v>0.95</v>
       </c>
-      <c r="I62" s="34">
+      <c r="I62" s="35">
         <v>0.89</v>
       </c>
-      <c r="J62" s="34">
+      <c r="J62" s="35">
         <v>1.25</v>
       </c>
-      <c r="K62" s="34">
+      <c r="K62" s="35">
         <v>0.75</v>
       </c>
-      <c r="L62" s="34">
+      <c r="L62" s="35">
         <v>0.85</v>
       </c>
-      <c r="M62" s="34">
+      <c r="M62" s="35">
         <v>0.63</v>
       </c>
-      <c r="N62" s="34">
+      <c r="N62" s="35">
         <v>0.79</v>
       </c>
-      <c r="O62" s="34">
+      <c r="O62" s="35">
         <v>0.65</v>
       </c>
-      <c r="P62" s="34">
+      <c r="P62" s="35">
         <v>0.8</v>
       </c>
-      <c r="Q62" s="34">
+      <c r="Q62" s="35">
         <v>0.96</v>
       </c>
-      <c r="R62" s="34">
+      <c r="R62" s="35">
         <v>0.58</v>
       </c>
-      <c r="S62" s="34">
+      <c r="S62" s="35">
         <v>0.17</v>
       </c>
-      <c r="T62" s="34">
+      <c r="T62" s="35">
         <v>0.88</v>
       </c>
-      <c r="U62" s="34">
+      <c r="U62" s="35">
         <v>1.23</v>
       </c>
-      <c r="V62" s="34">
+      <c r="V62" s="35">
         <v>1.01</v>
       </c>
-      <c r="W62" s="34">
+      <c r="W62" s="35">
         <v>0.73</v>
       </c>
-      <c r="X62" s="34">
+      <c r="X62" s="35">
         <v>0.75</v>
       </c>
-      <c r="Y62" s="34">
+      <c r="Y62" s="35">
         <v>0.56</v>
       </c>
-      <c r="Z62" s="34">
+      <c r="Z62" s="35">
         <v>0.57</v>
       </c>
-      <c r="AA62" s="34">
+      <c r="AA62" s="35">
         <v>0.68</v>
       </c>
-      <c r="AB62" s="34">
+      <c r="AB62" s="35">
         <v>0.52</v>
       </c>
-      <c r="AC62" s="34">
+      <c r="AC62" s="35">
         <v>0.41</v>
       </c>
-      <c r="AD62" s="34">
+      <c r="AD62" s="35">
         <v>0.44</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="31" t="s">
+      <c r="A63" s="32" t="s">
         <v>419</v>
       </c>
-      <c r="B63" s="34">
+      <c r="B63" s="35">
         <v>0.94</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="35">
         <v>0.96</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="35">
         <v>1.0</v>
       </c>
-      <c r="E63" s="34">
+      <c r="E63" s="35">
         <v>1.0</v>
       </c>
-      <c r="F63" s="34">
+      <c r="F63" s="35">
         <v>1.12</v>
       </c>
-      <c r="G63" s="34">
+      <c r="G63" s="35">
         <v>0.96</v>
       </c>
-      <c r="H63" s="34">
+      <c r="H63" s="35">
         <v>0.93</v>
       </c>
-      <c r="I63" s="34">
+      <c r="I63" s="35">
         <v>0.88</v>
       </c>
-      <c r="J63" s="34">
+      <c r="J63" s="35">
         <v>0.86</v>
       </c>
-      <c r="K63" s="34">
+      <c r="K63" s="35">
         <v>0.74</v>
       </c>
-      <c r="L63" s="34">
+      <c r="L63" s="35">
         <v>0.75</v>
       </c>
-      <c r="M63" s="34">
+      <c r="M63" s="35">
         <v>0.76</v>
       </c>
-      <c r="N63" s="34">
+      <c r="N63" s="35">
         <v>0.76</v>
       </c>
-      <c r="O63" s="34">
+      <c r="O63" s="35">
         <v>0.62</v>
       </c>
-      <c r="P63" s="34">
+      <c r="P63" s="35">
         <v>0.68</v>
       </c>
-      <c r="Q63" s="34">
+      <c r="Q63" s="35">
         <v>0.79</v>
       </c>
-      <c r="R63" s="34">
+      <c r="R63" s="35">
         <v>0.8</v>
       </c>
-      <c r="S63" s="34">
+      <c r="S63" s="35">
         <v>0.82</v>
       </c>
-      <c r="T63" s="34">
+      <c r="T63" s="35">
         <v>0.93</v>
       </c>
-      <c r="U63" s="34">
+      <c r="U63" s="35">
         <v>0.87</v>
       </c>
-      <c r="V63" s="34">
+      <c r="V63" s="35">
         <v>0.73</v>
       </c>
-      <c r="W63" s="34">
+      <c r="W63" s="35">
         <v>0.66</v>
       </c>
-      <c r="X63" s="34">
+      <c r="X63" s="35">
         <v>0.61</v>
       </c>
-      <c r="Y63" s="34">
+      <c r="Y63" s="35">
         <v>0.54</v>
       </c>
-      <c r="Z63" s="34">
+      <c r="Z63" s="35">
         <v>0.52</v>
       </c>
-      <c r="AA63" s="33"/>
-      <c r="AB63" s="33"/>
-      <c r="AC63" s="33"/>
-      <c r="AD63" s="33"/>
+      <c r="AA63" s="34"/>
+      <c r="AB63" s="34"/>
+      <c r="AC63" s="34"/>
+      <c r="AD63" s="34"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="30" t="s">
         <v>420</v>
       </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="30"/>
-      <c r="J64" s="30"/>
-      <c r="K64" s="30"/>
-      <c r="L64" s="30"/>
-      <c r="M64" s="30"/>
-      <c r="N64" s="30"/>
-      <c r="O64" s="30"/>
-      <c r="P64" s="30"/>
-      <c r="Q64" s="30"/>
-      <c r="R64" s="30"/>
-      <c r="S64" s="30"/>
-      <c r="T64" s="30"/>
-      <c r="U64" s="30"/>
-      <c r="V64" s="30"/>
-      <c r="W64" s="30"/>
-      <c r="X64" s="30"/>
-      <c r="Y64" s="30"/>
-      <c r="Z64" s="30"/>
-      <c r="AA64" s="30"/>
-      <c r="AB64" s="30"/>
-      <c r="AC64" s="30"/>
-      <c r="AD64" s="30"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="31"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
+      <c r="M64" s="31"/>
+      <c r="N64" s="31"/>
+      <c r="O64" s="31"/>
+      <c r="P64" s="31"/>
+      <c r="Q64" s="31"/>
+      <c r="R64" s="31"/>
+      <c r="S64" s="31"/>
+      <c r="T64" s="31"/>
+      <c r="U64" s="31"/>
+      <c r="V64" s="31"/>
+      <c r="W64" s="31"/>
+      <c r="X64" s="31"/>
+      <c r="Y64" s="31"/>
+      <c r="Z64" s="31"/>
+      <c r="AA64" s="31"/>
+      <c r="AB64" s="31"/>
+      <c r="AC64" s="31"/>
+      <c r="AD64" s="31"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="31" t="s">
+      <c r="A65" s="32" t="s">
         <v>421</v>
       </c>
-      <c r="B65" s="34">
+      <c r="B65" s="35">
         <v>8.4</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="35">
         <v>8.53</v>
       </c>
-      <c r="D65" s="34">
+      <c r="D65" s="35">
         <v>10.93</v>
       </c>
-      <c r="E65" s="34">
+      <c r="E65" s="35">
         <v>3.71</v>
       </c>
-      <c r="F65" s="34">
+      <c r="F65" s="35">
         <v>7.83</v>
       </c>
-      <c r="G65" s="34">
+      <c r="G65" s="35">
         <v>5.22</v>
       </c>
-      <c r="H65" s="34">
+      <c r="H65" s="35">
         <v>5.02</v>
       </c>
-      <c r="I65" s="34">
+      <c r="I65" s="35">
         <v>6.31</v>
       </c>
-      <c r="J65" s="34">
+      <c r="J65" s="35">
         <v>8.22</v>
       </c>
-      <c r="K65" s="34">
+      <c r="K65" s="35">
         <v>5.93</v>
       </c>
-      <c r="L65" s="34">
+      <c r="L65" s="35">
         <v>9.29</v>
       </c>
-      <c r="M65" s="34">
+      <c r="M65" s="35">
         <v>6.1</v>
       </c>
-      <c r="N65" s="34">
+      <c r="N65" s="35">
         <v>11.63</v>
       </c>
-      <c r="O65" s="34">
+      <c r="O65" s="35">
         <v>8.18</v>
       </c>
-      <c r="P65" s="34">
+      <c r="P65" s="35">
         <v>12.07</v>
       </c>
-      <c r="Q65" s="33"/>
-      <c r="R65" s="34">
+      <c r="Q65" s="34"/>
+      <c r="R65" s="35">
         <v>7.23</v>
       </c>
-      <c r="S65" s="33"/>
-      <c r="T65" s="34">
+      <c r="S65" s="34"/>
+      <c r="T65" s="35">
         <v>4.6</v>
       </c>
-      <c r="U65" s="33"/>
-      <c r="V65" s="34">
+      <c r="U65" s="34"/>
+      <c r="V65" s="35">
         <v>5.98</v>
       </c>
-      <c r="W65" s="33"/>
-      <c r="X65" s="34">
+      <c r="W65" s="34"/>
+      <c r="X65" s="35">
         <v>4.56</v>
       </c>
-      <c r="Y65" s="34">
+      <c r="Y65" s="35">
         <v>5.86</v>
       </c>
-      <c r="Z65" s="34">
+      <c r="Z65" s="35">
         <v>3.93</v>
       </c>
-      <c r="AA65" s="34">
+      <c r="AA65" s="35">
         <v>6.14</v>
       </c>
-      <c r="AB65" s="34">
+      <c r="AB65" s="35">
         <v>4.15</v>
       </c>
-      <c r="AC65" s="34">
+      <c r="AC65" s="35">
         <v>4.2</v>
       </c>
-      <c r="AD65" s="34">
+      <c r="AD65" s="35">
         <v>4.52</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="31" t="s">
+      <c r="A66" s="32" t="s">
         <v>422</v>
       </c>
-      <c r="B66" s="34">
+      <c r="B66" s="35">
         <v>7.01</v>
       </c>
-      <c r="C66" s="34">
+      <c r="C66" s="35">
         <v>6.42</v>
       </c>
-      <c r="D66" s="34">
+      <c r="D66" s="35">
         <v>5.91</v>
       </c>
-      <c r="E66" s="34">
+      <c r="E66" s="35">
         <v>5.54</v>
       </c>
-      <c r="F66" s="34">
+      <c r="F66" s="35">
         <v>6.36</v>
       </c>
-      <c r="G66" s="34">
+      <c r="G66" s="35">
         <v>5.85</v>
       </c>
-      <c r="H66" s="34">
+      <c r="H66" s="35">
         <v>6.4</v>
       </c>
-      <c r="I66" s="34">
+      <c r="I66" s="35">
         <v>7.05</v>
       </c>
-      <c r="J66" s="34">
+      <c r="J66" s="35">
         <v>7.84</v>
       </c>
-      <c r="K66" s="34">
+      <c r="K66" s="35">
         <v>7.75</v>
       </c>
-      <c r="L66" s="34">
+      <c r="L66" s="35">
         <v>9.08</v>
       </c>
-      <c r="M66" s="33"/>
-      <c r="N66" s="33"/>
-      <c r="O66" s="33"/>
-      <c r="P66" s="33"/>
-      <c r="Q66" s="33"/>
-      <c r="R66" s="33"/>
-      <c r="S66" s="33"/>
-      <c r="T66" s="32">
+      <c r="M66" s="34"/>
+      <c r="N66" s="34"/>
+      <c r="O66" s="34"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="34"/>
+      <c r="R66" s="34"/>
+      <c r="S66" s="34"/>
+      <c r="T66" s="33">
         <v>470.63</v>
       </c>
-      <c r="U66" s="33"/>
-      <c r="V66" s="34">
+      <c r="U66" s="34"/>
+      <c r="V66" s="35">
         <v>8.66</v>
       </c>
-      <c r="W66" s="34">
+      <c r="W66" s="35">
         <v>8.93</v>
       </c>
-      <c r="X66" s="34">
+      <c r="X66" s="35">
         <v>4.81</v>
       </c>
-      <c r="Y66" s="34">
+      <c r="Y66" s="35">
         <v>4.76</v>
       </c>
-      <c r="Z66" s="34">
+      <c r="Z66" s="35">
         <v>4.56</v>
       </c>
-      <c r="AA66" s="33"/>
-      <c r="AB66" s="33"/>
-      <c r="AC66" s="33"/>
-      <c r="AD66" s="33"/>
+      <c r="AA66" s="34"/>
+      <c r="AB66" s="34"/>
+      <c r="AC66" s="34"/>
+      <c r="AD66" s="34"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="29" t="s">
+      <c r="A67" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
-      <c r="M67" s="30"/>
-      <c r="N67" s="30"/>
-      <c r="O67" s="30"/>
-      <c r="P67" s="30"/>
-      <c r="Q67" s="30"/>
-      <c r="R67" s="30"/>
-      <c r="S67" s="30"/>
-      <c r="T67" s="30"/>
-      <c r="U67" s="30"/>
-      <c r="V67" s="30"/>
-      <c r="W67" s="30"/>
-      <c r="X67" s="30"/>
-      <c r="Y67" s="30"/>
-      <c r="Z67" s="30"/>
-      <c r="AA67" s="30"/>
-      <c r="AB67" s="30"/>
-      <c r="AC67" s="30"/>
-      <c r="AD67" s="30"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
+      <c r="M67" s="31"/>
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
+      <c r="P67" s="31"/>
+      <c r="Q67" s="31"/>
+      <c r="R67" s="31"/>
+      <c r="S67" s="31"/>
+      <c r="T67" s="31"/>
+      <c r="U67" s="31"/>
+      <c r="V67" s="31"/>
+      <c r="W67" s="31"/>
+      <c r="X67" s="31"/>
+      <c r="Y67" s="31"/>
+      <c r="Z67" s="31"/>
+      <c r="AA67" s="31"/>
+      <c r="AB67" s="31"/>
+      <c r="AC67" s="31"/>
+      <c r="AD67" s="31"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="31" t="s">
+      <c r="A68" s="32" t="s">
         <v>424</v>
       </c>
-      <c r="B68" s="34">
+      <c r="B68" s="35">
         <v>34.07</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="35">
         <v>14.24</v>
       </c>
-      <c r="D68" s="33"/>
-      <c r="E68" s="34">
+      <c r="D68" s="34"/>
+      <c r="E68" s="35">
         <v>7.54</v>
       </c>
-      <c r="F68" s="34">
+      <c r="F68" s="35">
         <v>10.12</v>
       </c>
-      <c r="G68" s="34">
+      <c r="G68" s="35">
         <v>6.29</v>
       </c>
-      <c r="H68" s="34">
+      <c r="H68" s="35">
         <v>7.29</v>
       </c>
-      <c r="I68" s="34">
+      <c r="I68" s="35">
         <v>6.04</v>
       </c>
-      <c r="J68" s="34">
+      <c r="J68" s="35">
         <v>24.3</v>
       </c>
-      <c r="K68" s="34">
+      <c r="K68" s="35">
         <v>8.4</v>
       </c>
-      <c r="L68" s="34">
+      <c r="L68" s="35">
         <v>12.3</v>
       </c>
-      <c r="M68" s="34">
+      <c r="M68" s="35">
         <v>9.62</v>
       </c>
-      <c r="N68" s="34">
+      <c r="N68" s="35">
         <v>17.16</v>
       </c>
-      <c r="O68" s="34">
+      <c r="O68" s="35">
         <v>17.86</v>
       </c>
-      <c r="P68" s="34">
+      <c r="P68" s="35">
         <v>24.32</v>
       </c>
-      <c r="Q68" s="34">
+      <c r="Q68" s="35">
         <v>30.98</v>
       </c>
-      <c r="R68" s="33"/>
-      <c r="S68" s="34">
+      <c r="R68" s="34"/>
+      <c r="S68" s="35">
         <v>4.08</v>
       </c>
-      <c r="T68" s="34">
+      <c r="T68" s="35">
         <v>6.13</v>
       </c>
-      <c r="U68" s="34">
+      <c r="U68" s="35">
         <v>34.15</v>
       </c>
-      <c r="V68" s="34">
+      <c r="V68" s="35">
         <v>6.63</v>
       </c>
-      <c r="W68" s="34">
+      <c r="W68" s="35">
         <v>6.08</v>
       </c>
-      <c r="X68" s="34">
+      <c r="X68" s="35">
         <v>4.92</v>
       </c>
-      <c r="Y68" s="34">
+      <c r="Y68" s="35">
         <v>6.28</v>
       </c>
-      <c r="Z68" s="34">
+      <c r="Z68" s="35">
         <v>4.3</v>
       </c>
-      <c r="AA68" s="34">
+      <c r="AA68" s="35">
         <v>8.55</v>
       </c>
-      <c r="AB68" s="34">
+      <c r="AB68" s="35">
         <v>4.86</v>
       </c>
-      <c r="AC68" s="34">
+      <c r="AC68" s="35">
         <v>3.32</v>
       </c>
-      <c r="AD68" s="34">
+      <c r="AD68" s="35">
         <v>9.25</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="31" t="s">
+      <c r="A69" s="32" t="s">
         <v>425</v>
       </c>
-      <c r="B69" s="34">
+      <c r="B69" s="35">
         <v>17.89</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="35">
         <v>12.52</v>
       </c>
-      <c r="D69" s="34">
+      <c r="D69" s="35">
         <v>10.91</v>
       </c>
-      <c r="E69" s="34">
+      <c r="E69" s="35">
         <v>7.54</v>
       </c>
-      <c r="F69" s="34">
+      <c r="F69" s="35">
         <v>8.36</v>
       </c>
-      <c r="G69" s="34">
+      <c r="G69" s="35">
         <v>7.78</v>
       </c>
-      <c r="H69" s="34">
+      <c r="H69" s="35">
         <v>8.84</v>
       </c>
-      <c r="I69" s="34">
+      <c r="I69" s="35">
         <v>9.65</v>
       </c>
-      <c r="J69" s="34">
+      <c r="J69" s="35">
         <v>13.29</v>
       </c>
-      <c r="K69" s="34">
+      <c r="K69" s="35">
         <v>11.7</v>
       </c>
-      <c r="L69" s="34">
+      <c r="L69" s="35">
         <v>14.62</v>
       </c>
-      <c r="M69" s="34">
+      <c r="M69" s="35">
         <v>17.78</v>
       </c>
-      <c r="N69" s="34">
+      <c r="N69" s="35">
         <v>32.68</v>
       </c>
-      <c r="O69" s="34">
+      <c r="O69" s="35">
         <v>26.84</v>
       </c>
-      <c r="P69" s="34">
+      <c r="P69" s="35">
         <v>12.82</v>
       </c>
-      <c r="Q69" s="34">
+      <c r="Q69" s="35">
         <v>14.87</v>
       </c>
-      <c r="R69" s="34">
+      <c r="R69" s="35">
         <v>10.72</v>
       </c>
-      <c r="S69" s="34">
+      <c r="S69" s="35">
         <v>8.31</v>
       </c>
-      <c r="T69" s="34">
+      <c r="T69" s="35">
         <v>7.7</v>
       </c>
-      <c r="U69" s="34">
+      <c r="U69" s="35">
         <v>8.01</v>
       </c>
-      <c r="V69" s="34">
+      <c r="V69" s="35">
         <v>5.6</v>
       </c>
-      <c r="W69" s="34">
+      <c r="W69" s="35">
         <v>5.82</v>
       </c>
-      <c r="X69" s="34">
+      <c r="X69" s="35">
         <v>5.53</v>
       </c>
-      <c r="Y69" s="34">
+      <c r="Y69" s="35">
         <v>5.11</v>
       </c>
-      <c r="Z69" s="34">
+      <c r="Z69" s="35">
         <v>5.39</v>
       </c>
-      <c r="AA69" s="33"/>
-      <c r="AB69" s="33"/>
-      <c r="AC69" s="33"/>
-      <c r="AD69" s="33"/>
+      <c r="AA69" s="34"/>
+      <c r="AB69" s="34"/>
+      <c r="AC69" s="34"/>
+      <c r="AD69" s="34"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="29" t="s">
+      <c r="A70" s="30" t="s">
         <v>426</v>
       </c>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="30"/>
-      <c r="L70" s="30"/>
-      <c r="M70" s="30"/>
-      <c r="N70" s="30"/>
-      <c r="O70" s="30"/>
-      <c r="P70" s="30"/>
-      <c r="Q70" s="30"/>
-      <c r="R70" s="30"/>
-      <c r="S70" s="30"/>
-      <c r="T70" s="30"/>
-      <c r="U70" s="30"/>
-      <c r="V70" s="30"/>
-      <c r="W70" s="30"/>
-      <c r="X70" s="30"/>
-      <c r="Y70" s="30"/>
-      <c r="Z70" s="30"/>
-      <c r="AA70" s="30"/>
-      <c r="AB70" s="30"/>
-      <c r="AC70" s="30"/>
-      <c r="AD70" s="30"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="31"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
+      <c r="M70" s="31"/>
+      <c r="N70" s="31"/>
+      <c r="O70" s="31"/>
+      <c r="P70" s="31"/>
+      <c r="Q70" s="31"/>
+      <c r="R70" s="31"/>
+      <c r="S70" s="31"/>
+      <c r="T70" s="31"/>
+      <c r="U70" s="31"/>
+      <c r="V70" s="31"/>
+      <c r="W70" s="31"/>
+      <c r="X70" s="31"/>
+      <c r="Y70" s="31"/>
+      <c r="Z70" s="31"/>
+      <c r="AA70" s="31"/>
+      <c r="AB70" s="31"/>
+      <c r="AC70" s="31"/>
+      <c r="AD70" s="31"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="31" t="s">
+      <c r="A71" s="32" t="s">
         <v>427</v>
       </c>
-      <c r="B71" s="33"/>
-      <c r="C71" s="34">
+      <c r="B71" s="34"/>
+      <c r="C71" s="35">
         <v>98.31</v>
       </c>
-      <c r="D71" s="33"/>
-      <c r="E71" s="34">
+      <c r="D71" s="34"/>
+      <c r="E71" s="35">
         <v>47.67</v>
       </c>
-      <c r="F71" s="34">
+      <c r="F71" s="35">
         <v>17.88</v>
       </c>
-      <c r="G71" s="34">
+      <c r="G71" s="35">
         <v>9.19</v>
       </c>
-      <c r="H71" s="34">
+      <c r="H71" s="35">
         <v>11.06</v>
       </c>
-      <c r="I71" s="34">
+      <c r="I71" s="35">
         <v>17.45</v>
       </c>
-      <c r="J71" s="33"/>
-      <c r="K71" s="34">
+      <c r="J71" s="34"/>
+      <c r="K71" s="35">
         <v>20.11</v>
       </c>
-      <c r="L71" s="34">
+      <c r="L71" s="35">
         <v>26.81</v>
       </c>
-      <c r="M71" s="34">
+      <c r="M71" s="35">
         <v>18.3</v>
       </c>
-      <c r="N71" s="34">
+      <c r="N71" s="35">
         <v>44.77</v>
       </c>
-      <c r="O71" s="34">
+      <c r="O71" s="35">
         <v>40.19</v>
       </c>
-      <c r="P71" s="32">
+      <c r="P71" s="33">
         <v>172.47</v>
       </c>
-      <c r="Q71" s="32">
+      <c r="Q71" s="33">
         <v>801.08</v>
       </c>
-      <c r="R71" s="33"/>
-      <c r="S71" s="33"/>
-      <c r="T71" s="32">
+      <c r="R71" s="34"/>
+      <c r="S71" s="34"/>
+      <c r="T71" s="33">
         <v>473.85</v>
       </c>
-      <c r="U71" s="33"/>
-      <c r="V71" s="34">
+      <c r="U71" s="34"/>
+      <c r="V71" s="35">
         <v>16.23</v>
       </c>
-      <c r="W71" s="34">
+      <c r="W71" s="35">
         <v>20.02</v>
       </c>
-      <c r="X71" s="34">
+      <c r="X71" s="35">
         <v>6.76</v>
       </c>
-      <c r="Y71" s="34">
+      <c r="Y71" s="35">
         <v>12.76</v>
       </c>
-      <c r="Z71" s="33"/>
-      <c r="AA71" s="33"/>
-      <c r="AB71" s="34">
+      <c r="Z71" s="34"/>
+      <c r="AA71" s="34"/>
+      <c r="AB71" s="35">
         <v>11.59</v>
       </c>
-      <c r="AC71" s="34">
+      <c r="AC71" s="35">
         <v>8.45</v>
       </c>
-      <c r="AD71" s="32">
+      <c r="AD71" s="33">
         <v>2758.27</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="31" t="s">
+      <c r="A72" s="32" t="s">
         <v>428</v>
       </c>
-      <c r="B72" s="33"/>
-      <c r="C72" s="34">
+      <c r="B72" s="34"/>
+      <c r="C72" s="35">
         <v>57.78</v>
       </c>
-      <c r="D72" s="34">
+      <c r="D72" s="35">
         <v>31.65</v>
       </c>
-      <c r="E72" s="34">
+      <c r="E72" s="35">
         <v>15.04</v>
       </c>
-      <c r="F72" s="34">
+      <c r="F72" s="35">
         <v>15.93</v>
       </c>
-      <c r="G72" s="34">
+      <c r="G72" s="35">
         <v>15.57</v>
       </c>
-      <c r="H72" s="34">
+      <c r="H72" s="35">
         <v>20.91</v>
       </c>
-      <c r="I72" s="34">
+      <c r="I72" s="35">
         <v>29.65</v>
       </c>
-      <c r="J72" s="34">
+      <c r="J72" s="35">
         <v>41.99</v>
       </c>
-      <c r="K72" s="34">
+      <c r="K72" s="35">
         <v>26.13</v>
       </c>
-      <c r="L72" s="34">
+      <c r="L72" s="35">
         <v>34.62</v>
       </c>
-      <c r="M72" s="34">
+      <c r="M72" s="35">
         <v>49.98</v>
       </c>
-      <c r="N72" s="33"/>
-      <c r="O72" s="33"/>
-      <c r="P72" s="33"/>
-      <c r="Q72" s="33"/>
-      <c r="R72" s="33"/>
-      <c r="S72" s="33"/>
-      <c r="T72" s="34">
+      <c r="N72" s="34"/>
+      <c r="O72" s="34"/>
+      <c r="P72" s="34"/>
+      <c r="Q72" s="34"/>
+      <c r="R72" s="34"/>
+      <c r="S72" s="34"/>
+      <c r="T72" s="35">
         <v>33.19</v>
       </c>
-      <c r="U72" s="34">
+      <c r="U72" s="35">
         <v>23.15</v>
       </c>
-      <c r="V72" s="34">
+      <c r="V72" s="35">
         <v>15.19</v>
       </c>
-      <c r="W72" s="34">
+      <c r="W72" s="35">
         <v>26.63</v>
       </c>
-      <c r="X72" s="34">
+      <c r="X72" s="35">
         <v>21.86</v>
       </c>
-      <c r="Y72" s="34">
+      <c r="Y72" s="35">
         <v>32.41</v>
       </c>
-      <c r="Z72" s="34">
+      <c r="Z72" s="35">
         <v>59.06</v>
       </c>
-      <c r="AA72" s="33"/>
-      <c r="AB72" s="33"/>
-      <c r="AC72" s="33"/>
-      <c r="AD72" s="33"/>
+      <c r="AA72" s="34"/>
+      <c r="AB72" s="34"/>
+      <c r="AC72" s="34"/>
+      <c r="AD72" s="34"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
